--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_level.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_level.xlsx
@@ -622,79 +622,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-15.71432506593403</v>
+        <v>-15.4388985509312</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.02708560671429439</v>
+        <v>-3.951191594454151</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.404237536968807</v>
+        <v>-3.015488859687167</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.115078584511231</v>
+        <v>-3.725778917405741</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.853550817806905</v>
+        <v>-11.1630552020018</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.35750997980141</v>
+        <v>-13.34824905127684</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.440350608130878</v>
+        <v>-9.382003270305084</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-11.40988947768255</v>
+        <v>-14.40085775104133</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.37240414154117</v>
+        <v>-11.99408441094033</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.455209234569324</v>
+        <v>-10.39632077790451</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-14.56881396657239</v>
+        <v>-12.49784559378227</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.15792350556054</v>
+        <v>-15.1514210004058</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-15.97681009666585</v>
+        <v>-16.27569343390767</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-16.20218577519658</v>
+        <v>-14.12693421800714</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-14.16873506946743</v>
+        <v>-17.16191781547788</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-10.88281715404412</v>
+        <v>-14.19869710382712</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-8.322911109475427</v>
+        <v>-11.96062539752967</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-3.034495523814087</v>
+        <v>-4.938746294176909</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1207933852253547</v>
+        <v>-2.347167585008123</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.06615954419543613</v>
+        <v>-2.161131072031509</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.476463973828956</v>
+        <v>-2.703608166332742</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.5523285447201758</v>
+        <v>-2.780006660069553</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>5.126248545525065</v>
+        <v>2.254219052540265</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>5.052054101483762</v>
+        <v>2.179294615043361</v>
       </c>
     </row>
     <row r="7">
@@ -704,79 +704,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.247798285525697</v>
+        <v>-2.196004599622533</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-17.06995283355995</v>
+        <v>-13.88393445943277</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-13.27667360153816</v>
+        <v>-9.639303939802552</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.37545777846712</v>
+        <v>-4.671918657607009</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-14.35819517800092</v>
+        <v>-10.68817915817593</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.55877148016</v>
+        <v>-1.980473381469729</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-9.713017323199523</v>
+        <v>0.09373758495848961</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-12.61189634130533</v>
+        <v>-3.026235129710194</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9.955298908283623</v>
+        <v>-2.986476561453721</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-10.72912174209694</v>
+        <v>-6.602028490231305</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7.8375388425507</v>
+        <v>-3.484876796204595</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.495751018070727</v>
+        <v>-0.9165845241624311</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.249520895638945</v>
+        <v>9.353783525812823</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-9.464939221586995</v>
+        <v>0.5910189497411835</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-12.74931587743163</v>
+        <v>-5.763592995243393</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-12.1593506528047</v>
+        <v>-5.172340551198268</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-12.29696494468495</v>
+        <v>-8.158660419530882</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-7.152022729583521</v>
+        <v>-2.561962303476641</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-12.19340207810486</v>
+        <v>-8.05268824487473</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-17.26686910360861</v>
+        <v>-10.72206928123921</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-15.18559984622506</v>
+        <v>-8.412625179405076</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-20.52589720026541</v>
+        <v>-14.20157806402955</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-22.88798991547274</v>
+        <v>-16.78761057554467</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-28.23386339495946</v>
+        <v>-22.58261014686313</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.295590260450005</v>
+        <v>7.531030546778503</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.515212608840677</v>
+        <v>1.118246977213794</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-10.39862949572363</v>
+        <v>-4.365925133069787</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-13.59694042662215</v>
+        <v>-7.105143147553427</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-18.93459907598035</v>
+        <v>-7.440429955830638</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-11.29559088136401</v>
+        <v>-11.31593174469427</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-12.06787083823171</v>
+        <v>-12.08705673838697</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-19.81164121597084</v>
+        <v>-18.45958706842707</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-19.77707959368102</v>
+        <v>-18.42463224839281</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-25.53235739920675</v>
+        <v>-21.23176886566499</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-35.22665800005036</v>
+        <v>-29.09569941756157</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-35.5154126947039</v>
+        <v>-29.38213444945298</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-34.15642851701882</v>
+        <v>-30.5112222783119</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-34.38716171134092</v>
+        <v>-34.80959691617494</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-37.54786211336258</v>
+        <v>-35.4762847637021</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-34.47185031069601</v>
+        <v>-36.930066649061</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-32.1218399214417</v>
+        <v>-33.00231919393033</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-37.22747847218326</v>
+        <v>-35.15434828432561</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-34.5268474857718</v>
+        <v>-32.91184776525265</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-31.85359155814178</v>
+        <v>-32.73528977678883</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-34.90381893981517</v>
+        <v>-33.28728274728255</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-34.99033835809666</v>
+        <v>-35.4127113147072</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-37.22549624094328</v>
+        <v>-35.14914227689028</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-42.31281076338168</v>
+        <v>-39.3173040244135</v>
       </c>
     </row>
     <row r="9">
@@ -868,79 +868,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.8760615008445711</v>
+        <v>-7.160558007350431</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.756677645576524</v>
+        <v>-14.59028001917576</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.670052942005171</v>
+        <v>-12.47531542658935</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.660875082125983</v>
+        <v>-2.540826090189071</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.300934845659967</v>
+        <v>-6.425031298393534</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.559913599443313</v>
+        <v>-9.792408742914013</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.092847180268926</v>
+        <v>-14.11559605598063</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.843721943310612</v>
+        <v>-7.288774063327708</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.803729354786121</v>
+        <v>-7.250501102973004</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.340432876384455</v>
+        <v>-11.57794799026718</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.834736501172749</v>
+        <v>-14.86501033316161</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.115179395030196</v>
+        <v>-15.14719913351677</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.23946005842798</v>
+        <v>-16.27199588431553</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-6.69352842738401</v>
+        <v>-9.376308056763037</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-10.12262309074914</v>
+        <v>-13.59668741879905</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-17.8447912408265</v>
+        <v>-16.57062071542653</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-26.2996235003029</v>
+        <v>-27.40062719552046</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-26.41282759062975</v>
+        <v>-31.07880979193617</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-26.20528225378492</v>
+        <v>-30.87301150684803</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-26.02662947596598</v>
+        <v>-30.69606441913026</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-26.57754289656954</v>
+        <v>-34.81573132250389</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-29.43774971851343</v>
+        <v>-34.90230642559201</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-26.39528178394518</v>
+        <v>-34.63884027189182</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-26.47947743004841</v>
+        <v>-34.72546728971962</v>
       </c>
     </row>
     <row r="10">
@@ -950,243 +950,243 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.633646978175463</v>
+        <v>-3.613932774640283</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.8936760122325893</v>
+        <v>-0.4012177235361776</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.884040159767501</v>
+        <v>5.265806867420473</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.036445614588835</v>
+        <v>-2.540574470565602</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.81306203969941</v>
+        <v>0.6759510901316759</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>9.215052995180059</v>
+        <v>7.964928512317456</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.449451629898896</v>
+        <v>10.75244387443529</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8.17526706139892</v>
+        <v>10.47939355067646</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.108123727105628</v>
+        <v>6.968566022373949</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.33945993428884</v>
+        <v>9.757348945633794</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.502595243518599</v>
+        <v>10.03401780975442</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.888127415477484</v>
+        <v>6.20162015052783</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.217911290802746</v>
+        <v>8.642587994621699</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1166359880720549</v>
+        <v>1.304827615078565</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.7735916749464025</v>
+        <v>0.6492918068416813</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-3.297273258880928</v>
+        <v>-2.320106883816095</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-3.432309354612869</v>
+        <v>-2.454616730902927</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.538475357102122</v>
+        <v>-2.560297661789676</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-6.443966588727598</v>
+        <v>-5.911508545665079</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-9.380311488846992</v>
+        <v>-9.293807129882794</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-6.804091037630933</v>
+        <v>-6.270725575537462</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-6.882167737228109</v>
+        <v>-6.34849659109846</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-12.85771692817506</v>
+        <v>-13.21683173793377</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-16.0628107633804</v>
+        <v>-16.86832443257595</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 3.898</t>
+          <t>X ≈ 3.899</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.5031997487503617</v>
+        <v>-0.06796541387392807</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.278531578889137</v>
+        <v>3.145446261023295</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.12680703540935</v>
+        <v>8.812922386835574</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.279532191899882</v>
+        <v>4.557390168399337</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>10.06056344968686</v>
+        <v>11.32579656725053</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.964013660485506</v>
+        <v>4.413027234344455</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.196248421575319</v>
+        <v>3.646985702039665</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.919844693793884</v>
+        <v>3.371778278474224</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.107691083762255</v>
+        <v>6.967980068972182</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.339123065642916</v>
+        <v>2.645398735888818</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.614617055823111</v>
+        <v>-0.6368608961421032</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>8.489027320452394</v>
+        <v>2.643373788137183</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>15.67407971535387</v>
+        <v>12.20103763406987</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>15.45877732517125</v>
+        <v>15.54518548888849</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>14.80680642455485</v>
+        <v>14.89421243906509</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>15.40524092368835</v>
+        <v>15.49183289653747</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>15.27613181095822</v>
+        <v>15.36296530524572</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>15.17589213321214</v>
+        <v>15.26292581223733</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>15.39644246347122</v>
+        <v>15.48320966485445</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>15.5880962486718</v>
+        <v>15.67463854592067</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>15.05014716411916</v>
+        <v>15.13752695427011</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>14.97898865551887</v>
+        <v>15.06652658381496</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>15.25840246371353</v>
+        <v>15.34558747137801</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>15.18718923661889</v>
+        <v>15.27453271027957</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 3.928</t>
+          <t>X ≈ 3.929</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.7133675962450496</v>
+        <v>17.65893537085024</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.076294510831318</v>
+        <v>17.33116030339083</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.02120727271407</v>
+        <v>30.09789360741163</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>14.31575988478436</v>
+        <v>36.49576169772959</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>19.80439586033372</v>
+        <v>43.27379484796597</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>14.14852990963931</v>
+        <v>36.37174950060557</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>25.08572630807542</v>
+        <v>42.7202137451579</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>24.81696233458891</v>
+        <v>42.45746639690437</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>30.71964341758629</v>
+        <v>35.40268866942702</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>29.9593117261293</v>
+        <v>41.75601797143253</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>24.38502108674356</v>
+        <v>42.04306048330525</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>35.83452249929357</v>
+        <v>41.77892401051909</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>40.58561573526326</v>
+        <v>40.67183648836303</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>40.37834482307957</v>
+        <v>40.46491392694176</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>28.00352480345346</v>
+        <v>39.82197556295642</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>28.60621614113487</v>
+        <v>40.4275831369346</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>28.48139046473874</v>
+        <v>40.3067320681709</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>28.38543369435991</v>
+        <v>40.21471088435393</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>28.61026429203873</v>
+        <v>40.44301268557948</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>28.80620359031901</v>
+        <v>40.64246718630113</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>28.27255397080581</v>
+        <v>40.11339775259501</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>34.08427815682577</v>
+        <v>40.05043677729115</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>40.25033749166791</v>
+        <v>40.33753871549614</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>40.18718923661889</v>
+        <v>40.27453271028038</v>
       </c>
     </row>
     <row r="13">
@@ -1196,243 +1196,243 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.621332155192313</v>
+        <v>-3.61365269541718</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-11.08886835878771</v>
+        <v>-18.13325370066827</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.172901535439038</v>
+        <v>-8.926378303705903</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.794098052753036</v>
+        <v>1.007108519882408</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5928215182628662</v>
+        <v>-2.875679331717095</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7796910758412352</v>
+        <v>-2.69014298082331</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.852876855778987</v>
+        <v>3.645495181817175</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.419531012711701</v>
+        <v>3.370424156041864</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2249744163925982</v>
+        <v>6.966459427370879</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.84919637208553</v>
+        <v>6.19967422446436</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7210674109604298</v>
+        <v>-0.6375702364917615</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.84551705005633</v>
+        <v>-0.9152156648448937</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7251933872818768</v>
+        <v>1.52300758067674</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.353213890864147</v>
+        <v>-2.256256141493949</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>5.546618774203637</v>
+        <v>0.6483750431253199</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>11.84170205104079</v>
+        <v>8.366021370809122</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>14.56229700942644</v>
+        <v>15.36180911524229</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>23.01680034863413</v>
+        <v>25.95553689622606</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>26.09256475780196</v>
+        <v>29.74509827010312</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>31.99473192643533</v>
+        <v>37.07493735155347</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>34.31664711772519</v>
+        <v>40.11287916473416</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>34.25187182125257</v>
+        <v>40.05009236817521</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>34.53768584172257</v>
+        <v>40.33736510853024</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>34.47290352233317</v>
+        <v>36.70310413885181</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 3.99</t>
+          <t>X ≈ 3.991</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.323246909587446</v>
+        <v>10.56501599550791</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>13.41038931595729</v>
+        <v>11.41798775823852</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9.40293054123746</v>
+        <v>13.53853099404945</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>16.43640053033585</v>
+        <v>12.83316067412352</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.20763564260223</v>
+        <v>10.1381961641647</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12.398326991087</v>
+        <v>9.14454825652507</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12.925256048534</v>
+        <v>9.563744476418854</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>11.36092197824967</v>
+        <v>9.290740021579325</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>12.69764922284535</v>
+        <v>9.33433819211956</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>15.80991482029448</v>
+        <v>12.12349821359452</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>14.79647050430682</v>
+        <v>11.2162252071843</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.64275711002429</v>
+        <v>8.571009862969007</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.230106936776565</v>
+        <v>9.825840648160032</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.012641119361284</v>
+        <v>13.16907659160519</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>7.358789719735384</v>
+        <v>10.14380039613059</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>9.250054256205438</v>
+        <v>11.9272149870356</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>6.527806957897724</v>
+        <v>8.234200699940288</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>7.720941457517931</v>
+        <v>9.320076271607164</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>10.53241526326099</v>
+        <v>11.91571056501069</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>10.72274622350167</v>
+        <v>12.10625216186807</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>11.48101568665883</v>
+        <v>12.75767682277496</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>11.40907794794894</v>
+        <v>15.06569191689193</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>12.98598584092502</v>
+        <v>17.72532744770054</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>16.81056585999552</v>
+        <v>22.41738985313751</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 4.021</t>
+          <t>X ≈ 4.022</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1835100109813794</v>
+        <v>-3.043853457449778</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.183611107316324</v>
+        <v>3.46791684746966</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>8.208860992180192</v>
+        <v>7.745242006529885</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>14.04872261831411</v>
+        <v>15.0297944735641</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>13.69193208347819</v>
+        <v>19.2705432612599</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>13.88332746297547</v>
+        <v>19.46377378018069</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>16.39727497406671</v>
+        <v>20.98849201354007</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>17.21940423189601</v>
+        <v>21.86285120310343</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>18.35914828915079</v>
+        <v>24.19798505752578</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>17.59527084760367</v>
+        <v>23.43719844489863</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>15.68793936676663</v>
+        <v>21.43081943498981</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>13.22711693403973</v>
+        <v>18.87168365910222</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>13.20457606872678</v>
+        <v>16.61266592238312</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>16.27448686357771</v>
+        <v>18.68954493464385</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>15.62375885139255</v>
+        <v>19.18652062548234</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>15.1266416229649</v>
+        <v>17.49309897082189</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>17.19067237306884</v>
+        <v>18.51230293325878</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>17.09138140063494</v>
+        <v>19.56072496720786</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>15.11892972322079</v>
+        <v>16.34047569429475</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>16.40841309133062</v>
+        <v>18.82845776105626</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>18.06697435472592</v>
+        <v>19.44136830871209</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>21.2919699097171</v>
+        <v>20.52114445414383</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>22.67272242856085</v>
+        <v>24.24984554377991</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>20.40696945639911</v>
+        <v>21.8837281125795</v>
       </c>
     </row>
     <row r="16">
@@ -1442,243 +1442,243 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.891395209177368</v>
+        <v>-0.4634295554463961</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.255696976411393</v>
+        <v>-0.009921602971424193</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2058201951752778</v>
+        <v>-0.6528889535154789</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.531503398256987</v>
+        <v>-3.728074291295556</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.636480213903525</v>
+        <v>-8.003886925785402</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.451625658738912</v>
+        <v>-5.454074295184</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.093989944446115</v>
+        <v>-7.012222576840074</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.628280828324122</v>
+        <v>-6.501308339610077</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.099628441158011</v>
+        <v>-3.30553141710886</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.858361103531998</v>
+        <v>3.821934803160886</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.008846946781063</v>
+        <v>4.88822180252776</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.734563427995667</v>
+        <v>4.613667545817037</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.236656856687759</v>
+        <v>5.86720011876357</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>14.13796223301839</v>
+        <v>11.18533023700734</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>11.73831008645998</v>
+        <v>8.952096141140764</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>13.210765843179</v>
+        <v>11.13097250836549</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>9.581768596799563</v>
+        <v>8.626604536911557</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>7.729546740950759</v>
+        <v>6.148958381226151</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>7.948326243187388</v>
+        <v>6.366996234956865</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>5.510342569911749</v>
+        <v>4.178462132328455</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>6.722382385333226</v>
+        <v>6.016824316782582</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.143021894217398</v>
+        <v>3.564425905375373</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.173071455711955</v>
+        <v>3.047120748350608</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.467890991004865</v>
+        <v>1.385643821391305</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 4.083</t>
+          <t>X ≈ 4.085</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.65044811004357</v>
+        <v>1.234839780100017</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.368925661405449</v>
+        <v>5.375730391058774</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>7.40767333773428</v>
+        <v>6.931501915849225</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.228257020245593</v>
+        <v>6.970492084897096</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.563521949212713</v>
+        <v>5.148466181958256</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.751581857457381</v>
+        <v>3.842707452292913</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.374769903420294</v>
+        <v>3.824493762866524</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>9.660882793899809</v>
+        <v>8.781906395379011</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>10.39943251823453</v>
+        <v>10.31989674012338</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>8.936564537857265</v>
+        <v>8.80585030998553</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>9.911062978214559</v>
+        <v>10.58052667159263</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>8.942171194336908</v>
+        <v>10.30849806610132</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.431040739569141</v>
+        <v>8.443754365200526</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.909282012678197</v>
+        <v>9.724577795644322</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>9.044515649808062</v>
+        <v>12.07137425134312</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>7.549781888430722</v>
+        <v>9.670038255319241</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.327174497388441</v>
+        <v>7.29112607297192</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.829034996168623</v>
+        <v>4.938801675651234</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.650622493588983</v>
+        <v>5.156595143783228</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.442407287253587</v>
+        <v>3.844029844344533</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4964199795913302</v>
+        <v>1.050871181413513</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.223273227689134</v>
+        <v>3.230165387829103</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.198366777576908</v>
+        <v>5.009467167674515</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.921454970884469</v>
+        <v>6.439946244114957</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 4.114</t>
+          <t>X ≈ 4.115</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.277966379514517</v>
+        <v>-1.746876657013232</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.534397167910704</v>
+        <v>-4.319635867639896</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.078052226203177</v>
+        <v>-6.497637723934268</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.864434001595427</v>
+        <v>-6.463888659029166</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1831323412413752</v>
+        <v>-3.065279343238572</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.855207406502316</v>
+        <v>-5.866276119795323</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.806626592728065</v>
+        <v>-1.406821631090871</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.19965119486691</v>
+        <v>-0.1901792893008292</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-6.277065300042018</v>
+        <v>-3.141240464806437</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-9.871111717384977</v>
+        <v>-7.650465956190033</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-11.01082715480204</v>
+        <v>-9.622813517329483</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-12.70263416886566</v>
+        <v>-12.89543241427311</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-18.77138313548003</v>
+        <v>-19.26001924595148</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-21.11884960834664</v>
+        <v>-23.98169805603619</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-21.78226485632417</v>
+        <v>-23.89607113356021</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-21.19702343817307</v>
+        <v>-24.06174245443388</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-19.21607266621466</v>
+        <v>-22.70372913828248</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-20.03555962932703</v>
+        <v>-23.56677275167375</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-17.70368176023666</v>
+        <v>-22.60958347490974</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-17.52319800051642</v>
+        <v>-23.93261260986554</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-17.36386649709875</v>
+        <v>-22.98121060566869</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-17.44601426829152</v>
+        <v>-22.31400215679999</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-15.75975663818367</v>
+        <v>-19.04147795760228</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-15.84117955770719</v>
+        <v>-19.12396353032113</v>
       </c>
     </row>
     <row r="19">
@@ -1688,161 +1688,161 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.098471210595221</v>
+        <v>-3.125474337151815</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-9.788752314431875</v>
+        <v>-8.751632255447618</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-8.060824615269794</v>
+        <v>-7.297993491772182</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-14.57734441202962</v>
+        <v>-11.3799947326372</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-16.52621935972616</v>
+        <v>-15.08671588567965</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-16.87259103627203</v>
+        <v>-16.35067458093145</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-21.34452116560517</v>
+        <v>-20.49882286695087</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-20.57424111600842</v>
+        <v>-21.74937091429177</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-21.60036797949837</v>
+        <v>-23.16615426814538</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-20.79237817408587</v>
+        <v>-22.49597982076317</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-19.99659390792474</v>
+        <v>-21.74743463457371</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-20.80942581479722</v>
+        <v>-21.54816947267035</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-18.76096990304509</v>
+        <v>-21.70852818741511</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-17.40068519746917</v>
+        <v>-20.0042229858562</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-14.88388533626237</v>
+        <v>-18.73277620400499</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-13.76700345338298</v>
+        <v>-18.14811599689624</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-13.90594300693609</v>
+        <v>-17.32058068032841</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-15.07759920970059</v>
+        <v>-16.94809663645184</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-15.92995135383433</v>
+        <v>-17.22428125422609</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-15.21863417468368</v>
+        <v>-15.5908894973518</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-15.76754444571012</v>
+        <v>-15.16954160942933</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-16.91279616219245</v>
+        <v>-15.73652575762928</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-15.58175910531978</v>
+        <v>-15.95401794446922</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-16.19578948678536</v>
+        <v>-16.03614690137011</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 4.176</t>
+          <t>X ≈ 4.177</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3214508408232106</v>
+        <v>2.162944534531</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2110098925274571</v>
+        <v>2.314139180027915</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.114738419137701</v>
+        <v>-0.5573103506783781</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.294737774324666</v>
+        <v>-0.3023708954475879</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.294633314570149</v>
+        <v>0.8126679244453783</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.051137301006968</v>
+        <v>0.5198825981371087</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.345328286085504</v>
+        <v>-0.2450818147413827</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7342981594669808</v>
+        <v>1.886227797133003</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6954909857553346</v>
+        <v>0.962139312476495</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8997942989727505</v>
+        <v>2.605564562342757</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.594963600892271</v>
+        <v>4.81119498407282</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.215372241830416</v>
+        <v>4.53873333844853</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.7284235516010682</v>
+        <v>3.906081645236569</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.03299774090044139</v>
+        <v>1.753895819754149</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.571318260421926</v>
+        <v>0.1328349239199511</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-3.826448668592164</v>
+        <v>-0.7263993003149238</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-4.910872804077592</v>
+        <v>-0.8602081337619865</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-4.543148340413659</v>
+        <v>-1.933788153146267</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-3.379956073138921</v>
+        <v>-1.719914952504055</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-6.997457905549929</v>
+        <v>-5.410918171633504</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.019059631774148</v>
+        <v>-7.409906920739921</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-9.526083551158258</v>
+        <v>-8.45933051004566</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-9.25633106572969</v>
+        <v>-8.189458456015494</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-7.431858382428835</v>
+        <v>-7.298282823700099</v>
       </c>
     </row>
     <row r="21">
@@ -1852,243 +1852,243 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.382429265739383</v>
+        <v>-0.1994798388045425</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.578106490087428</v>
+        <v>3.132760623977568</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.816276405577732</v>
+        <v>3.277327873724168</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5555525164333019</v>
+        <v>1.525275687604946</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3597337214057603</v>
+        <v>2.769861200269432</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1703979149956254</v>
+        <v>5.057120311234954</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.605958248649621</v>
+        <v>3.771388225397921</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.330057711970412</v>
+        <v>2.969104747603865</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.407602637346479</v>
+        <v>3.535096067218163</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-6.411082913770016</v>
+        <v>0.66664578515595</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.908010443554033</v>
+        <v>0.940412778784335</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.743390991338771</v>
+        <v>1.193084316509804</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.629055358023436</v>
+        <v>-0.4490671964427548</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.852518324930841</v>
+        <v>-0.1431670265119607</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.390974613917372</v>
+        <v>-0.7972022266436198</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-3.919239292861441</v>
+        <v>-0.2060446596948751</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.374974961475779</v>
+        <v>-0.8667602750759613</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.361221448699247</v>
+        <v>-0.4445651981140628</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.82848033323485</v>
+        <v>-1.285813772587481</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.082363939659636</v>
+        <v>-0.5719381375252865</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.309192843726116</v>
+        <v>-1.642683635410137</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.704036710057757</v>
+        <v>-1.719812068037527</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.993305469681239</v>
+        <v>-1.447401866326622</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-4.1948332352911</v>
+        <v>-1.52440908866155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 4.238</t>
+          <t>X ≈ 4.239</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.908896593350015</v>
+        <v>-3.089778679679021</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.866823335984208</v>
+        <v>-2.41701407328852</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.360893905570322</v>
+        <v>-2.332638539507052</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2540638829187998</v>
+        <v>-1.524272212106276</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.080261918948842</v>
+        <v>-0.3390102310551555</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.861671603252368</v>
+        <v>2.373131921998947</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.856652201385671</v>
+        <v>2.623759840520378</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.639903345670611</v>
+        <v>2.346209846395773</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.62105501603034</v>
+        <v>1.374559363112027</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.915613805914155</v>
+        <v>1.115119019413982</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.189986760496801</v>
+        <v>2.401926938373954</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.565035557979698</v>
+        <v>1.117033328269464</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4937341625309344</v>
+        <v>0.5098420822110583</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.600725168464876</v>
+        <v>1.811618706108597</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.78542496762951</v>
+        <v>2.174766500642001</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-4.081914543977803</v>
+        <v>0.7354249968697388</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-6.106042297646994</v>
+        <v>-0.4135868675337235</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-6.687533032740511</v>
+        <v>-2.55268293313717</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-7.894581493440043</v>
+        <v>-3.865963494091297</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-6.293973968363467</v>
+        <v>-4.190945821607158</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-6.840310405761294</v>
+        <v>-6.263356336637109</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-7.394404933872217</v>
+        <v>-6.343417351902232</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-8.072742847012066</v>
+        <v>-7.093938568630143</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-7.680109341580263</v>
+        <v>-6.664242799923592</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 4.268</t>
+          <t>X ≈ 4.269</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.597302090131649</v>
+        <v>-3.389742780975958</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.037816679217777</v>
+        <v>-1.063364578070171</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.183753446064301</v>
+        <v>-1.72839702351974</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7650048098755988</v>
+        <v>-2.813649061966558</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.558106426575677</v>
+        <v>-2.762175475381731</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.315484908561928</v>
+        <v>-2.579910505072014</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.6943556616996815</v>
+        <v>-0.6686983203038466</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.305897196966676</v>
+        <v>-2.094181680596151</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.561036925135539</v>
+        <v>-2.056397590304499</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.7432931308668671</v>
+        <v>-2.057589066781368</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.114347944364823</v>
+        <v>-0.6385369264247842</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.845898877324778</v>
+        <v>-2.057909249068381</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.458865216879524</v>
+        <v>-2.022144077159858</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.967656019556877</v>
+        <v>-2.244787589977271</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5.477312690400069</v>
+        <v>-0.5957140208267617</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>4.343231082994016</v>
+        <v>-2.309056939036843</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.213309115395852</v>
+        <v>-2.058588729560931</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.109958860459543</v>
+        <v>-0.2414690716734782</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.460050936343997</v>
+        <v>-1.951301952530514</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.913208780630626</v>
+        <v>-1.766661973932862</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.9375279180759648</v>
+        <v>-2.309689893709944</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.729087612372282</v>
+        <v>-2.002799602897632</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.56799365089077</v>
+        <v>-1.732081944715368</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.361102280097249</v>
+        <v>-2.19650976076219</v>
       </c>
     </row>
     <row r="24">
@@ -2098,243 +2098,243 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.730941257398591</v>
+        <v>4.334090481112163</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.950727595734861</v>
+        <v>5.310831139167234</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.335954139992275</v>
+        <v>7.843482383507101</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.861560337625491</v>
+        <v>7.15098938244482</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.951515366993256</v>
+        <v>10.34867179363594</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7.17834183356873</v>
+        <v>12.29996921951185</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.465642954543704</v>
+        <v>11.98923159441095</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.97114390014162</v>
+        <v>8.195009129053034</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.380865102610464</v>
+        <v>6.03360384761217</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.801104877689902</v>
+        <v>5.716397144175403</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.843721322601695</v>
+        <v>7.315642255730189</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.579816922065987</v>
+        <v>6.614397671515391</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.517024851289889</v>
+        <v>8.164332114332929</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.477919128932264</v>
+        <v>6.177477782847419</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.518664778028779</v>
+        <v>7.302498561932516</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>6.527068677570277</v>
+        <v>8.344356517233578</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>8.455160798473401</v>
+        <v>9.5505003803367</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>8.355773957154476</v>
+        <v>9.896501581551533</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>6.5186761870171</v>
+        <v>11.00870561367277</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>7.121741840364898</v>
+        <v>11.20276332070605</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.58484684021095</v>
+        <v>11.56056256576822</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>6.924495349230334</v>
+        <v>12.38311672061921</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>6.375724054410306</v>
+        <v>9.987365990329437</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>4.649999153974264</v>
+        <v>9.917389853137514</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 4.331</t>
+          <t>X ≈ 4.332</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.505506681483972</v>
+        <v>-1.742609955928984</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-6.615777768684403</v>
+        <v>-3.131121896319527</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-8.583444009851817</v>
+        <v>-7.159171931006632</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-10.35208108451913</v>
+        <v>-8.377068436528496</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-10.71990888327958</v>
+        <v>-11.31650279205105</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-11.61899568385724</v>
+        <v>-12.19010039425131</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-10.77999131120227</v>
+        <v>-13.99884961644272</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-11.5967843468913</v>
+        <v>-12.19189509905831</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-11.56559359362422</v>
+        <v>-11.63788661857612</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-8.044774066835629</v>
+        <v>-9.797186887993654</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.099989653025531</v>
+        <v>-8.495354119175218</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.902710992550432</v>
+        <v>-8.237366141898022</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.868171765390102</v>
+        <v>-6.212278079343477</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.015715363479806</v>
+        <v>-4.338833635699501</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-6.832604687523109</v>
+        <v>-4.995354870951758</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-8.403677861830523</v>
+        <v>-5.983143099785337</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-5.843780649066709</v>
+        <v>-4.543601207394211</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-5.954134841897464</v>
+        <v>-4.652943840971403</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-4.119888960084111</v>
+        <v>-4.441650937534234</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-3.937262081728662</v>
+        <v>-4.786335697168411</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.771973995687141</v>
+        <v>-4.275673874304978</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.2241476509630687</v>
+        <v>-2.772607996384203</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-2.667618058707014</v>
+        <v>-1.974614410962189</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.117158589468062</v>
+        <v>-0.9953085595608897</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 4.361</t>
+          <t>X ≈ 4.363</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.112041054264004</v>
+        <v>1.301984206567163</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.965716612877792</v>
+        <v>-1.689680341434624</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.605643451621717</v>
+        <v>-6.63684862031532</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-6.037035349415802</v>
+        <v>-10.858502748137</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.886547099546107</v>
+        <v>-13.84372305499741</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.972356648168493</v>
+        <v>-15.45053370981262</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.503576444159201</v>
+        <v>-12.67544031589226</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.778694213389656</v>
+        <v>-14.73064476726305</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.507559867567203</v>
+        <v>-12.04422153764713</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.533710522156468</v>
+        <v>-9.269455710215006</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.280304764679848</v>
+        <v>-8.131667693594665</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2025994725606566</v>
+        <v>-4.834438531599254</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.834146140027407</v>
+        <v>-2.389857246916705</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.863714270964032</v>
+        <v>0.06100829497406579</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.714011876139146</v>
+        <v>0.3020598124007705</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.311155915862166</v>
+        <v>0.8955100198266308</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.930161049068765</v>
+        <v>1.656446971722723</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.333906073623517</v>
+        <v>2.447429139405699</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>7.061225316073937</v>
+        <v>3.560884691907283</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>7.254125282808921</v>
+        <v>3.750655727586206</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>9.740210492007371</v>
+        <v>5.908007933287571</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>11.1829210251593</v>
+        <v>8.532131487676729</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>11.46569841953487</v>
+        <v>7.01168226820333</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>11.39931044874011</v>
+        <v>6.04029847604604</v>
       </c>
     </row>
     <row r="27">
@@ -2344,243 +2344,243 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.005233160593988</v>
+        <v>2.162604922199307</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.671700000572514</v>
+        <v>2.449543193637844</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.785082418283885</v>
+        <v>2.948201006357984</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.368597114527617</v>
+        <v>6.720154497752368</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.024880932720578</v>
+        <v>10.22004982124211</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.856651504188115</v>
+        <v>12.31290217510728</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.106470189549562</v>
+        <v>14.11814498698156</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.114587531351923</v>
+        <v>15.78035854372142</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.195291917110261</v>
+        <v>12.0072250997964</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.779322908638633</v>
+        <v>9.974758502010033</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.069003964142901</v>
+        <v>8.320353916305216</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.760976059171455</v>
+        <v>11.91696388853347</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.627341652526539</v>
+        <v>11.45599959410966</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.095118284376262</v>
+        <v>9.961545737661808</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>11.72879643864631</v>
+        <v>11.8919489631533</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>12.33780997791532</v>
+        <v>11.85638857657743</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>10.8937828745736</v>
+        <v>11.7357162281581</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>10.80012644860991</v>
+        <v>11.64323152314229</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>11.68965516847428</v>
+        <v>13.16229311186886</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>11.22704022944895</v>
+        <v>13.36489059159382</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.69885129246264</v>
+        <v>14.13443333869224</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>9.967654720669593</v>
+        <v>12.77636595100596</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>10.91754174465694</v>
+        <v>12.41446517780545</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>9.520522569952234</v>
+        <v>12.35245478820253</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 4.424</t>
+          <t>X ≈ 4.425</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.252568243817535</v>
+        <v>-5.788299730368166</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-5.742103533859606</v>
+        <v>-8.199063045365591</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.09099135818465953</v>
+        <v>-3.467185687478924</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.608784483484804</v>
+        <v>0.4716708129808111</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.359968680586057</v>
+        <v>0.6628323316174018</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.124667950012089</v>
+        <v>0.8250536442727565</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.163924618567961</v>
+        <v>1.618223030215006</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.060595853861969</v>
+        <v>0.3263735861980237</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.538846758840151</v>
+        <v>1.926096805538883</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.321568921786223</v>
+        <v>2.203470371009622</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.626978102073892</v>
+        <v>1.418851871219971</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.4576034444584</v>
+        <v>4.2854278991868</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.086326204871057</v>
+        <v>3.18136157482305</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2724249313494767</v>
+        <v>4.00681848698008</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3.632618440066594</v>
+        <v>7.013204305648209</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.136340594904119</v>
+        <v>7.621516677482191</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.865438793672872</v>
+        <v>7.501338856473041</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.913727553054507</v>
+        <v>9.504846810496048</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>5.718610017357015</v>
+        <v>9.209848053301819</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>7.057637602226059</v>
+        <v>10.46615880644596</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>9.136128969413598</v>
+        <v>12.05217477540383</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>8.836580497332598</v>
+        <v>11.99438301502874</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.165327110880661</v>
+        <v>10.70199718578992</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.279143259607395</v>
+        <v>9.586702022449693</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 4.454</t>
+          <t>X ≈ 4.456</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>9.347917968549936</v>
+        <v>7.427641505726577</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.526774006125471</v>
+        <v>4.336683349221857</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.376275804638375</v>
+        <v>5.829991453553326</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.117053999785689</v>
+        <v>-1.000555153799496</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.223020804611764</v>
+        <v>-2.569550886641835</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.482539711492187</v>
+        <v>-0.9395745328437499</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.184788429548334</v>
+        <v>1.120600354699633</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.093340181439274</v>
+        <v>0.3465396296589276</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.137923498764053</v>
+        <v>4.108971381247251</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.267748539791441</v>
+        <v>5.375691104205998</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.556426030110181</v>
+        <v>3.002656018928803</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.145629068624032</v>
+        <v>1.463959300100377</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.233064654433228</v>
+        <v>-0.09200763117716804</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.451931565879086</v>
+        <v>0.1852176178422127</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.5083313152432183</v>
+        <v>-2.408148932290352</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.899162231442844</v>
+        <v>-3.799486421437614</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.6483451232558011</v>
+        <v>-3.478648362634985</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.235657757532536</v>
+        <v>-5.527083414788102</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-2.867948988214614</v>
+        <v>-6.472912460114721</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.001368451804396</v>
+        <v>-5.83600872896595</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.544732667437188</v>
+        <v>-5.129795762824386</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-4.372594743215835</v>
+        <v>-6.365554745952615</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-4.849624060150376</v>
+        <v>-6.440427093525486</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-6.429352116764612</v>
+        <v>-8.505955094597631</v>
       </c>
     </row>
     <row r="30">
@@ -2590,407 +2590,407 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.541978327183052</v>
+        <v>4.182282138268675</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.07277334901142</v>
+        <v>7.929137992980124</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.152417361790988</v>
+        <v>3.089758399731444</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.45475417332991</v>
+        <v>6.458437033349931</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.857430629007553</v>
+        <v>4.081830234272019</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.308464871951458</v>
+        <v>1.547707984995249</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.062151625788999</v>
+        <v>1.456031409948501</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.519507008109734</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2082561197296187</v>
+        <v>-4.903141832481793</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1917661908923733</v>
+        <v>-4.995785399674745</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.806526806526769</v>
+        <v>-7.442814192886892</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.843282725241409</v>
+        <v>-7.041291487491385</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.9378036929057245</v>
+        <v>-6.123637227816936</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.916805853813699</v>
+        <v>-7.024988213107015</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-4.848661645627814</v>
+        <v>-9.723947837218191</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.738281560866952</v>
+        <v>-9.129560915275199</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-4.387570981266208</v>
+        <v>-9.263478052252673</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-8.280468922804673</v>
+        <v>-12.76967930029152</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-6.549136222033447</v>
+        <v>-11.87351581052368</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-6.362042865110283</v>
+        <v>-12.36694210939917</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-5.39025556559158</v>
+        <v>-12.22921616852172</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-5.466237942122191</v>
+        <v>-12.30506212993079</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-5.948963317384376</v>
+        <v>-12.03058741744874</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-2.994628945199274</v>
+        <v>-10.74587545298495</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 4.517</t>
+          <t>X ≈ 4.518</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7862240413083512</v>
+        <v>5.089311616726768</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.132516422839061</v>
+        <v>7.929137992980124</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.045443867854004</v>
+        <v>12.84032529315544</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.28128331879423</v>
+        <v>16.8892760356175</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.57276423353785</v>
+        <v>24.48999349957812</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.546415370855328</v>
+        <v>19.91505492377082</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.826904597451488</v>
+        <v>17.55580465257881</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.59097525473071</v>
+        <v>20.45219638242899</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.965831877305412</v>
+        <v>18.90638197704206</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11.19176619089234</v>
+        <v>19.72076788830717</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>11.46620046620048</v>
+        <v>21.58212911777071</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.853686971728393</v>
+        <v>18.12877653971945</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.72886297376094</v>
+        <v>23.35482082206972</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.840769903762073</v>
+        <v>21.54644035832155</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>10.51497471800856</v>
+        <v>24.06290023534417</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>7.110203287617928</v>
+        <v>23.0699855699856</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.976065382370081</v>
+        <v>21.34876684570651</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>9.537712895377048</v>
+        <v>24.41852931648846</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>8.420560747663551</v>
+        <v>23.04711911011123</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.940987437919922</v>
+        <v>20.05936174547604</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>6.730956555620487</v>
+        <v>19.51681557751001</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.654974179089926</v>
+        <v>19.44096961610091</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>4.263157894736871</v>
+        <v>13.36623797937666</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>6.853855903285634</v>
+        <v>22.81421524996291</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 4.547</t>
+          <t>X ≈ 4.549</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.683650911325259</v>
+        <v>-9.593228065812923</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-11.49625710248628</v>
+        <v>-8.737528673686541</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-11.78695535952954</v>
+        <v>-11.36602391319369</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-9.052685056134337</v>
+        <v>-12.07897793263647</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-11.7169164109045</v>
+        <v>-15.98619697661231</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-10.38027683859557</v>
+        <v>-12.22780221908636</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-11.15337267338394</v>
+        <v>-11.80927471250049</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-10.28258796366009</v>
+        <v>-10.89700996677744</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-9.091639387062472</v>
+        <v>-9.665046594386517</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-9.865705073475468</v>
+        <v>-10.43796227042301</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.74069608552367</v>
+        <v>-11.35437881873728</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.571600384593481</v>
+        <v>-6.871223460280483</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-7.546999095204562</v>
+        <v>-6.803909336660425</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-8.91785078589313</v>
+        <v>-8.215464403583212</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-7.278128730267305</v>
+        <v>-6.492655320211369</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-3.23462429858894</v>
+        <v>-4.707792207792245</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-5.66761277854939</v>
+        <v>-6.032185535245873</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-4.623206644852729</v>
+        <v>-6.137026239067055</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-4.407025459232969</v>
+        <v>-5.921134858142729</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.36935738966627</v>
+        <v>-6.924765238650885</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-3.613871030586402</v>
+        <v>-5.0863590256645</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-3.689853407116964</v>
+        <v>-5.162204987073622</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-3.415003024803426</v>
+        <v>-3.697254084115393</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-2.341546395565054</v>
+        <v>-4.963562527814901</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 4.578</t>
+          <t>X ≈ 4.579</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.339337594421814</v>
+        <v>2.41975894717411</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.832150122472704</v>
+        <v>0.5698306336727796</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.534883720930239</v>
+        <v>-2.383339930509742</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.678021019399324</v>
+        <v>-3.096293949952482</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.741211667913241</v>
+        <v>-0.4017813921967317</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.642711667151595</v>
+        <v>-4.760269751553871</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.726758689506084</v>
+        <v>-5.532218435444243</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.733832397587868</v>
+        <v>-1.264975334742779</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>16.91821282968633</v>
+        <v>3.3219663926265</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.85843285755898</v>
+        <v>1.033899201438473</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.7042957042957</v>
+        <v>1.307958843600375</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>17.56797268601406</v>
+        <v>5.574663985606961</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.0145772594752</v>
+        <v>2.936350403599313</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>19.07886514185727</v>
+        <v>5.745574557455754</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>14.13402233705618</v>
+        <v>3.572279744723666</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>11.87210804952269</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>13.16654157284631</v>
+        <v>5.547901044840714</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>11.63295099061522</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>11.84913217623498</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>14.89336839030091</v>
+        <v>8.876100562214901</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>12.92143274609666</v>
+        <v>8.333554394248871</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>11.41687894099467</v>
+        <v>5.227405402536753</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>8.834586466165398</v>
+        <v>3.986728599867284</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.330046379476016</v>
+        <v>2.3957448314925</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 4.608</t>
+          <t>X ≈ 4.611</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.725302506702576</v>
+        <v>3.502010029425151</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.902185717126294</v>
+        <v>-5.404195340353233</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-9.851081191350481</v>
+        <v>-12.5565001036699</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-17.58263060967336</v>
+        <v>-16.12659698025551</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.93046753008176</v>
+        <v>-10.74810173851707</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.988867280216844</v>
+        <v>-9.132564123848283</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-9.761963115005216</v>
+        <v>-9.904512807738627</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.28621772772545</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-9.999080403396384</v>
+        <v>-5.855522784862721</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-10.77314608980943</v>
+        <v>-8.057009889470621</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-12.25309777941357</v>
+        <v>-10.64009310445157</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-14.28666390546464</v>
+        <v>-10.91884250789956</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-20.67464579816889</v>
+        <v>-16.32771886046994</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-22.65045816641341</v>
+        <v>-17.97736916548797</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-23.30958668550022</v>
+        <v>-21.49265532021138</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-20.95997215097857</v>
+        <v>-19.46969696969697</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-19.3397240913141</v>
+        <v>-19.60361410667444</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-17.69035728006148</v>
+        <v>-19.70845481049562</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-19.228562059354</v>
+        <v>-20.92113485814271</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-17.28708273751862</v>
+        <v>-17.87714619103184</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-19.5848329180637</v>
+        <v>-19.84826378756929</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-21.41520125950653</v>
+        <v>-19.92410974897838</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-21.14035087719296</v>
+        <v>-21.07820646506777</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-19.46193357039864</v>
+        <v>-19.72546728971962</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3347</v>
+        <v>3354</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09983154504402592</v>
+        <v>-0.0725912650458298</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.270169344940264</v>
+        <v>-0.2730172767106893</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3285367066232183</v>
+        <v>-0.3025318497016585</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.4618661204878123</v>
+        <v>-0.4360219950747179</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4838965571949956</v>
+        <v>-0.4884769873417696</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4583284517191402</v>
+        <v>-0.4628471267291303</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3824650237604459</v>
+        <v>-0.3579602798749022</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.4063485632889154</v>
+        <v>-0.411634807811744</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.5263354833926286</v>
+        <v>-0.5313485915878857</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.5396629472609931</v>
+        <v>-0.5451334049100538</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.5457042957042972</v>
+        <v>-0.521292985651435</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.4505702476821867</v>
+        <v>-0.4859420749991159</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6052644830585976</v>
+        <v>-0.6113104546113206</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.6006956905185703</v>
+        <v>-0.5771653265207561</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.5569362871563257</v>
+        <v>-0.5933732166473931</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.5400699364257804</v>
+        <v>-0.5761812052710269</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.5969817255607168</v>
+        <v>-0.6330696258651614</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.6247286992147849</v>
+        <v>-0.631073858114668</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.6593915196395486</v>
+        <v>-0.6655315748526291</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.72329188168613</v>
+        <v>-0.7291839686205392</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.7118295140312512</v>
+        <v>-0.7180880354096359</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.7104085222139389</v>
+        <v>-0.7167199992763784</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.7464000503049775</v>
+        <v>-0.7524666311312203</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.8047438377760869</v>
+        <v>-0.8107386075490766</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3310</v>
+        <v>3312</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.07471113177558664</v>
+        <v>0.1222713273476472</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2734921344300503</v>
+        <v>-0.2263737618117716</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3165122562537945</v>
+        <v>-0.2681284093576295</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.4433861020077927</v>
+        <v>-0.3943040630886401</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4015167361549175</v>
+        <v>-0.3531109592573074</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3476729482330256</v>
+        <v>-0.2994452907294303</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2923919824850003</v>
+        <v>-0.2435249520977152</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2833482569950831</v>
+        <v>-0.2342352415026809</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.4050954409903653</v>
+        <v>-0.385987811270013</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4400027621762703</v>
+        <v>-0.4202089273539684</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3889505018003376</v>
+        <v>-0.3694164127222379</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3197025526545474</v>
+        <v>-0.2999667987711376</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4334375381330702</v>
+        <v>-0.4126679168303866</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.4262983693303326</v>
+        <v>-0.4053385470997384</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.4047802282603996</v>
+        <v>-0.3832648612274383</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4244561457756717</v>
+        <v>-0.4034319094560033</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.5106193729308615</v>
+        <v>-0.4894230852824606</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.5977917286679073</v>
+        <v>-0.5764475772225666</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.6654121030151785</v>
+        <v>-0.6442064805209498</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.7321165652987105</v>
+        <v>-0.7110252191207636</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.7144604883477115</v>
+        <v>-0.692909338097202</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.7121755793641711</v>
+        <v>-0.6905551322010979</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.8120459711647001</v>
+        <v>-0.7905948916125567</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.8702125760699317</v>
+        <v>-0.848655695516733</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3272</v>
+        <v>3277</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1481388083823916</v>
+        <v>0.147031674446815</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07842321433013666</v>
+        <v>-0.08050417852927438</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1659969350066035</v>
+        <v>-0.1680395648151958</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3164243893838758</v>
+        <v>-0.3486169984538705</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2394281723437501</v>
+        <v>-0.2427272586280296</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2174707036690791</v>
+        <v>-0.2814910694368109</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1829837419754838</v>
+        <v>-0.247127084779116</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1401682975807219</v>
+        <v>-0.2044152854186763</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2941823200376987</v>
+        <v>-0.3582132899833397</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3205081040965112</v>
+        <v>-0.3541840006830199</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3024448914859903</v>
+        <v>-0.3361417366703918</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2595895203544814</v>
+        <v>-0.2933810128728425</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4529828989164884</v>
+        <v>-0.5169785059339844</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3213263789923815</v>
+        <v>-0.4159801438008088</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2614145941930062</v>
+        <v>-0.3258002641293132</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2881706961219024</v>
+        <v>-0.3524975785249751</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3737363864618359</v>
+        <v>-0.4075117924235343</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.5216729089751269</v>
+        <v>-0.5552412862799727</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.5315295788546024</v>
+        <v>-0.5650801876456413</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.5400870431545215</v>
+        <v>-0.6041022584328957</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.5463971339469325</v>
+        <v>-0.6104589095205171</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.4820651204417246</v>
+        <v>-0.5462506455932257</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.555662759097558</v>
+        <v>-0.6197387582779186</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.5524195653371038</v>
+        <v>-0.6165261850507235</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3232</v>
+        <v>3228</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.07205648843105905</v>
+        <v>0.03494495054834346</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.06064116736836667</v>
+        <v>-0.09870083485870396</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.03935544291852011</v>
+        <v>-0.1043170143677088</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1520615671408265</v>
+        <v>-0.2460551083343248</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.008052294823500006</v>
+        <v>-0.1334684506469443</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.08036525592532939</v>
+        <v>-0.1139918150726231</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.03589355514063186</v>
+        <v>-0.06740076723674093</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1032905256666794</v>
+        <v>0.07269234077940467</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05305735377972809</v>
+        <v>-0.08397087085010213</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.008480266285737059</v>
+        <v>-0.03726898879202167</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1297854687685174</v>
+        <v>0.1004190831448639</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1767449248726152</v>
+        <v>0.1481768924531863</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.03586104720729821</v>
+        <v>-0.06167554904225625</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1002804939327149</v>
+        <v>0.10610387783683</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.2000513404501802</v>
+        <v>0.2077727657588682</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1348946456426248</v>
+        <v>0.2027381353710211</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.01918568699088752</v>
+        <v>0.08726688250639825</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.06739313715324613</v>
+        <v>-0.03003798922166112</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1107954463432463</v>
+        <v>-0.07406667732880123</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1525436704442811</v>
+        <v>-0.1163611839597039</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1211815175376714</v>
+        <v>-0.1144352515123614</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.05498253086678062</v>
+        <v>-0.01698900594434605</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1018281863024342</v>
+        <v>-0.095593537580271</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.03558304060883444</v>
+        <v>-0.0290608461012809</v>
       </c>
     </row>
     <row r="10">
@@ -3512,79 +3512,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3196</v>
+        <v>3200</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.08273616540662942</v>
+        <v>0.0979056014299573</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.01478352387552917</v>
+        <v>0.0281004830040672</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.009723055569608618</v>
+        <v>0.003929221739227273</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2400671113753745</v>
+        <v>-0.2259758622430965</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.09038131142469297</v>
+        <v>-0.07841727572915858</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.04117134467168881</v>
+        <v>-0.02930566695400927</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.04359653575568245</v>
+        <v>0.05552094153976839</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1252218300731798</v>
+        <v>0.1371051718153424</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.03333764413135043</v>
+        <v>-0.02126373131903847</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.05157927500447812</v>
+        <v>0.06371195247088224</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2194984821971389</v>
+        <v>0.2313665905375473</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2701458245961774</v>
+        <v>0.2820114326804202</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0678090292645237</v>
+        <v>0.08016475389138833</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1768065018073699</v>
+        <v>0.1890749822645859</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3163267720907186</v>
+        <v>0.3285617923737547</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.3374192676429004</v>
+        <v>0.3495050253155014</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3156428618164711</v>
+        <v>0.3277859556891372</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.2293639468033177</v>
+        <v>0.2416387640520981</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1831349432274365</v>
+        <v>0.1954240899294888</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1389041045866222</v>
+        <v>0.1512112193480348</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.1768250561936</v>
+        <v>0.1892010891088134</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.2759873122981986</v>
+        <v>0.2882575214775684</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.1943433811303308</v>
+        <v>0.2066598713449537</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.2622831039530666</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="11">
@@ -3594,817 +3594,817 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3164</v>
+        <v>3172</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1203228470104918</v>
+        <v>0.1306708834381425</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02397148378559422</v>
+        <v>0.03189017713494025</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.04910372020007259</v>
+        <v>-0.04251862633109482</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2117851543264422</v>
+        <v>-0.2055443486765611</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1197460987938257</v>
+        <v>-0.08507626508733779</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1347867615096305</v>
+        <v>-0.09987267736371308</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.04141843359089137</v>
+        <v>-0.03890334664468043</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.04380544340996551</v>
+        <v>0.04581132736133497</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.08533725344853593</v>
+        <v>-0.082964624478997</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.008212593241808008</v>
+        <v>-0.02185609160495972</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2065215238019817</v>
+        <v>0.1448362519063764</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2919741253807402</v>
+        <v>0.2297576356754618</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.03594958793416936</v>
+        <v>0.004582203216600078</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1797743146000883</v>
+        <v>0.1792259678513517</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.327349967509555</v>
+        <v>0.325730632094718</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.3741797483157043</v>
+        <v>0.373070325900521</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.3535488260787218</v>
+        <v>0.352346887348844</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.2674710446936359</v>
+        <v>0.2663721246837341</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.2501599903268499</v>
+        <v>0.2493314398023259</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.2351793571118677</v>
+        <v>0.2345846473992523</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.2474285059415138</v>
+        <v>0.2462244014070762</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.3483833178559905</v>
+        <v>0.3468417318029537</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.3263490479753912</v>
+        <v>0.3251522310737656</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.4273915122194012</v>
+        <v>0.4258567960306863</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 3.913</t>
+          <t>X &gt; 3.914</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1173963993538791</v>
+        <v>0.1324399089867256</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.008547446877614107</v>
+        <v>0.004161306158842137</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1345246941283023</v>
+        <v>-0.1213838770844902</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2614003187561877</v>
+        <v>-0.2479623405589209</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1975573819669307</v>
+        <v>-0.18669981448474</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1508285481745659</v>
+        <v>-0.1400638979514497</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.05087830764312429</v>
+        <v>-0.07172933053881536</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.03710960200574931</v>
+        <v>0.01619075654989643</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.125029189783902</v>
+        <v>-0.1457592973214332</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.02488990718418904</v>
+        <v>-0.04561026945795277</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1728290738756968</v>
+        <v>0.1517979313419247</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2293214894948434</v>
+        <v>0.2082623264296188</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.08357752131998808</v>
+        <v>-0.1040376288647948</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.06299212598425186</v>
+        <v>0.04237900010674167</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.2166789627423356</v>
+        <v>0.1959858831776771</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.2592926565294178</v>
+        <v>0.2384248577141932</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2394908669586187</v>
+        <v>0.2186645350266048</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1535213293673792</v>
+        <v>0.1328150307742177</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.1343922262009087</v>
+        <v>0.1136607685868469</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.117832221634977</v>
+        <v>0.09707780606381533</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1342867072802747</v>
+        <v>0.1136046585698764</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.236557035020347</v>
+        <v>0.2157503908817304</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.212218703396502</v>
+        <v>0.1913824515799618</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.3145777716507396</v>
+        <v>0.2936166797460231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 3.944</t>
+          <t>X &gt; 3.945</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3123</v>
+        <v>3130</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1219186497301834</v>
+        <v>0.05404663855027536</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.002735183000829977</v>
+        <v>-0.07333964782239377</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2170246760163295</v>
+        <v>-0.256549974459233</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.340750854606398</v>
+        <v>-0.4123112659697981</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.3064376910028344</v>
+        <v>-0.3810918033902766</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2286668747140581</v>
+        <v>-0.3033755233763031</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1877090084011144</v>
+        <v>-0.2631309928582297</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.09777912564519653</v>
+        <v>-0.1736424252280457</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2929316663530059</v>
+        <v>-0.3047619399842105</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.1881084239201272</v>
+        <v>-0.2325824085545918</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.04103039817325538</v>
+        <v>-0.03557512799593354</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.03550515354653072</v>
+        <v>0.02232326458385359</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.304959617177154</v>
+        <v>-0.2864217303476053</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1564638445090551</v>
+        <v>-0.1384246704925189</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.0654217167314215</v>
+        <v>0.01874503476972222</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1049866369206143</v>
+        <v>0.05866504432470521</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.08575654317948533</v>
+        <v>0.03935688471860743</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.0001586290715778205</v>
+        <v>-0.04646501457725805</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.02061572292468838</v>
+        <v>-0.0667261089971376</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.03833246400947132</v>
+        <v>-0.08427537327270329</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.01888349556312363</v>
+        <v>-0.06530815399126055</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.05230751242326193</v>
+        <v>0.03757607477638203</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.005728148797096821</v>
+        <v>0.01181497947299448</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.09753185589522673</v>
+        <v>0.1147883013346913</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 3.975</t>
+          <t>X &gt; 3.976</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3088</v>
+        <v>3102</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1162581987291489</v>
+        <v>0.08715288656802755</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1229172331755137</v>
+        <v>0.08967698450503292</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2061905794879024</v>
+        <v>-0.1782923364131577</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3876160462377385</v>
+        <v>-0.4251235657776178</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3166300719368706</v>
+        <v>-0.3585745723157601</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2400958022624522</v>
+        <v>-0.2818315231156632</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2221716072503099</v>
+        <v>-0.2984119512369858</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1603134050630999</v>
+        <v>-0.2056327102943101</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2937019072042375</v>
+        <v>-0.3703951438159123</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2111996376054179</v>
+        <v>-0.2906427521150405</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.04966816479231539</v>
+        <v>-0.03014125854465277</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.07949342334125475</v>
+        <v>0.03078589837625145</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3166355741577433</v>
+        <v>-0.3027544256115249</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1962432229864035</v>
+        <v>-0.1193082033139063</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.00329675008260466</v>
+        <v>0.01306172070333389</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.02803960643890946</v>
+        <v>-0.01632076390919224</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.0783234167682707</v>
+        <v>-0.09895022761364913</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2610373739613792</v>
+        <v>-0.2811703832111903</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.316587651948474</v>
+        <v>-0.3358205908200915</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.4014015228389951</v>
+        <v>-0.419690575173135</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4080491598976721</v>
+        <v>-0.4279739324968403</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.335317083045986</v>
+        <v>-0.323594285060878</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3972500042595968</v>
+        <v>-0.3521809597963852</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.292085374780072</v>
+        <v>-0.2154737371728785</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 4.006</t>
+          <t>X &gt; 4.007</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3011</v>
+        <v>3018</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.06804539832700129</v>
+        <v>-0.20447749817383</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2168819532655988</v>
+        <v>-0.2256239117817813</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4519236669325579</v>
+        <v>-0.5600727074399572</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.8178549291325155</v>
+        <v>-0.7941414173852053</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6369118587251421</v>
+        <v>-0.6507312130925484</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5632969165394073</v>
+        <v>-0.5441959702627202</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.55838945165263</v>
+        <v>-0.5729053706946061</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4549447981268955</v>
+        <v>-0.4699452714200234</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6259284223200865</v>
+        <v>-0.6405070060487077</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6209059854162149</v>
+        <v>-0.63616556229384</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3274503274503289</v>
+        <v>-0.3431613987438666</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1906398559262925</v>
+        <v>-0.2069141722088403</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.5352005603224441</v>
+        <v>-0.5846636324361896</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4061681962048596</v>
+        <v>-0.489163843729159</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1848045314395748</v>
+        <v>-0.268907148990472</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.2653073671242581</v>
+        <v>-0.3487452182098494</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.2472613240579733</v>
+        <v>-0.3308868339471616</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.4651597153841251</v>
+        <v>-0.5484019004427196</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.5940281117528983</v>
+        <v>-0.6768174818372543</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.6858782337218372</v>
+        <v>-0.768325164275673</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.7120870188099389</v>
+        <v>-0.7949701761823391</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.635655315323163</v>
+        <v>-0.7519243185148241</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.7394981477598321</v>
+        <v>-0.8553322872416231</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7294497537497548</v>
+        <v>-0.84541427447774</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 4.037</t>
+          <t>X &gt; 4.038</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2920</v>
+        <v>2931</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.07588496758970109</v>
+        <v>-0.1201971472843724</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.3540206068659302</v>
+        <v>-0.3352581820154441</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7218316819939403</v>
+        <v>-0.8065968903520684</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.281162654070059</v>
+        <v>-1.263838593268048</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.083461447334912</v>
+        <v>-1.242048469751943</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.013517059873593</v>
+        <v>-1.138086576980079</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.086802281358267</v>
+        <v>-1.212905907176498</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.00575499050089</v>
+        <v>-1.132843017337294</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.217586634903604</v>
+        <v>-1.377780567812941</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.188601907267177</v>
+        <v>-1.350728055854319</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8265600747701001</v>
+        <v>-0.9894719864391277</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6087959750656466</v>
+        <v>-0.7732185090645416</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9633922292414496</v>
+        <v>-1.095126843377599</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.9260105285474012</v>
+        <v>-1.058439744008396</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6774686642607008</v>
+        <v>-0.8463968168100351</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.7449879692126657</v>
+        <v>-0.878339365069543</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.7907037783177344</v>
+        <v>-0.8902036233524484</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.012298496739525</v>
+        <v>-1.145295123740432</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.083712756609955</v>
+        <v>-1.18193672657403</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.218611285290258</v>
+        <v>-1.350010634935472</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.29732489038247</v>
+        <v>-1.395639384024648</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.319016238432305</v>
+        <v>-1.383366482698143</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.469125569830091</v>
+        <v>-1.600521803208487</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.388153229134538</v>
+        <v>-1.520076638064907</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 4.068</t>
+          <t>X &gt; 4.069</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>-0.1047792209284282</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2767607686163984</v>
+        <v>-0.3498722315553948</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.7427957979944182</v>
+        <v>-0.8135014179960649</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.189737548996185</v>
+        <v>-1.153145652821884</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.8984849186860018</v>
+        <v>-0.9383081326894711</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8332090127350966</v>
+        <v>-0.944213331884292</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8427469023162075</v>
+        <v>-0.9524018428707421</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8179545822643206</v>
+        <v>-0.891692703395627</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.181751721891125</v>
+        <v>-1.291186412015698</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.474900475774341</v>
+        <v>-1.583082965029334</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.14489093737054</v>
+        <v>-1.253496734178817</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.9071363071928715</v>
+        <v>-1.015196278374731</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.337164715269942</v>
+        <v>-1.407873081249178</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.538017975025838</v>
+        <v>-1.60842727256739</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.181887330540881</v>
+        <v>-1.286543024546859</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.311971552467348</v>
+        <v>-1.417795085587478</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.212108571889864</v>
+        <v>-1.317696610230627</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.367455430843833</v>
+        <v>-1.472951430915401</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.450659458668717</v>
+        <v>-1.521033180460975</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.491990023527258</v>
+        <v>-1.598348449079957</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.623143361313176</v>
+        <v>-1.728605667911175</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.500296476180722</v>
+        <v>-1.605620258419094</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.738979618622615</v>
+        <v>-1.809292912476387</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.544813614414608</v>
+        <v>-1.650600979559201</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 4.099</t>
+          <t>X &gt; 4.1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2663</v>
+        <v>2672</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1982647883033906</v>
+        <v>-0.1714593583299262</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.579927557761394</v>
+        <v>-0.6348666734744342</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.180466502616717</v>
+        <v>-1.199012437233115</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.426978714374165</v>
+        <v>-1.557503369557153</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.138089493267124</v>
+        <v>-1.241280057782348</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.079406945306452</v>
+        <v>-1.182484463731427</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.122921481069618</v>
+        <v>-1.190173966958717</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.380655950943044</v>
+        <v>-1.373200442967878</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.803647833921907</v>
+        <v>-1.869133290471723</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.03398402701329</v>
+        <v>-2.100196784481788</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.738582792394453</v>
+        <v>-1.84254056388226</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.43603265443987</v>
+        <v>-1.5788382498625</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.754308305221862</v>
+        <v>-1.898242261779792</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.99162815085824</v>
+        <v>-2.172532689510561</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.731033266023381</v>
+        <v>-1.951439356018923</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.787837396270739</v>
+        <v>-1.969696969696976</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.563260460326504</v>
+        <v>-1.746204625524761</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.646500917536578</v>
+        <v>-1.792099321324599</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.670893525200022</v>
+        <v>-1.853415129235103</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.649563743182405</v>
+        <v>-1.869245272817025</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.68364709529223</v>
+        <v>-1.866955376354355</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.700247834668666</v>
+        <v>-1.846323660721112</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.004109372530429</v>
+        <v>-2.148699757783291</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.945743545957143</v>
+        <v>-2.053311601096873</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 4.13</t>
+          <t>X &gt; 4.131</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2522</v>
+        <v>2539</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.0260848024347311</v>
+        <v>-0.08893454512595156</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5265650617141802</v>
+        <v>-0.4418480429805314</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9625602428920246</v>
+        <v>-0.9214554608127727</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.45842946952952</v>
+        <v>-1.300493033401267</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.211956376163904</v>
+        <v>-1.145733817149932</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9242174667066791</v>
+        <v>-0.9371342115626646</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.084696889180705</v>
+        <v>-1.178825349656798</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.223051538019476</v>
+        <v>-1.435170436444722</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.553547967655867</v>
+        <v>-1.802496719307278</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.595825817519867</v>
+        <v>-1.809457989744807</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.22019006634391</v>
+        <v>-1.434987864863558</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8061393897554723</v>
+        <v>-0.9860430455038482</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8029175236729316</v>
+        <v>-0.9887832862402703</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9222632715934154</v>
+        <v>-1.030106933800475</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.6100088194601696</v>
+        <v>-0.8019174866164107</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.702708438337261</v>
+        <v>-0.8124531534425543</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.5763268675310229</v>
+        <v>-0.6483902260774244</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.6184052480827873</v>
+        <v>-0.6514803507706688</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.7745322479834584</v>
+        <v>-0.7661483352316765</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.7621004480657945</v>
+        <v>-0.7135036990370125</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.8069972397590419</v>
+        <v>-0.7609309787573508</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.8199333750569124</v>
+        <v>-0.7741687808556179</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.235058514300015</v>
+        <v>-1.263808264842801</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.168877377179676</v>
+        <v>-1.159102579203676</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 4.161</t>
+          <t>X &gt; 4.162</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2213910522071671</v>
+        <v>0.1791868424254162</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2194894385047164</v>
+        <v>0.2918920117850945</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3908063003011932</v>
+        <v>-0.3584178121296802</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4017216678199986</v>
+        <v>-0.41048988293295</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.0215832300527552</v>
+        <v>0.08523159481625697</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3603987419815269</v>
+        <v>0.4238556367399298</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5471998391688331</v>
+        <v>0.5270981345106165</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3356561057945484</v>
+        <v>0.3585395071628668</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.06119160484900732</v>
+        <v>0.08387852932566631</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.04957395675105403</v>
+        <v>0.01712730695034281</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2922194975880501</v>
+        <v>0.3585672292471429</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.8050936213447173</v>
+        <v>0.8295583449789206</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.643575127279064</v>
+        <v>0.8407355520117648</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4050474919304108</v>
+        <v>0.6452757951851567</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.5397293061434283</v>
+        <v>0.781347363697364</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.34959981480268</v>
+        <v>0.7182568961723135</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.4973525815727342</v>
+        <v>0.8237363206759838</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.5462599039241312</v>
+        <v>0.7874836247331132</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.4462127356926189</v>
+        <v>0.6870772889915813</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.4023504262290487</v>
+        <v>0.6001445969136299</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.3980511213029985</v>
+        <v>0.5113252535265929</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.4763212110534099</v>
+        <v>0.5469823281093937</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.07945452496337424</v>
+        <v>0.03331269272387516</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.04151657166602263</v>
+        <v>0.1545155649738987</v>
       </c>
     </row>
     <row r="21">
@@ -4414,79 +4414,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2750618608401112</v>
+        <v>-0.01294013668778149</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2620529316858651</v>
+        <v>0.09603732600323411</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2203610343145286</v>
+        <v>-0.3391550650958237</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1156890019226395</v>
+        <v>-0.4209612094124822</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1517176341821482</v>
+        <v>0.01477936919162204</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5988274467967756</v>
+        <v>0.4145554232712882</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8331842583323876</v>
+        <v>0.6018837807475279</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4414425444503465</v>
+        <v>0.2105828603674453</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1360048553324944</v>
+        <v>-0.001181048168028553</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1434380498310901</v>
+        <v>-0.2335629020815517</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.06454705799582428</v>
+        <v>-0.07266987347691867</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4679191814661792</v>
+        <v>0.4703246596687407</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6351861587726546</v>
+        <v>0.5438567108249757</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4418320718345115</v>
+        <v>0.5379059197450005</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.7484486983179721</v>
+        <v>0.8441558087345769</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.7624859642908604</v>
+        <v>0.8581718827620506</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.032064131001434</v>
+        <v>0.9868263806732642</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.049449984578999</v>
+        <v>1.051038860390456</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.8245062619895265</v>
+        <v>0.9201945441622925</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.133969894060307</v>
+        <v>1.182316167351203</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.230251337002727</v>
+        <v>1.278496775810979</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.465259535000882</v>
+        <v>1.419243938198683</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.8278637770897816</v>
+        <v>0.829688271774323</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.7804095756019507</v>
+        <v>0.8763192641120554</v>
       </c>
     </row>
     <row r="22">
@@ -4496,1145 +4496,1145 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1946</v>
+        <v>1938</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1737713171237303</v>
+        <v>0.005251815685838324</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1416739319965146</v>
+        <v>-0.2001137077001474</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4066516120641737</v>
+        <v>-0.6918461256928126</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1770872497476006</v>
+        <v>-0.6107644981308979</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1984999267282106</v>
+        <v>-0.2539050818268009</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6691882455629852</v>
+        <v>-0.03820245279947443</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.147761527727454</v>
+        <v>0.2927835020896694</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6949507898989111</v>
+        <v>-0.05843707600390502</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4601375036864752</v>
+        <v>-0.3460501786159043</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4298614289875715</v>
+        <v>-0.3213541517657035</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4279156269967856</v>
+        <v>-0.1714689556633928</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9445960626374443</v>
+        <v>0.3998388107817732</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.025234971716998</v>
+        <v>0.6406898472922649</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8346349344368846</v>
+        <v>0.6043263463923481</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.127080429858509</v>
+        <v>1.004226329212635</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.190721881954339</v>
+        <v>0.9619577065620248</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.343704911299973</v>
+        <v>1.167594119546642</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.269953332535586</v>
+        <v>1.196894983743057</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.158643782004908</v>
+        <v>1.135331578148723</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.42816692509944</v>
+        <v>1.353396695535757</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.736942531334542</v>
+        <v>1.563379695171548</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.846623734189187</v>
+        <v>1.725374787104073</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.177384910658773</v>
+        <v>1.05175743384919</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.235493450390734</v>
+        <v>1.110446022973875</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 4.253</t>
+          <t>X &gt; 4.254</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1735</v>
+        <v>1742</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.5486663771294715</v>
+        <v>0.3534871641884294</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.3859349830304808</v>
+        <v>0.04931939887580938</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1689887164273998</v>
+        <v>-0.5072334316012004</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.167725826347521</v>
+        <v>-0.5079817702668592</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3540150560872064</v>
+        <v>-0.2443295311673523</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4025519409679106</v>
+        <v>-0.3095121757963142</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5750952844180119</v>
+        <v>0.03051521142811708</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2151899891681737</v>
+        <v>-0.3289943646321092</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1675014560279635</v>
+        <v>-0.5396434450789798</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.005945722052992153</v>
+        <v>-0.4829779988100285</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.02960426301387287</v>
+        <v>-0.4610129253713779</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.869142037555477</v>
+        <v>0.3191441348761472</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.209962630118326</v>
+        <v>0.6554120987020795</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.25242224378114</v>
+        <v>0.4684886296848916</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.602895207305188</v>
+        <v>0.8725237611298908</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.831947406952416</v>
+        <v>0.9874458874458867</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.249697223166137</v>
+        <v>1.345499672628016</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.237693749292504</v>
+        <v>1.61877631078584</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.259641207433667</v>
+        <v>1.698049048963334</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.367286076984556</v>
+        <v>1.977214797349767</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.780055136364645</v>
+        <v>2.443999822745887</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.970460650016825</v>
+        <v>2.633229700562879</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.302328401649284</v>
+        <v>1.968265135620683</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.319754078117455</v>
+        <v>1.985210092599544</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 4.284</t>
+          <t>X &gt; 4.285</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1505</v>
+        <v>1483</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.182269531594628</v>
+        <v>1.007227255757932</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1334879464038536</v>
+        <v>0.2436451912082518</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.681367917339756</v>
+        <v>-0.2939621097489393</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3102693787271349</v>
+        <v>-0.1053062284258388</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.017177172225189</v>
+        <v>0.1954021610454078</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.1102100256545384</v>
+        <v>0.08700378326128089</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5568694460294523</v>
+        <v>0.1526300494042374</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4476484960193403</v>
+        <v>-0.02071148207332385</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.1982880176562531</v>
+        <v>-0.2747484190416145</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1204473407716407</v>
+        <v>-0.2079784933450384</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3572514442079608</v>
+        <v>-0.4300090708381106</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7198702281555143</v>
+        <v>0.7342869713168909</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.019100440779411</v>
+        <v>1.12303654209267</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.837469573729031</v>
+        <v>0.9423514354114602</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.010791538792347</v>
+        <v>1.128945598976664</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.448163190680283</v>
+        <v>1.563166880068295</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.949610355915091</v>
+        <v>1.940010054399387</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.951566855227114</v>
+        <v>1.943660703272002</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.076189886736394</v>
+        <v>2.335393559676014</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.436679949517043</v>
+        <v>2.631067854505673</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.06163736905993</v>
+        <v>3.274212659267846</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.16017214414191</v>
+        <v>3.442893618024968</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.414552317047601</v>
+        <v>2.614515906899875</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.313435083794971</v>
+        <v>2.715530687353876</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 4.315</t>
+          <t>X &gt; 4.316</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6939254637842112</v>
+        <v>0.415315133057895</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.406315691868592</v>
+        <v>-0.6579033809464931</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.259508802434262</v>
+        <v>-1.741767960812773</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9180150567614547</v>
+        <v>-1.396338966182014</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9282779688150953</v>
+        <v>-1.611057249359902</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.244095514737566</v>
+        <v>-2.085914610479882</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9585091676367767</v>
+        <v>-1.953326063448422</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.8023007421418455</v>
+        <v>-1.482444140446873</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7947315029763189</v>
+        <v>-1.397124040749674</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5847934541089757</v>
+        <v>-1.262037383579028</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9705811429949307</v>
+        <v>-1.808107480013099</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3634908932969765</v>
+        <v>-0.3118963462720359</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.5404799282350439</v>
+        <v>-0.1297436073765965</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.523147489517477</v>
+        <v>0.01092307812341886</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.1470501897066683</v>
+        <v>0.0305533323348044</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.4750079034060306</v>
+        <v>0.3566645141230751</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.7030995031050224</v>
+        <v>0.5859593530411971</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.7244741246915467</v>
+        <v>0.5286993397020012</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.224977151449039</v>
+        <v>0.7922466970109809</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.538987964097274</v>
+        <v>1.106000511829826</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.386564770470422</v>
+        <v>1.799913708468736</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.438900397798754</v>
+        <v>1.852258212956571</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.655562958027986</v>
+        <v>1.302745915884607</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.86573238784613</v>
+        <v>1.434183226563135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 4.346</t>
+          <t>X &gt; 4.347</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.239519082625122</v>
+        <v>0.7964813403649202</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6525731145578249</v>
+        <v>-0.2210451572030294</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.01057082452431501</v>
+        <v>-0.784862025890682</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6907598729025111</v>
+        <v>-0.1632942279619414</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.7414718812882057</v>
+        <v>0.1032691128537735</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5251182305061945</v>
+        <v>-0.3011565608230597</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.7163311608303715</v>
+        <v>0.174341180958983</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.038463839205598</v>
+        <v>0.4092252344854188</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.042004942509521</v>
+        <v>0.411758321128076</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.687344110989919</v>
+        <v>0.2455731363596385</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.266400266400268</v>
+        <v>-0.6269022325349241</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.432055441022584</v>
+        <v>1.088023084917985</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.462807927889379</v>
+        <v>0.9446479956156821</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.297151905598582</v>
+        <v>0.7792445911257815</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.337278639577178</v>
+        <v>0.9183072112330777</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.989074799424131</v>
+        <v>1.47649969078541</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.819527629147281</v>
+        <v>1.492021919323705</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.863365737158993</v>
+        <v>1.443961546381701</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.136427906335136</v>
+        <v>1.716738896010092</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.472843393598623</v>
+        <v>2.146796346877174</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.095713179157158</v>
+        <v>2.873078244117551</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.893025366262314</v>
+        <v>2.669173833111152</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.392787524366476</v>
+        <v>1.881644141841655</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.37439961660035</v>
+        <v>1.863317757009341</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 4.377</t>
+          <t>X &gt; 4.378</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.9785128521538056</v>
+        <v>0.7379716238389094</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.05137465439073452</v>
+        <v>-0.051057143178312</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6299250432442847</v>
+        <v>-0.1075205118331866</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.628530695865571</v>
+        <v>1.074628760296072</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.944110218637874</v>
+        <v>1.717571647401719</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.57017280704796</v>
+        <v>1.452316706682517</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.583308778421312</v>
+        <v>1.661646442846866</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.988690727212543</v>
+        <v>2.161598091830655</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.676157587631089</v>
+        <v>1.85348278861926</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.275706530816016</v>
+        <v>1.346895557600291</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1537004662004691</v>
+        <v>0.2417411107159992</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.60342628351146</v>
+        <v>1.773521770458551</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.271660468541739</v>
+        <v>1.33060219991296</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.8000175526648547</v>
+        <v>0.8623772593977748</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.145379181049002</v>
+        <v>0.9896351166245054</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.804793165453887</v>
+        <v>1.543746670427133</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.525331629749573</v>
+        <v>1.472990448190977</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.379615658581045</v>
+        <v>1.327814619556193</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.449972512369435</v>
+        <v>1.503287192835344</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.806392274933621</v>
+        <v>1.961156731383227</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.16955304684857</v>
+        <v>2.521798582493069</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.73751720683844</v>
+        <v>1.990562467462802</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.128136797690424</v>
+        <v>1.287864963503651</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.116439500610447</v>
+        <v>1.379850749904989</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 4.408</t>
+          <t>X &gt; 4.409</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.9734839358852696</v>
+        <v>0.4654330798047468</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.187461477784062</v>
+        <v>-0.5294328597866169</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.03610621481775667</v>
+        <v>-0.6920933240088942</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7364228378990632</v>
+        <v>-0.005384859043395807</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.176085617493065</v>
+        <v>0.09101060544963957</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.5752270045749057</v>
+        <v>-0.6253605133639724</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7320236947710796</v>
+        <v>-0.7213358873354139</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.6475558205363754</v>
+        <v>-0.4437299946180104</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6374246523464322</v>
+        <v>-0.08897226221462518</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4280999352408728</v>
+        <v>-0.3036521361128734</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5831822498489174</v>
+        <v>-1.303732643396721</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4445398765491149</v>
+        <v>-0.1669628086514265</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1127211846549017</v>
+        <v>-0.6064303450637922</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3847567381214816</v>
+        <v>-0.8783332320962174</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.8464810305439627</v>
+        <v>-1.096024923580991</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1775813914710938</v>
+        <v>-0.4291065637929137</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2378649658885834</v>
+        <v>-0.4903136140636022</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.3933788439337889</v>
+        <v>-0.6455694837385408</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4771948633090162</v>
+        <v>-0.7271313308058609</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.03337195727076647</v>
+        <v>-0.2204271375266345</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.5642898889538301</v>
+        <v>0.3002510639158444</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.1885578253143834</v>
+        <v>-0.07280863373676283</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.7142857142857153</v>
+        <v>-0.84070203401496</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.465257438412479</v>
+        <v>-0.7192561095953991</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 4.439</t>
+          <t>X &gt; 4.44</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.433087594421849</v>
+        <v>2.384192010198703</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.843551866268811</v>
+        <v>1.823749128970576</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.02077713785813273</v>
+        <v>0.15935546932851</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.492777691298862</v>
+        <v>-0.151754212959915</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.8454344891171885</v>
+        <v>-0.08443469689727578</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1368158919035309</v>
+        <v>-1.070373948093419</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5057784894033404</v>
+        <v>-1.439155100674746</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.252902584904497</v>
+        <v>-0.6800117750956645</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.3856631009340603</v>
+        <v>-0.7072320898208133</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1785596404433036</v>
+        <v>-1.07288290534364</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.200466200466202</v>
+        <v>-2.139071074017764</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.117696176125385</v>
+        <v>-1.533037230374525</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4476076144743502</v>
+        <v>-1.768593775029082</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4161303085521837</v>
+        <v>-2.377186600449178</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.09746547337901</v>
+        <v>-3.584083891639963</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.661726536943462</v>
+        <v>-2.899184149184151</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.383892019120836</v>
+        <v>-2.942297894796432</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-1.875620437956208</v>
+        <v>-3.759901755833248</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-2.207644380541581</v>
+        <v>-3.775977278202532</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.928461465236808</v>
+        <v>-3.49926600670004</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.829771106230758</v>
+        <v>-3.305452802108881</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-2.226780770080744</v>
+        <v>-3.775242435062538</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-2.915012249725436</v>
+        <v>-4.382212021909638</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-2.348926333204538</v>
+        <v>-3.881311445563782</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 4.47</t>
+          <t>X &gt; 4.471</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.5562050643013663</v>
+        <v>1.125887166486891</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.3009629997362921</v>
+        <v>1.196789881321664</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.43285821455364</v>
+        <v>-1.255427950670786</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2195258781475644</v>
+        <v>0.06001559580939642</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.742946774911502</v>
+        <v>0.5355841496312834</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5763552699680901</v>
+        <v>-1.103007473601963</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.236075224547349</v>
+        <v>-2.077795914084597</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.0247838087022032</v>
+        <v>-0.9361290626916343</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6328075784769354</v>
+        <v>-1.908840663738395</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.202791632236917</v>
+        <v>-2.681756339774886</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.948765520194087</v>
+        <v>-3.421895480574413</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.00345588541451</v>
+        <v>-2.280766587876371</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.9037900874635483</v>
+        <v>-2.186890115178741</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.737461388754966</v>
+        <v>-3.016488261402202</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.804753173147908</v>
+        <v>-3.87747131557505</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.597279705579346</v>
+        <v>-2.674565123855182</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.935499243480216</v>
+        <v>-2.808482260832655</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-2.448681662446006</v>
+        <v>-3.319002477838424</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-2.028418844173181</v>
+        <v>-3.103111096914098</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-1.637243854597045</v>
+        <v>-2.916265286946071</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-1.364281539617593</v>
+        <v>-2.850292185135231</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-1.644345548801219</v>
+        <v>-3.128977903136615</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-2.389903329752954</v>
+        <v>-3.868701973616027</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.241382191952532</v>
+        <v>-2.727495687285554</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 4.501</t>
+          <t>X &gt; 4.502</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.9134096583253992</v>
+        <v>-0.1726390209464199</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.827190536867946</v>
+        <v>-1.663485183458086</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.123518482926521</v>
+        <v>-3.101504232489077</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.311718522826403</v>
+        <v>-2.658388887769966</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.142840567939551</v>
+        <v>-0.9710579730340072</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.746177221737305</v>
+        <v>-2.229178492138928</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.927041549252387</v>
+        <v>-3.579161858110211</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.263773348621243</v>
+        <v>-1.256217233499122</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9429204504413633</v>
+        <v>-0.6366953695034923</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.716986136854409</v>
+        <v>-1.698628386580445</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.001211079423371</v>
+        <v>-1.713586085458985</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.325083977992314</v>
+        <v>-0.2582314426642043</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8912487580826394</v>
+        <v>-0.5143414863989406</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.671334379291963</v>
+        <v>-1.313455044926457</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-2.05113328944023</v>
+        <v>-1.393563660426089</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.176575110892308</v>
+        <v>0.06787528463829062</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.031383407201574</v>
+        <v>-0.06604185233918258</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.298413734045603</v>
+        <v>0.6961694669610168</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.361562157364375</v>
+        <v>0.623043506844887</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.1048608084972287</v>
+        <v>1.098906657853369</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.1201558107415437</v>
+        <v>1.134395171968272</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.235156174727571</v>
+        <v>0.7695318695187083</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.077624228168183</v>
+        <v>-0.4010801232015524</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.5949336684090341</v>
+        <v>0.6791569877370165</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 4.532</t>
+          <t>X &gt; 4.533</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>283</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.363842617592283</v>
+        <v>-1.344027325446099</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.141600508521748</v>
+        <v>-3.798945466552098</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.288437833840085</v>
+        <v>-6.650392077420541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.589015830676395</v>
+        <v>-7.009989206403922</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.247682829815183</v>
+        <v>-6.63906589803247</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.47389610670001</v>
+        <v>-7.158813492853817</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.246991941488382</v>
+        <v>-8.284119067203527</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.405491176364691</v>
+        <v>-6.088832278741066</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.30389721574528</v>
+        <v>-4.987274425448263</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-5.138033573536411</v>
+        <v>-6.466903882403486</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-5.570313079146999</v>
+        <v>-6.899558021160296</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.022638116610871</v>
+        <v>-4.351452300933367</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.500819005037648</v>
+        <v>-5.827971258248851</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.722245408369886</v>
+        <v>-6.402407025154808</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-5.3813739274567</v>
+        <v>-7.060550322735367</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-3.372717796009859</v>
+        <v>-5.052735838954924</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-3.153498810798311</v>
+        <v>-4.83329608547303</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.905161073998606</v>
+        <v>-4.584779898834846</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.688979888378846</v>
+        <v>-4.36888851791052</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-1.441815860077689</v>
+        <v>-3.121972036564401</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-1.631823185251115</v>
+        <v>-2.957804423611698</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-2.061162452241042</v>
+        <v>-3.387007275480165</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.493025850846202</v>
+        <v>-3.465889453457478</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-2.568994508964153</v>
+        <v>-4.248435487599487</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 4.563</t>
+          <t>X &gt; 4.564</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.441378410748371</v>
+        <v>2.138047358929839</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.5668440000237283</v>
+        <v>-1.714317379118462</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.40389178927385</v>
+        <v>-4.659874116591666</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.607693266314961</v>
+        <v>-4.870315573220338</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.9322577198418642</v>
+        <v>-2.693543231697262</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.296063843052494</v>
+        <v>-5.019139859670233</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.069159677840865</v>
+        <v>-6.796113669188728</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.796779847310098</v>
+        <v>-4.059249737057378</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7348483948034712</v>
+        <v>-3.01273742951453</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.039526326114483</v>
+        <v>-4.790678231179164</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.275296132438989</v>
+        <v>-5.019131151831317</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.00345588541451</v>
+        <v>-3.287830304023018</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.14868804664723</v>
+        <v>-5.416017496507287</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.85991036834681</v>
+        <v>-5.637096372953877</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-4.539447050698925</v>
+        <v>-7.30026479616258</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-3.434014399456899</v>
+        <v>-5.198340185777369</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-2.037540059806751</v>
+        <v>-4.327232197126705</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.142559213466413</v>
+        <v>-3.929560338133818</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-1.926378027846653</v>
+        <v>-3.713668957209492</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.301531655607036</v>
+        <v>-1.516772895985184</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.7520366416584139</v>
+        <v>-2.059319063951214</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-1.338223099821626</v>
+        <v>-2.637677588174377</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-2.083780880773361</v>
+        <v>-3.368228001320468</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-2.66995362052397</v>
+        <v>-3.946572817357819</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 4.593</t>
+          <t>X &gt; 4.595</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>1.998250630928929</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.02499273467015</v>
+        <v>-2.847804362909606</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-6.258767072720566</v>
+        <v>-5.789582810436833</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-7.766423425045119</v>
+        <v>-5.750657130631453</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-5.75085182415026</v>
+        <v>-3.830808505434369</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-7.15093912649921</v>
+        <v>-5.147601717833233</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-9.511336548589171</v>
+        <v>-7.423309800219819</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.202675538920083</v>
+        <v>-5.445882147228531</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-10.54210463063114</v>
+        <v>-6.156274664561955</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-11.31617031704418</v>
+        <v>-7.68107003984656</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-11.04173604173604</v>
+        <v>-8.158890096932758</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-11.32091620287483</v>
+        <v>-7.685759801132633</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-13.23939099449303</v>
+        <v>-9.560801567236872</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-15.04811898512686</v>
+        <v>-11.28563984217971</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-14.91359671056287</v>
+        <v>-12.69566283900838</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-11.93741576000112</v>
+        <v>-9.84563681932103</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-10.48425207794735</v>
+        <v>-9.227674257050381</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-9.79562043795621</v>
+        <v>-9.332514960871563</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-9.579439252336449</v>
+        <v>-9.116623579947237</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-7.805044308111782</v>
+        <v>-6.674138672234854</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-8.348408523744574</v>
+        <v>-7.216684840200884</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-8.424390900275135</v>
+        <v>-6.540651102361856</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-8.149540517961562</v>
+        <v>-7.018056089127931</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-8.225509176079512</v>
+        <v>-7.093888342351207</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 4.624</t>
+          <t>X &gt; 4.626</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.936024724418729</v>
+        <v>0.3274068548220015</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.300355053510728</v>
+        <v>-0.00736994352781295</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.29120323559151</v>
+        <v>1.729214182044366</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3426172926912514</v>
+        <v>5.778164924506392</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.472038849685106</v>
+        <v>3.855072864657529</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.632650651688991</v>
+        <v>-0.7198657111498505</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-9.304297211115042</v>
+        <v>-4.666417569643372</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.1336624264287</v>
+        <v>-3.357327427094866</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-10.99068986182506</v>
+        <v>-6.49044341978334</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-11.76475554823811</v>
+        <v>-7.26335909581983</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-10.04104591061112</v>
+        <v>-5.401997866356311</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.870950709431064</v>
+        <v>-4.093445682502725</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-7.097223982760802</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-8.767925748411876</v>
+        <v>-3.850385038503845</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-7.977778905179854</v>
+        <v>-2.921226748782821</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-4.483999610932784</v>
+        <v>0.8477633477633475</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-3.168862153861767</v>
+        <v>2.301147798087463</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.273881307521428</v>
+        <v>2.196307094266281</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-1.608424759582824</v>
+        <v>3.999500062492189</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.02794395965908336</v>
+        <v>5.773647459761804</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>0.9338551063451419</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>2.30714809213341</v>
+        <v>8.329858504989851</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>2.581998474446983</v>
+        <v>8.604333217471904</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>1.056754454010203</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
   </sheetData>
@@ -5828,79 +5828,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.692278770892436</v>
+        <v>5.089311616726768</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.68088961827102</v>
+        <v>11.10374116758329</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.65253077975375</v>
+        <v>12.84032529315548</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>21.7620546328447</v>
+        <v>23.23848238482385</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>22.8672620880813</v>
+        <v>22.90269191227658</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>21.58388813773982</v>
+        <v>21.50235651107238</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>17.86961583236322</v>
+        <v>19.14310623988043</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>20.53215172531895</v>
+        <v>22.03949796973053</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>24.98543972044262</v>
+        <v>25.2555883262484</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>25.68196226932371</v>
+        <v>26.06997423751351</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>24.48580830933771</v>
+        <v>24.75673229237383</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>19.79486344231658</v>
+        <v>22.89068130162426</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>27.49356885611388</v>
+        <v>28.11672558397449</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>27.27214245278164</v>
+        <v>27.8956467075279</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>25.14242569840071</v>
+        <v>27.23750340994734</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>24.26706603271598</v>
+        <v>26.24458874458874</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>27.07410459805639</v>
+        <v>29.28527478221444</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>28.43967367969085</v>
+        <v>29.18043407839326</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>30.12644310060472</v>
+        <v>30.98362704661918</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>33.25471292811604</v>
+        <v>34.34507603119037</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>32.71134871248325</v>
+        <v>33.80252986322434</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>32.63536633595269</v>
+        <v>33.72668390181524</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>34.38080495356036</v>
+        <v>35.58846020159888</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>37.24601276603066</v>
+        <v>38.68723112297878</v>
       </c>
     </row>
     <row r="7">
@@ -5910,79 +5910,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.284515616587321</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.360328366247288</v>
+        <v>6.738661802503927</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.672498399829315</v>
+        <v>7.979214182044366</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.5456488044583</v>
+        <v>11.73054587688735</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.26283683174024</v>
+        <v>10.50189826148292</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.61518873137177</v>
+        <v>8.903150161866023</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.924661703922858</v>
+        <v>7.238344335118533</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.646021126290357</v>
+        <v>6.960132890365458</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>12.35726918617387</v>
+        <v>11.46590578656587</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13.41806588508193</v>
+        <v>12.47870439624367</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.85763777506897</v>
+        <v>10.9670497526913</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.743595228609095</v>
+        <v>8.902586063529014</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.20592719394442</v>
+        <v>12.24370971095862</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.98450079061218</v>
+        <v>12.02263083451203</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>12.32537227152537</v>
+        <v>11.36448753693147</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>12.92060084113475</v>
+        <v>11.95887445887446</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>15.53875651386859</v>
+        <v>14.50352875046842</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>18.18603093819058</v>
+        <v>17.07725947521867</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>20.23707450913144</v>
+        <v>19.07886514185727</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>22.25903025137561</v>
+        <v>21.05142523753959</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>21.71566603574282</v>
+        <v>20.50887906957356</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>21.63968365921226</v>
+        <v>20.43303310816446</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>24.66682761950749</v>
+        <v>23.38607924921794</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>26.42572134671065</v>
+        <v>25.09596128170895</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>147</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.320526351156381</v>
+        <v>-3.300711059010197</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.757320190499911</v>
+        <v>1.806689013388279</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.718557190317988</v>
+        <v>3.770030508574983</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.086184284705453</v>
+        <v>7.818981251037009</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.360259286960854</v>
+        <v>5.442374451959118</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.867201463069954</v>
+        <v>6.309612746900036</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.094105628281582</v>
+        <v>5.537664063009686</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.135192941805549</v>
+        <v>4.579180509413071</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.578076775264563</v>
+        <v>8.022028235545463</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.164555306538588</v>
+        <v>7.929384668352498</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.758717473003188</v>
+        <v>7.523172201670896</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.799265203020873</v>
+        <v>6.56415068937936</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.11661807580175</v>
+        <v>11.56343760211508</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>9.301542399137873</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.834702609165006</v>
+        <v>7.282854883870236</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6.429931178774389</v>
+        <v>7.877241805813227</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>8.336609600057187</v>
+        <v>9.103868886522832</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.63295099061522</v>
+        <v>12.40038872691935</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>11.84913217623498</v>
+        <v>12.61628010784367</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.03622553315805</v>
+        <v>13.48339802665524</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>12.1731334263688</v>
+        <v>13.62112396753275</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>10.73660683215116</v>
+        <v>12.18473378843657</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>12.37200143215181</v>
+        <v>13.8197527186057</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>12.29603277403386</v>
+        <v>13.74392046538242</v>
       </c>
     </row>
     <row r="9">
@@ -6074,79 +6074,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.254245293278686</v>
+        <v>-0.5796226236360482</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.055221169073164</v>
+        <v>1.636620986177405</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.6846163412510933</v>
+        <v>1.729214182044366</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.64440757402118</v>
+        <v>4.077484652397551</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1399893608085776</v>
+        <v>2.211081934952318</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.39672236233875</v>
+        <v>1.88784403941704</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.6236265275503783</v>
+        <v>1.115895355526689</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.794051483237197</v>
+        <v>-1.203132415757004</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.9212685974479768</v>
+        <v>1.389375174320975</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1472029110349311</v>
+        <v>0.6164594982844847</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.252159605100779</v>
+        <v>-1.660501267716867</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.066099124528336</v>
+        <v>-2.449454752797507</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.6219111021031836</v>
+        <v>1.019219915040253</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.738552734384136</v>
+        <v>-1.752879369569605</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-3.467199970048483</v>
+        <v>-3.431430830415472</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-2.337212042150341</v>
+        <v>-3.347247990105139</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.3323125142430712</v>
+        <v>-1.440348800551995</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.166946406963575</v>
+        <v>0.4956268221574405</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.917886950872109</v>
+        <v>1.22172228471441</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.639739666083955</v>
+        <v>1.918772176315095</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.096375450451163</v>
+        <v>1.886430089981715</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.9508743573430536</v>
+        <v>0.2799718836746621</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.760484097945401</v>
+        <v>1.574854759422017</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.6149967232499023</v>
+        <v>0.4786143429334402</v>
       </c>
     </row>
     <row r="10">
@@ -6156,79 +6156,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.194294692573671</v>
+        <v>-1.408704256289106</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2133335418450386</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.140264886849522</v>
+        <v>-0.05650010366991154</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.462133767637631</v>
+        <v>3.248403019744487</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.303031014485946</v>
+        <v>1.126898261482921</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.5933843128914944</v>
+        <v>0.4210073047231617</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.6281420151704182</v>
+        <v>-0.7973699505957583</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.803643579349995</v>
+        <v>-1.968438538205973</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4800321762590372</v>
+        <v>0.3051915008515778</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7424640034275498</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.158612687760666</v>
+        <v>-3.318664533022989</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.886223342172997</v>
+        <v>-4.043842507899555</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.9751729006785226</v>
+        <v>-1.14914743189852</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.541890783831391</v>
+        <v>-2.709512022630832</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-4.546310782738821</v>
+        <v>-4.706941034497099</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-4.847943199676529</v>
+        <v>-5.005411255411261</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-4.533650611650806</v>
+        <v>-4.69289982096015</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.293378285489844</v>
+        <v>-3.458454810495624</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.628766606596542</v>
+        <v>-2.796134858142729</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.993242756399923</v>
+        <v>-2.162860476746133</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.536606972032715</v>
+        <v>-2.705406644712163</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-3.957880828383914</v>
+        <v>-4.120538320406972</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-2.786169459523251</v>
+        <v>-2.95320646506778</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.758999104188291</v>
+        <v>-3.921895861148194</v>
       </c>
     </row>
     <row r="11">
@@ -6238,817 +6238,817 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.503799660480105</v>
+        <v>-1.656720129304979</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2995025385917174</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.6133150934792511</v>
+        <v>0.5387379915681834</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.64440757402118</v>
+        <v>2.603561749903221</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.494713068473466</v>
+        <v>1.077295086879751</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.681927353426104</v>
+        <v>1.26426127297713</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5166746558926221</v>
+        <v>0.4923125890867794</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5462796472300724</v>
+        <v>-0.5795496493170873</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.063871092991654</v>
+        <v>1.049239119899205</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1023514561664882</v>
+        <v>0.2763234438627151</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.573015220074041</v>
+        <v>-1.830569294927741</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.636509106703024</v>
+        <v>-2.902969492026529</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4476076144743502</v>
+        <v>-0.05787759062868503</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.237661468786989</v>
+        <v>-2.263083451202263</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.073260576109092</v>
+        <v>-4.111702939259004</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-4.654502594735</v>
+        <v>-4.707792207792203</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-4.396483637237722</v>
+        <v>-4.444883947944277</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.325032202662094</v>
+        <v>-3.359248461289276</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.108851017042333</v>
+        <v>-3.14335708036495</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.921757660119262</v>
+        <v>-2.956511270396923</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-3.072965013006957</v>
+        <v>-3.102232041537555</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-4.325417977772808</v>
+        <v>-4.368554193422845</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-4.050567595459235</v>
+        <v>-4.094079480940792</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-5.303006841812483</v>
+        <v>-5.360387924640264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 3.913</t>
+          <t>X &lt; 3.914</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.330913301635491</v>
+        <v>-1.497989970574821</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.09687106461300488</v>
+        <v>-0.04705248321035782</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.524131032758191</v>
+        <v>1.372071324901512</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.96066310849303</v>
+        <v>2.801974448315917</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.23685938936741</v>
+        <v>2.10904111862579</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.707227796183851</v>
+        <v>1.581721590437454</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5757090223273735</v>
+        <v>0.8097729065471029</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.4197774334413253</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.413860551140502</v>
+        <v>1.6444772151373</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2813719256593501</v>
+        <v>0.5144186819579559</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.953154372509218</v>
+        <v>-1.711521675880128</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.590757472716092</v>
+        <v>-2.347413936470979</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.9439167372018034</v>
+        <v>1.172281139530043</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7112014224028371</v>
+        <v>-0.4773691654879713</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.445598758693954</v>
+        <v>-2.206941034497099</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.925639006288868</v>
+        <v>-2.683982683982684</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.701353972468588</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.731104308923946</v>
+        <v>-1.494169096209909</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.514923123304186</v>
+        <v>-1.278277715285583</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.327829766381114</v>
+        <v>-1.091431905317556</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.512771042945815</v>
+        <v>-1.276835216140725</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.66402223668068</v>
+        <v>-2.42410974897841</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.389171854367106</v>
+        <v>-2.149635036496356</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.540409329689354</v>
+        <v>-3.296895861148194</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 3.944</t>
+          <t>X &lt; 3.945</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.295797540713281</v>
+        <v>-0.5796226236360482</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.02906131938390644</v>
+        <v>0.786280850122985</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.305153991200505</v>
+        <v>2.749622345309675</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.618175459553775</v>
+        <v>4.417620706819321</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.252794679496255</v>
+        <v>4.081830234272047</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.42649545093537</v>
+        <v>3.248388257104118</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.991237453984837</v>
+        <v>2.816575627635537</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.036921200676659</v>
+        <v>1.858092074038922</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.105471516945009</v>
+        <v>3.260123473640704</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.993567992694125</v>
+        <v>2.487207797604214</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4347004347004315</v>
+        <v>0.3803150588137498</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3760427580013754</v>
+        <v>-0.238570399056016</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.22886297376094</v>
+        <v>3.060036241570863</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.656085219077355</v>
+        <v>1.478413147437195</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.692232489198652</v>
+        <v>-0.2001383134086652</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.110517433102785</v>
+        <v>-0.6261595547309824</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.9068175005127657</v>
+        <v>-0.4199406372866861</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.001676859341095849</v>
+        <v>0.4956268221574405</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.217858044960856</v>
+        <v>0.7115182030817664</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.4049514018839275</v>
+        <v>0.8983640130497932</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.1994250240889599</v>
+        <v>0.6959538995055325</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.5522330281172714</v>
+        <v>-0.400300225168877</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.06045519203414784</v>
+        <v>-0.1258255126868235</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.029026979597326</v>
+        <v>-1.222065929175407</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 3.975</t>
+          <t>X &lt; 3.976</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.092686574762446</v>
+        <v>-0.8458160575313443</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.154902100229059</v>
+        <v>-0.8700338496699871</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.936696409751981</v>
+        <v>1.729214182044366</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.639609280081245</v>
+        <v>4.121850224713434</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.972113696398345</v>
+        <v>3.475500745954974</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.252983570474854</v>
+        <v>2.730789913418818</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.084117342937226</v>
+        <v>2.890518248162003</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.503361961679353</v>
+        <v>1.991188790986563</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.753344465422188</v>
+        <v>3.585471003957181</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.979278779009142</v>
+        <v>2.812555327920691</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4653201783111172</v>
+        <v>0.2915839141819916</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7445003394498997</v>
+        <v>-0.2977244954771905</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.964512520588741</v>
+        <v>2.926939524623208</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.836741706380366</v>
+        <v>1.153065617120717</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.03084602720796426</v>
+        <v>-0.1261956928821988</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.2622677387760461</v>
+        <v>0.1576322228496139</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.7323594407789784</v>
+        <v>0.9553921045056768</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.440029108871592</v>
+        <v>2.713905437951581</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.958325098116724</v>
+        <v>3.240355825087086</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.749648062290547</v>
+        <v>4.04831964747747</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.810513453908513</v>
+        <v>4.126891491933804</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.130301470127193</v>
+        <v>3.119368511891167</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>3.707266656066153</v>
+        <v>3.393843224373221</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.724953587072065</v>
+        <v>2.075774946305224</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 4.006</t>
+          <t>X &lt; 4.007</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5060042610885134</v>
+        <v>1.531566679671478</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.612262167290638</v>
+        <v>1.689400718760091</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.358413132694942</v>
+        <v>4.192268369236494</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.075780123040786</v>
+        <v>5.942368536985867</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.730007186120524</v>
+        <v>4.867661808280957</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.18192735342609</v>
+        <v>4.069406319501489</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.144125636284791</v>
+        <v>4.282679310487985</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.375288980220908</v>
+        <v>3.511857028296482</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.642302465540673</v>
+        <v>4.78487130380725</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.603530896774679</v>
+        <v>4.75087188392839</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.426984779925952</v>
+        <v>2.561877338898199</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.412510501140112</v>
+        <v>1.544211679292573</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.964157091407998</v>
+        <v>4.361936311943836</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.007436570428702</v>
+        <v>3.648246598058826</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.367915894479147</v>
+        <v>2.004881625601421</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.963144464088529</v>
+        <v>2.599268547544412</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.82900655884071</v>
+        <v>2.465351410566939</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.439673679690848</v>
+        <v>4.084648637780241</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.391148982957667</v>
+        <v>5.039456274862196</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>5.06843841831212</v>
+        <v>5.718912922268643</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>5.260368320326386</v>
+        <v>5.915283010460264</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.694189865364443</v>
+        <v>5.593131630331946</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5.459236326109398</v>
+        <v>6.36021718025242</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>5.383267667991447</v>
+        <v>6.284384927029144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 4.037</t>
+          <t>X &lt; 4.038</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4475540272875804</v>
+        <v>0.7202076533023174</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.087231714227649</v>
+        <v>2.008148907690838</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.254322598685746</v>
+        <v>4.829764747097975</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7.548333072076105</v>
+        <v>7.565086589724203</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.381349085605756</v>
+        <v>7.432135873769219</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.967360965748775</v>
+        <v>6.807743033497438</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.396669940579649</v>
+        <v>7.252832889160835</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.917628561343939</v>
+        <v>6.771781687815476</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.161556660204504</v>
+        <v>8.233147165876218</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.988693378601084</v>
+        <v>8.068750759616591</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.858318034670738</v>
+        <v>5.908733322671019</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.577133865515918</v>
+        <v>4.615785136261565</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.65872269319982</v>
+        <v>6.535219418289834</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.437296289867582</v>
+        <v>6.314140541843244</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3.976564564367933</v>
+        <v>5.047477974485794</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.371392332374114</v>
+        <v>5.236185383244205</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.638056030332706</v>
+        <v>5.305108002859029</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>5.935842487895492</v>
+        <v>6.822985351776182</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>6.352424475118461</v>
+        <v>7.038876732700508</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>7.140720236851145</v>
+        <v>8.03708156903771</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>7.599360029234397</v>
+        <v>8.30589442744084</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>7.72377845430703</v>
+        <v>8.230048466031739</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>8.59983124143023</v>
+        <v>9.518721961475251</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>8.123060980105862</v>
+        <v>9.037210195067395</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 4.068</t>
+          <t>X &lt; 4.069</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.009810677619242369</v>
+        <v>0.4787005440801479</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.276801718837184</v>
+        <v>1.597881742499318</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.425585189119467</v>
+        <v>3.713982241125841</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.484825959972618</v>
+        <v>5.26274066110151</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.140652357729124</v>
+        <v>4.280746634434692</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.838470231588786</v>
+        <v>4.306161932002183</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.881035081955382</v>
+        <v>4.341967690761265</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.76552664135388</v>
+        <v>4.06375624600819</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.438371300905153</v>
+        <v>5.882303201751654</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.785023395895038</v>
+        <v>7.209549076603693</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.265004163862237</v>
+        <v>5.706548944936863</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.17016331756848</v>
+        <v>4.620045098839434</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.14484992318998</v>
+        <v>6.404799025521278</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7.065348479074707</v>
+        <v>7.314576368783889</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.427427137801928</v>
+        <v>5.848678628553891</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>6.02265570741131</v>
+        <v>6.443065550496883</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.562253528101493</v>
+        <v>5.986046636459648</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.272895059596813</v>
+        <v>6.688960375287905</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.652208382247558</v>
+        <v>6.904851756212231</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>6.839301739170629</v>
+        <v>7.253248454710132</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>7.437862482754802</v>
+        <v>7.841558506453318</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.872483695131258</v>
+        <v>7.281059879454553</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>7.962994762599813</v>
+        <v>8.201738146056144</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>7.071365419326881</v>
+        <v>7.479702338713331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 4.099</t>
+          <t>X &lt; 4.1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7044169595012093</v>
+        <v>0.6144720355041997</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.059663349985932</v>
+        <v>2.274376088218219</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.190968377014883</v>
+        <v>4.293803847697859</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.064264405642717</v>
+        <v>5.575530679318952</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.037507964209532</v>
+        <v>4.441867866346151</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.827896852336771</v>
+        <v>4.229897882230759</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.98072694347433</v>
+        <v>4.255821538765936</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4.892562556318019</v>
+        <v>4.908461157842659</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>6.389112300585793</v>
+        <v>6.678671744012682</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>7.202348201474337</v>
+        <v>7.501500748827254</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>6.154031154031159</v>
+        <v>6.578751880350872</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>5.081200199241586</v>
+        <v>5.635108859881612</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.205053449951421</v>
+        <v>6.772585090897827</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7.041828104820233</v>
+        <v>7.748314725089529</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6.118149321183154</v>
+        <v>6.95719270410472</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>6.316552493967144</v>
+        <v>7.019664732430684</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>5.521038927343668</v>
+        <v>6.220853978431933</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>5.812845170509398</v>
+        <v>6.381970721419279</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.896751223854032</v>
+        <v>6.597862102343605</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.819294316226838</v>
+        <v>6.651729188907368</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>5.937305761969704</v>
+        <v>6.641097914558351</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>5.993598517714268</v>
+        <v>6.56525195314925</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>7.06209969367864</v>
+        <v>7.637599006056845</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>6.853855903285549</v>
+        <v>7.295809306025056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 4.13</t>
+          <t>X &lt; 4.131</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.0740087203973232</v>
+        <v>0.2574579713137979</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.493401914159278</v>
+        <v>1.278613376353803</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.728863654040595</v>
+        <v>2.665453084384971</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.133029778755912</v>
+        <v>3.760408669462002</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.433200838163273</v>
+        <v>3.311623846632237</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.617070641510566</v>
+        <v>2.707629580752226</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.070284728684292</v>
+        <v>3.404607450534186</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.460540472122027</v>
+        <v>4.143345158323484</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.393925522790319</v>
+        <v>5.201781492780555</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.511721597804254</v>
+        <v>5.219826268721476</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.448363230971928</v>
+        <v>4.137953707493566</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.277321308406165</v>
+        <v>2.842255151503188</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.26732451222248</v>
+        <v>2.849036587471936</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.603311709782098</v>
+        <v>2.966940761872806</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.721217750338546</v>
+        <v>2.308797464292248</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.981998159412811</v>
+        <v>2.338212634822803</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.624894813808247</v>
+        <v>1.865312446997876</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.742841100505331</v>
+        <v>1.873466093459179</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.181987726481829</v>
+        <v>2.202351824665996</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.146115643048162</v>
+        <v>2.050214583786556</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.271647748485606</v>
+        <v>2.185634517515446</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.30714809213341</v>
+        <v>2.222782906388836</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.473860235873971</v>
+        <v>3.627201121695748</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>3.286408857577641</v>
+        <v>3.325380167907497</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 4.161</t>
+          <t>X &lt; 4.162</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4809389032740086</v>
+        <v>-0.3869516047243593</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4766056378959505</v>
+        <v>-0.6300693746598753</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8482477762297762</v>
+        <v>0.773341457152398</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8715694064960999</v>
+        <v>0.885318693438343</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.04680676526649563</v>
+        <v>-0.1837440064233107</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7812514664889676</v>
+        <v>-0.9133681044689297</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.185683706807296</v>
+        <v>-1.13536261787349</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7269970954996978</v>
+        <v>-0.7719608637264699</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1324784145533044</v>
+        <v>-0.1805195113259686</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.107280783826269</v>
+        <v>-0.03684490321947465</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6321098256582118</v>
+        <v>-0.7710345736148412</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.740783074354596</v>
+        <v>-1.783056204377218</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.390952694441822</v>
+        <v>-1.806309930261762</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.8750519088339672</v>
+        <v>-1.385775607808256</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.165516833450738</v>
+        <v>-1.677282791731621</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.7546200610763805</v>
+        <v>-1.541191011860121</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.073089763559217</v>
+        <v>-1.766767177251893</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.178108917218879</v>
+        <v>-1.688289824244478</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.9619277315991184</v>
+        <v>-1.472398443320152</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.8670002732935629</v>
+        <v>-1.285552633352125</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.8573690972212802</v>
+        <v>-1.094826574003761</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.025517372369357</v>
+        <v>-1.170672535412862</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.1709919961193265</v>
+        <v>-0.07126656720211599</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.08930845923364217</v>
+        <v>-0.3304168772539882</v>
       </c>
     </row>
     <row r="21">
@@ -7058,79 +7058,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.456029200944954</v>
+        <v>0.02145049643695529</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4342591439365648</v>
+        <v>-0.1591242972867946</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3649995510460684</v>
+        <v>0.5616847184470615</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1915345329128399</v>
+        <v>0.6968417244476512</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2510663243647571</v>
+        <v>-0.02445375966478025</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.990492966053047</v>
+        <v>-0.6855985990107314</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.377488414741038</v>
+        <v>-0.9949412690228954</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7294880657326033</v>
+        <v>-0.3479406860196121</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2246443131708205</v>
+        <v>0.001950505147213732</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.236811235937374</v>
+        <v>0.385549863806169</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.1065151065151042</v>
+        <v>0.1199024897768908</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7717956537542747</v>
+        <v>-0.7756549321753496</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.047198802300841</v>
+        <v>-0.8965039689620795</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7280846650925312</v>
+        <v>-0.8862798384695836</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.232773029739192</v>
+        <v>-1.390221131424084</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.255305077890434</v>
+        <v>-1.412642227985323</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.69832329201855</v>
+        <v>-1.623660367275825</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.726122368458135</v>
+        <v>-1.728501071097007</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.35550102839823</v>
+        <v>-1.512609690172681</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.863388366455851</v>
+        <v>-1.942571898708898</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.020652195988262</v>
+        <v>-2.099613055109785</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.405514881399121</v>
+        <v>-2.329661021144943</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.358463726884779</v>
+        <v>-1.361277287845617</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.279992230562577</v>
+        <v>-1.437109541068892</v>
       </c>
     </row>
     <row r="22">
@@ -7140,1145 +7140,1145 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1473</v>
+        <v>1486</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2322849446141362</v>
+        <v>-0.006930558923215813</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1892832981460444</v>
+        <v>0.2639454018117604</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5430303604414348</v>
+        <v>0.9120636340728225</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2363567773277495</v>
+        <v>0.8047623737148797</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2648013279164658</v>
+        <v>0.3343823991487582</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8922509940839873</v>
+        <v>0.05028532818018761</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.529569503685671</v>
+        <v>-0.3851896006630611</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.9256574676046512</v>
+        <v>0.07684121568750868</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6125795279899435</v>
+        <v>0.4548021526493145</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5719812632828223</v>
+        <v>0.4221287377164558</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5691016383480729</v>
+        <v>0.2251251228124289</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.255613775046939</v>
+        <v>-0.5246875377015101</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.362107834114141</v>
+        <v>-0.840312592444576</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.108313599292956</v>
+        <v>-0.7922124648534776</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.49588746800638</v>
+        <v>-1.315766260415195</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.57954552433047</v>
+        <v>-1.259737346547567</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.781572092171629</v>
+        <v>-1.528243985543888</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.682925258051249</v>
+        <v>-1.56578993835565</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.534632735024843</v>
+        <v>-1.484488059450172</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.890648678848549</v>
+        <v>-1.768705506548088</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.29823556929464</v>
+        <v>-2.042072670476436</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.442106608418548</v>
+        <v>-2.252508133904385</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.556258262764857</v>
+        <v>-1.372380662337534</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.632226920882808</v>
+        <v>-1.448212915560809</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 4.253</t>
+          <t>X &lt; 4.254</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5727764198299354</v>
+        <v>-0.3709303476769108</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4026649436962799</v>
+        <v>-0.05172379287571971</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1762138872010155</v>
+        <v>0.5316602496509617</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1747974021614596</v>
+        <v>0.5321426154638615</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3687306463046127</v>
+        <v>0.25580517502123</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.419046052563381</v>
+        <v>0.3238652969093394</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5983176593232429</v>
+        <v>-0.03191216224855964</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2237515861243935</v>
+        <v>0.3438597461493771</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1740662399340351</v>
+        <v>0.5637060243779999</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.006175218450508169</v>
+        <v>0.5042267335971573</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.03072936564623063</v>
+        <v>0.4810212152358986</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9016574463239024</v>
+        <v>-0.3328054771538405</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.25450994785426</v>
+        <v>-0.6830781266496686</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.297789082777946</v>
+        <v>-0.4879857783637931</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.660005487850512</v>
+        <v>-0.9083169475258117</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.896130837481039</v>
+        <v>-1.027366410838468</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.327180856743098</v>
+        <v>-1.399095676234488</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.313435164797063</v>
+        <v>-1.682295476369589</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.334783670388703</v>
+        <v>-1.763669255968445</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.444602427479893</v>
+        <v>-2.052447702837512</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.869201797506982</v>
+        <v>-2.535540838698914</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.063949019643246</v>
+        <v>-2.730292864317285</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.373421677709707</v>
+        <v>-2.039646927102766</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.390007913024817</v>
+        <v>-2.056026148221413</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 4.284</t>
+          <t>X &lt; 4.285</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1914</v>
+        <v>1941</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.9438389990995759</v>
+        <v>-0.7814962633546898</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1064974368645011</v>
+        <v>-0.1889160292470038</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.5432431775655502</v>
+        <v>0.2277789866369915</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2472104506577182</v>
+        <v>0.08154315369605314</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.01367712145830779</v>
+        <v>-0.1512076485781577</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.08769585635938171</v>
+        <v>-0.06728113275384118</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4428188593818234</v>
+        <v>-0.1179521247327955</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3557332092191317</v>
+        <v>0.01599511160635103</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1574701080655743</v>
+        <v>0.2120417989306347</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.0955901309467535</v>
+        <v>0.1604038148055267</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2833373523028655</v>
+        <v>0.3314237866943941</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5705554525140712</v>
+        <v>-0.5655636383919287</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8071871829788719</v>
+        <v>-0.8644083430636158</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.662887358515917</v>
+        <v>-0.7248483735545079</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.799549837895313</v>
+        <v>-0.8677933197697882</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.144760139759285</v>
+        <v>-1.200763430284297</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.540131064860816</v>
+        <v>-1.48924007267135</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.540657010578997</v>
+        <v>-1.491041106219477</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.637955448783678</v>
+        <v>-1.790348076660429</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.921081527597288</v>
+        <v>-2.015660947784625</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.412199139259343</v>
+        <v>-2.506687280614116</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.488181515789904</v>
+        <v>-2.634053077159756</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.899851509651874</v>
+        <v>-1.998939518722004</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.819080355857594</v>
+        <v>-2.074771771945279</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 4.315</t>
+          <t>X &lt; 4.316</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2156</v>
+        <v>2165</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4139091588249073</v>
+        <v>-0.2459279448407372</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2421686753484025</v>
+        <v>0.3892721621212232</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.7500970790007386</v>
+        <v>1.029775053044041</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5462956019596206</v>
+        <v>0.8249041744788954</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.5519723358167639</v>
+        <v>0.9510074663658088</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.7391866207694022</v>
+        <v>1.230352405350018</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.5690592460923369</v>
+        <v>1.151244368110937</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4759474254171678</v>
+        <v>0.8730329233578615</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4710885254191624</v>
+        <v>0.822141352385735</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.3463734883567682</v>
+        <v>0.7420663230005147</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5744255744255753</v>
+        <v>1.062315341605853</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.214958668345858</v>
+        <v>0.1831040443934242</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.3193745030479604</v>
+        <v>0.07610825929249643</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3088899601835422</v>
+        <v>-0.006402487823841341</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.08675688372304791</v>
+        <v>-0.01789451519654506</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.2800255311823179</v>
+        <v>-0.2087269927916608</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4141634364301368</v>
+        <v>-0.3426441297691341</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4264182116111215</v>
+        <v>-0.3089167042600636</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.7204411076240191</v>
+        <v>-0.462540334883073</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9044052646156047</v>
+        <v>-0.6452095364624029</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.401387291009058</v>
+        <v>-1.049187575098166</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.430987478300295</v>
+        <v>-1.078844160063852</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.9706083390293898</v>
+        <v>-0.7581800711383764</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.092959186386679</v>
+        <v>-0.8340123243616517</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 4.346</t>
+          <t>X &lt; 4.347</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2340</v>
+        <v>2354</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.5837393286550707</v>
+        <v>-0.3698190760487918</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3070440167214343</v>
+        <v>0.1025409140465996</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.0049691910157037</v>
+        <v>0.3637572091107586</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3244209830426712</v>
+        <v>0.07561202569181091</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3479214212198514</v>
+        <v>-0.04777402884356974</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2461772217372982</v>
+        <v>0.1391921572538095</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3355123727649882</v>
+        <v>-0.08050503980560819</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4859478221923652</v>
+        <v>-0.1887929501491712</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4871595756860785</v>
+        <v>-0.1897866518368545</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.3210543219281803</v>
+        <v>-0.1130846558257659</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1243201243201284</v>
+        <v>0.2884176371432972</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6676805496391722</v>
+        <v>-0.5001023695332378</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.681393436495469</v>
+        <v>-0.433799695522751</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6036745406824053</v>
+        <v>-0.3575123867526884</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.6217774187435836</v>
+        <v>-0.4209233138999409</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.9239847465700919</v>
+        <v>-0.6761540640045283</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.8444474381427014</v>
+        <v>-0.6826285501748686</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8639965063322776</v>
+        <v>-0.6600266031889106</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.9896956625928581</v>
+        <v>-0.7839822910836176</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.144482647550127</v>
+        <v>-0.9794644335370037</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.431436606772664</v>
+        <v>-1.309606183491134</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.336478812363055</v>
+        <v>-1.215528610490722</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.10436347278452</v>
+        <v>-0.8560921308039084</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.094862045432386</v>
+        <v>-0.8469626168224309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 4.377</t>
+          <t>X &lt; 4.378</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2472</v>
+        <v>2465</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3839633764519306</v>
+        <v>-0.2939911296591404</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.02013836573810579</v>
+        <v>0.02031929308637359</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2466696771280183</v>
+        <v>0.04274649151988541</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6370506403325251</v>
+        <v>-0.426799820012107</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7597129737881048</v>
+        <v>-0.6814543899224645</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6129517632691233</v>
+        <v>-0.5756241064620014</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.6174391838180142</v>
+        <v>-0.6579176179385584</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.7747205381495377</v>
+        <v>-0.8549931600547183</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6522911000409053</v>
+        <v>-0.7323700755030913</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.495936074479836</v>
+        <v>-0.5316549198965816</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.0596895014370773</v>
+        <v>-0.09532347246083361</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.6220411836114579</v>
+        <v>-0.6986164864564941</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4928198741354919</v>
+        <v>-0.5236041111219407</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3097155331311683</v>
+        <v>-0.3390034743839436</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.4429540845804496</v>
+        <v>-0.3886275021876315</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.6972400780778543</v>
+        <v>-0.6055996066138007</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.5886595367237319</v>
+        <v>-0.5772449383174489</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.5318663926487588</v>
+        <v>-0.5198138368647918</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.5584036536309398</v>
+        <v>-0.5878981151696721</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.6949348921771374</v>
+        <v>-0.7661638670677746</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.8337683634733537</v>
+        <v>-0.9841664244861335</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.6670322934019737</v>
+        <v>-0.7760367266660282</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.432634985522057</v>
+        <v>-0.5015620141839747</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.4276974947726941</v>
+        <v>-0.5368263160887921</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 4.408</t>
+          <t>X &lt; 4.409</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2622</v>
+        <v>2619</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3044457770503115</v>
+        <v>-0.1471472279795023</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.05855490095542848</v>
+        <v>0.1671786846290644</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.01126425771202832</v>
+        <v>0.2182776195614125</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.229465087171441</v>
+        <v>0.001696261439789737</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3660129152838891</v>
+        <v>-0.02863411183295028</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1787986303312508</v>
+        <v>0.196514586673743</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2272567839601933</v>
+        <v>0.2263986633790367</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2007867589992571</v>
+        <v>0.1390997806725451</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1974022950821208</v>
+        <v>0.02785691294998571</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1324138243632049</v>
+        <v>0.09495650991845395</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1801592762691158</v>
+        <v>0.4071986644897052</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1371597101938491</v>
+        <v>0.05208423622306668</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.03473635286086818</v>
+        <v>0.18894507887439</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1184205521220676</v>
+        <v>0.2733263017023404</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.2602073648430405</v>
+        <v>0.3406507398987983</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.05452060264463654</v>
+        <v>0.1332049012461312</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.0729379986935399</v>
+        <v>0.1520178139059354</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.1204741463305936</v>
+        <v>0.1999071597220166</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.1459612053294492</v>
+        <v>0.224885978599751</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.01019486566509187</v>
+        <v>0.06808917688393024</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.1721708280560819</v>
+        <v>-0.09263186698892412</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.05745907796575267</v>
+        <v>0.0224347336485593</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.2173913043478208</v>
+        <v>0.2587269337212916</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.14142264622987</v>
+        <v>0.2210771929073374</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 4.439</t>
+          <t>X &lt; 4.44</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2796</v>
+        <v>2808</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5557373520449573</v>
+        <v>-0.5425565151413707</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4204245690741502</v>
+        <v>-0.4143703505282161</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.004730840097607825</v>
+        <v>-0.0361500833199031</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.1120269055522343</v>
+        <v>0.03437168071314289</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1918973358595792</v>
+        <v>0.01909402867868693</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.03100574281182844</v>
+        <v>0.2416727503886094</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1144409572739988</v>
+        <v>0.3244249211991104</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.05713323920218727</v>
+        <v>0.1530510832836427</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.08698753739840726</v>
+        <v>0.1589257295858175</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.04021096827969473</v>
+        <v>0.240710908250179</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2699121007472129</v>
+        <v>0.4791580147995589</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.02642073332721395</v>
+        <v>0.3428587538017069</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1005159548391248</v>
+        <v>0.3949103621592656</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.0932987625029611</v>
+        <v>0.5299568418380289</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.4695147632304995</v>
+        <v>0.7977394701834015</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.3721080495227014</v>
+        <v>0.6442631442631495</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.3093987157034519</v>
+        <v>0.6527961497358135</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.4186652763294987</v>
+        <v>0.83285573081492</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.4919893190921272</v>
+        <v>0.8350718980640366</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.4290826760151916</v>
+        <v>0.7726299587443108</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.4072695245379663</v>
+        <v>0.7286592893537716</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.4958128733953941</v>
+        <v>0.8308760060073581</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.6492858890164257</v>
+        <v>0.9629005760392602</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.5233838002812661</v>
+        <v>0.8514557872034487</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 4.47</t>
+          <t>X &lt; 4.471</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2929</v>
+        <v>2931</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.09408631862163475</v>
+        <v>-0.1879019543256675</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.05080795206146149</v>
+        <v>-0.1998027130008779</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2414054600606619</v>
+        <v>0.2096632722495571</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.03691077095212592</v>
+        <v>-0.01002632623993094</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1246656612793089</v>
+        <v>-0.0895060968705863</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.09651601497767359</v>
+        <v>0.1843956203749499</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2065723541023488</v>
+        <v>0.3474740114123875</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.004133440921457066</v>
+        <v>0.156603877810312</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1053246309285569</v>
+        <v>0.3194359970207259</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2002609241577034</v>
+        <v>0.4489323855718226</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3245734550969104</v>
+        <v>0.5730280135608723</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1671857816569471</v>
+        <v>0.3820652150265147</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1506316812439294</v>
+        <v>0.3664639112111132</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2896754271827007</v>
+        <v>0.5056541016223335</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.4677770778905668</v>
+        <v>0.650201822645748</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.2664852079448039</v>
+        <v>0.4486426015857816</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.323022693905088</v>
+        <v>0.4712667646666091</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.4088088635770148</v>
+        <v>0.5571223090140833</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.338761156661505</v>
+        <v>0.5210605486303379</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2735252263049972</v>
+        <v>0.4898530788635114</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.2280006665800229</v>
+        <v>0.4789345764388813</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.274899119383349</v>
+        <v>0.5259413931968382</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.3996766660679043</v>
+        <v>0.6505013891516711</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.2076740437202957</v>
+        <v>0.4587701718975694</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 4.501</t>
+          <t>X &lt; 4.502</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3061</v>
+        <v>3078</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1080185560852698</v>
+        <v>0.01926252861898092</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2161512367305676</v>
+        <v>0.1856664107988664</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3684878808262297</v>
+        <v>0.3462795948503512</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2719668850383954</v>
+        <v>0.296902051377792</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1340804176230606</v>
+        <v>0.1084875875588551</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.3212947025756989</v>
+        <v>0.2491265369121649</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4581761183560644</v>
+        <v>0.4001260106320288</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1470363532032479</v>
+        <v>0.1404819530674501</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1097417169239279</v>
+        <v>0.0712242476069278</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1998962721931363</v>
+        <v>0.1900793731425736</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2330623182932854</v>
+        <v>0.1918152007663636</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.03787180739382734</v>
+        <v>0.02891523597470069</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1038629737609398</v>
+        <v>0.05761157471480516</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1948348120438084</v>
+        <v>0.1471682142307529</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.2391875301692536</v>
+        <v>0.1561946959855689</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.1372479275657952</v>
+        <v>-0.007610125886209573</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.1203504758077543</v>
+        <v>0.007406963017615453</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.03483277365122461</v>
+        <v>-0.07810461594309714</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.04221762959440412</v>
+        <v>-0.06992314413503209</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.01224801613115289</v>
+        <v>-0.1233684956577861</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.01403909276940141</v>
+        <v>-0.1273939401171731</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.02748478960250367</v>
+        <v>-0.08644741131606537</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.1259926432672103</v>
+        <v>0.04507103690409764</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.0695806119864173</v>
+        <v>-0.07634448270208338</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 4.532</t>
+          <t>X &lt; 4.533</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3136</v>
+        <v>3141</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.122180266153407</v>
+        <v>0.1202148334706905</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2815303812259842</v>
+        <v>0.3398993256510323</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4740664893812863</v>
+        <v>0.5952121941524382</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.411499201546718</v>
+        <v>0.6275947312281929</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3810124376664632</v>
+        <v>0.5945745725136717</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.4911580843995296</v>
+        <v>0.6413245389292896</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5607036852017799</v>
+        <v>0.7423703913928463</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3955437826495043</v>
+        <v>0.5458155004383087</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2967321206143723</v>
+        <v>0.4472112365025041</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.461607460733596</v>
+        <v>0.5800741041902313</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.5006029220065429</v>
+        <v>0.6190789220001136</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2717301737613838</v>
+        <v>0.3905680308164037</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4047447659439669</v>
+        <v>0.5232601097983505</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4247919423295272</v>
+        <v>0.5750178318371368</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.4842380990366379</v>
+        <v>0.6343288067727357</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.3035875115365059</v>
+        <v>0.454088358978801</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.2839453272211045</v>
+        <v>0.4345053342404199</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.2616679134123459</v>
+        <v>0.4122951100636314</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.2422735779723624</v>
+        <v>0.3930055469067639</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.1299470982172011</v>
+        <v>0.280927849395141</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.1471188153635126</v>
+        <v>0.2662400292245977</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.185885587630402</v>
+        <v>0.304970747362681</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.2249047866718143</v>
+        <v>0.312172729257945</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.2318320937617528</v>
+        <v>0.3827784918785895</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 4.563</t>
+          <t>X &lt; 4.564</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3223</v>
+        <v>3225</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.08703332363113248</v>
+        <v>-0.1309948966831982</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.03423772696599059</v>
+        <v>0.1050659557882838</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1452413041608054</v>
+        <v>0.2856792819475444</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1576034166505522</v>
+        <v>0.2986726653531235</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.05636104660363372</v>
+        <v>0.1652327691454261</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1993299948282328</v>
+        <v>0.3079891557429448</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2461590422397535</v>
+        <v>0.4171581184973974</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1087276474445176</v>
+        <v>0.2492411902728833</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.04448124934572917</v>
+        <v>0.1850415890350092</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1840429903980407</v>
+        <v>0.2943331176303303</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1983801118535311</v>
+        <v>0.3084642060575788</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.06079670897719325</v>
+        <v>0.2021248781280747</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1908295785846832</v>
+        <v>0.3330616445627186</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1733815132063086</v>
+        <v>0.3467641972852675</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.2752882493616866</v>
+        <v>0.4492123359419793</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.2083153272341534</v>
+        <v>0.3199720683481857</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.1236402017715648</v>
+        <v>0.2664353982760517</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.1300531451964773</v>
+        <v>0.242024917142885</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.1169671912818941</v>
+        <v>0.2287987995308711</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.01831428710845273</v>
+        <v>0.09347717754754825</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.04569100488686928</v>
+        <v>0.1269530649709694</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.08133076823721552</v>
+        <v>0.1626581469001209</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.1266814679378356</v>
+        <v>0.2077735189903223</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.1623676418314304</v>
+        <v>0.2435249583423911</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 4.593</t>
+          <t>X &lt; 4.595</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.04862589357745861</v>
+        <v>-0.08019533310608296</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1529861491910864</v>
+        <v>0.114324775208857</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2379615724691604</v>
+        <v>0.2324923048877068</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2953725781936853</v>
+        <v>0.2309989122241021</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2187824063535331</v>
+        <v>0.1539267465929797</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2721287616849608</v>
+        <v>0.2068996761776418</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.3620629622725815</v>
+        <v>0.2984583444465656</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3123412263233476</v>
+        <v>0.2190209632843647</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.401543283996233</v>
+        <v>0.2476662221375605</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.4311573812965221</v>
+        <v>0.309102062117887</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4208284153837667</v>
+        <v>0.3284298979697482</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.4315992258887107</v>
+        <v>0.3094780664700707</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.504892029451014</v>
+        <v>0.3850958838408474</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5740426860811354</v>
+        <v>0.4547076943380546</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.5690833390463084</v>
+        <v>0.5116736841176106</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.455654161090628</v>
+        <v>0.3969292806819382</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.4003078066125454</v>
+        <v>0.3721287677949334</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.3741279706524594</v>
+        <v>0.3764708795256055</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.3659822152196455</v>
+        <v>0.3678734636325842</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.2982819480807066</v>
+        <v>0.2693961891979484</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.3191442578858741</v>
+        <v>0.2913840569965771</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.3221466626508871</v>
+        <v>0.2641684168278502</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.3117310580640975</v>
+        <v>0.2835362879264949</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.3147325102295753</v>
+        <v>0.286687070657166</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 4.624</t>
+          <t>X &lt; 4.626</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3350</v>
+        <v>3354</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.06006098606133747</v>
+        <v>0.04585706187155836</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.06753395572131637</v>
+        <v>0.08243296025613489</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.06736666367719835</v>
+        <v>0.08265333548352771</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.007015012817710442</v>
+        <v>0.008554175642530026</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.03014861401847924</v>
+        <v>0.04517258277385849</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1153957526622804</v>
+        <v>0.1302726834725263</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1906731534205406</v>
+        <v>0.2056706901636645</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1667328304882929</v>
+        <v>0.1818370022772768</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2253663002870425</v>
+        <v>0.2403937651945398</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2413103843128539</v>
+        <v>0.2565293029284348</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2060161069973745</v>
+        <v>0.2212077568493029</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1820629384148447</v>
+        <v>0.1973615494809806</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1457031998841174</v>
+        <v>0.1613492779295385</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1800556180477457</v>
+        <v>0.1957240908395264</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.163878161493713</v>
+        <v>0.1797460221275031</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.09213697830683287</v>
+        <v>0.1079353919924984</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.065133002268837</v>
+        <v>0.08100356663707231</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.06731162402233792</v>
+        <v>0.08321185617104021</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.03307937657562121</v>
+        <v>0.0489667877552904</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.0005748757353813971</v>
+        <v>0.01530679969392423</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.01921741793552201</v>
+        <v>-0.003163996088808574</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.04749201024976202</v>
+        <v>-0.03138030916910139</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.05316559078986671</v>
+        <v>-0.03711640758427848</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.02176598726170198</v>
+        <v>-0.005729663005247687</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_level.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_level.xlsx
@@ -625,158 +625,158 @@
         <v>42</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-15.4388985509312</v>
+        <v>-15.34215466685826</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-3.951191594454151</v>
+        <v>-3.765520526039161</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.015488859687167</v>
+        <v>-2.647551884971662</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.725778917405741</v>
+        <v>-3.237925911590501</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-11.1630552020018</v>
+        <v>-10.61547648525615</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-13.34824905127684</v>
+        <v>-12.8304394807071</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-9.382003270305084</v>
+        <v>-8.886877979221651</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-14.40085775104133</v>
+        <v>-13.93231808972767</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.99408441094033</v>
+        <v>-11.43923526790667</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-10.39632077790451</v>
+        <v>-9.864263902814052</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-12.49784559378227</v>
+        <v>-11.96748595205484</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-15.1514210004058</v>
+        <v>-14.61878801109284</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-16.27569343390767</v>
+        <v>-15.73464558751959</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-14.12693421800714</v>
+        <v>-13.61271283343786</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-17.16191781547788</v>
+        <v>-16.67151640775744</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-14.19869710382712</v>
+        <v>-13.74105923934488</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-11.96062539752967</v>
+        <v>-11.47280867707185</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-4.938746294176909</v>
+        <v>-4.47865340350031</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-2.347167585008123</v>
+        <v>-1.888322773731154</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-2.161131072031509</v>
+        <v>-1.674434196667569</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-2.703608166332742</v>
+        <v>-2.241640266515397</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-2.780006660069553</v>
+        <v>-2.317211976747089</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.254219052540265</v>
+        <v>2.686339077513225</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.179294615043361</v>
+        <v>2.52523160612462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 3.774</t>
+          <t>X ≈ 3.776</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.196004599622533</v>
+        <v>1.211644706201255</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-13.88393445943277</v>
+        <v>-10.86041989008779</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.639303939802552</v>
+        <v>-7.378926862321251</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.671918657607009</v>
+        <v>-5.604089098073494</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.68817915817593</v>
+        <v>-10.61401608464464</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.980473381469729</v>
+        <v>-3.356683720352592</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.09373758495848961</v>
+        <v>-1.779583053507061</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.026235129710194</v>
+        <v>-9.191780775714854</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.986476561453721</v>
+        <v>-9.0678292618394</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.602028490231305</v>
+        <v>-12.2341509956315</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.484876796204595</v>
+        <v>-11.96635435842045</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.9165845241624311</v>
+        <v>-7.500559674633386</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.353783525812823</v>
+        <v>3.2508627265481</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.5910189497411835</v>
+        <v>-4.116727321228467</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-5.763592995243393</v>
+        <v>-11.92148087651682</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-5.172340551198268</v>
+        <v>-13.74025691742317</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-8.158660419530882</v>
+        <v>-13.84813545602724</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-2.561962303476641</v>
+        <v>-9.231726960464314</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-8.05268824487473</v>
+        <v>-13.77500069840821</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-10.72206928123921</v>
+        <v>-18.32086401261642</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-8.412625179405076</v>
+        <v>-16.51432487516833</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-14.20157806402955</v>
+        <v>-21.35325213495683</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-16.78761057554467</v>
+        <v>-23.49621726215341</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-22.58261014686313</v>
+        <v>-28.42714934625688</v>
       </c>
     </row>
     <row r="8">
@@ -786,243 +786,243 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.531030546778503</v>
+        <v>5.939921565468879</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.118246977213794</v>
+        <v>0.9661914151920286</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.365925133069787</v>
+        <v>-5.012085273218212</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-7.105143147553427</v>
+        <v>-5.603279619191269</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.440429955830638</v>
+        <v>-5.878246331663512</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-11.31593174469427</v>
+        <v>-10.45980764231447</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-12.08705673838697</v>
+        <v>-11.25367880241667</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-18.45958706842707</v>
+        <v>-13.92926263557387</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-18.42463224839281</v>
+        <v>-13.80686301371551</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-21.23176886566499</v>
+        <v>-16.97436066847049</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-29.09569941756157</v>
+        <v>-23.82255524959668</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-29.38213444945298</v>
+        <v>-26.47749895753764</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-30.5112222783119</v>
+        <v>-29.97045005241791</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-34.80959691617494</v>
+        <v>-34.97396076228102</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-35.4762847637021</v>
+        <v>-33.2901193399679</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-36.930066649061</v>
+        <v>-32.74031435304006</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-33.00231919393033</v>
+        <v>-30.47828424282941</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-35.15434828432561</v>
+        <v>-32.99701040699066</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-32.91184776525265</v>
+        <v>-30.41557598618529</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-32.73528977678883</v>
+        <v>-27.83242611935551</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-33.28728274728255</v>
+        <v>-28.4077466353699</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-35.4127113147072</v>
+        <v>-30.87088635737202</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-35.14914227689028</v>
+        <v>-30.63670148654554</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-39.3173040244135</v>
+        <v>-35.57000648911348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 3.837</t>
+          <t>X ≈ 3.838</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-7.160558007350431</v>
+        <v>-4.935715281026667</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-14.59028001917576</v>
+        <v>-10.85790631715691</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.47531542658935</v>
+        <v>-6.430654242938793</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.540826090189071</v>
+        <v>-1.343267407852039</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.425031298393534</v>
+        <v>-4.457276493554247</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-9.792408742914013</v>
+        <v>-7.143674844549651</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-14.11559605598063</v>
+        <v>-7.936492104058829</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.288774063327708</v>
+        <v>0.2873895370506716</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.250501102973004</v>
+        <v>0.4140548245489626</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-11.57794799026718</v>
+        <v>-0.3781774654819188</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-14.86501033316161</v>
+        <v>-2.95223039517947</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-15.14719913351677</v>
+        <v>-3.228544206814462</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-16.27199588431553</v>
+        <v>-4.341384893293373</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.376308056763037</v>
+        <v>1.106938468179941</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-13.59668741879905</v>
+        <v>-2.421882406799732</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-16.57062071542653</v>
+        <v>-4.712840873937985</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-27.40062719552046</v>
+        <v>-13.37108755579634</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-31.07880979193617</v>
+        <v>-16.3599285651488</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-30.87301150684803</v>
+        <v>-16.15092484694577</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-30.69606441913026</v>
+        <v>-15.94164029998657</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-34.81573132250389</v>
+        <v>-19.36793920209034</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-34.90230642559201</v>
+        <v>-19.44896598674317</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-34.63884027189182</v>
+        <v>-19.21145887296627</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-34.72546728971962</v>
+        <v>-19.37953029863728</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 3.867</t>
+          <t>X ≈ 3.869</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.613932774640283</v>
+        <v>-5.880676418828031</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4012177235361776</v>
+        <v>-1.397908127211188</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.265806867420473</v>
+        <v>2.085554972267225</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.540574470565602</v>
+        <v>-3.236071732361715</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.6759510901316759</v>
+        <v>1.223690693383446</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.964928512317456</v>
+        <v>10.85093437644669</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10.75244387443529</v>
+        <v>10.06375539801013</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>10.47939355067646</v>
+        <v>5.025560007554262</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.968566022373949</v>
+        <v>0.4140116847808386</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>9.757348945633794</v>
+        <v>-0.3781540115546846</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>10.03401780975442</v>
+        <v>-0.106445691144252</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.20162015052783</v>
+        <v>-5.125965711285026</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>8.642587994621699</v>
+        <v>-1.493785517952247</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.304827615078565</v>
+        <v>-11.23546392171824</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.6492918068416813</v>
+        <v>-11.91882940422131</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.320106883816095</v>
+        <v>-16.11267319296289</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.454616730902927</v>
+        <v>-16.22147767774918</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.560297661789676</v>
+        <v>-16.35939713308625</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-5.911508545665079</v>
+        <v>-20.90495764626004</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-9.293807129882794</v>
+        <v>-25.45320526515349</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-6.270725575537462</v>
+        <v>-21.27060172141903</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-6.34849659109846</v>
+        <v>-21.35232593065081</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-13.21683173793377</v>
+        <v>-30.63635275694946</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-16.86832443257595</v>
+        <v>-35.57000648911348</v>
       </c>
     </row>
     <row r="11">
@@ -1035,158 +1035,158 @@
         <v>28</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.06796541387392807</v>
+        <v>0.02947316447718862</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.145446261023295</v>
+        <v>3.331314740291802</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8.812922386835574</v>
+        <v>9.181173980098215</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.557390168399337</v>
+        <v>5.045284496907939</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11.32579656725053</v>
+        <v>11.87399824820562</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.413027234344455</v>
+        <v>4.931226922795794</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.646985702039665</v>
+        <v>4.142311453840406</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.371778278474224</v>
+        <v>3.84068046132839</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6.967980068972182</v>
+        <v>7.523179689668602</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.645398735888818</v>
+        <v>3.17758717249859</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.6368608961421032</v>
+        <v>-0.1064327313779927</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.643373788137183</v>
+        <v>3.17623609299882</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>12.20103763406987</v>
+        <v>12.74258944664343</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>15.54518548888849</v>
+        <v>16.0599024844178</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>14.89421243906509</v>
+        <v>15.38510717890507</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>15.49183289653747</v>
+        <v>15.94987567150646</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>15.36296530524572</v>
+        <v>15.8510904780539</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>15.26292581223733</v>
+        <v>15.72319490807531</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>15.48320966485445</v>
+        <v>15.94217472305562</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>15.67463854592067</v>
+        <v>16.16142719462651</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>15.13752695427011</v>
+        <v>15.59956587797875</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>15.06652658381496</v>
+        <v>15.52936757379815</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>15.34558747137801</v>
+        <v>15.77772097994639</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>15.27453271027957</v>
+        <v>15.62046970136272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 3.929</t>
+          <t>X ≈ 3.93</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>14</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>17.65893537085024</v>
+        <v>17.75738817699533</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.33116030339083</v>
+        <v>17.51779953733141</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>30.09789360741163</v>
+        <v>30.46724694176674</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>36.49576169772959</v>
+        <v>36.98522550128169</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>43.27379484796597</v>
+        <v>43.82349166608216</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>36.37174950060557</v>
+        <v>36.89136070824066</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>42.7202137451579</v>
+        <v>43.2171783459404</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>42.45746639690437</v>
+        <v>42.92791349150043</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>35.40268866942702</v>
+        <v>35.95893251726638</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>41.75601797143253</v>
+        <v>42.28955535461908</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>42.04306048330525</v>
+        <v>42.57485565417386</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>41.77892401051909</v>
+        <v>42.31294370123001</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>40.67183648836303</v>
+        <v>41.21416047522515</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>40.46491392694176</v>
+        <v>40.98024678514285</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>39.82197556295642</v>
+        <v>40.31342538150192</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>40.4275831369346</v>
+        <v>40.8861211033478</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>40.3067320681709</v>
+        <v>40.79528981394451</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>40.21471088435393</v>
+        <v>40.67535176304145</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>40.44301268557948</v>
+        <v>40.90228787408513</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>40.64246718630113</v>
+        <v>41.12950365248136</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>40.11339775259501</v>
+        <v>40.5756228837145</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>40.05043677729115</v>
+        <v>40.51340194860737</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>40.33753871549614</v>
+        <v>40.76973451478089</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>40.27453271028038</v>
+        <v>40.62046970136434</v>
       </c>
     </row>
     <row r="13">
@@ -1196,79 +1196,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.61365269541718</v>
+        <v>-5.879807863938332</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-18.13325370066827</v>
+        <v>-22.67653102047176</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-8.926378303705903</v>
+        <v>-16.83636143732521</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.007108519882408</v>
+        <v>-12.69981506670678</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.875679331717095</v>
+        <v>-10.61094877525284</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.69014298082331</v>
+        <v>-12.8249745054345</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.645495181817175</v>
+        <v>-6.515433530613912</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.370424156041864</v>
+        <v>-6.820312286903579</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6.966459427370879</v>
+        <v>-1.956700988043522</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.19967422446436</v>
+        <v>-2.749370813496732</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6375702364917615</v>
+        <v>-7.220345879914774</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9152156648448937</v>
+        <v>-7.497929410918992</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.52300758067674</v>
+        <v>-3.867230963230661</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.256256141493949</v>
+        <v>-4.115323151755327</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.6483750431253199</v>
+        <v>-2.422225324539951</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>8.366021370809122</v>
+        <v>2.886680524983028</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>15.36180911524229</v>
+        <v>7.535125143936391</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>25.95553689622606</v>
+        <v>14.53387228062509</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>29.74509827010312</v>
+        <v>17.12978267643733</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>37.07493735155347</v>
+        <v>22.10539250721567</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>40.11287916473416</v>
+        <v>23.92431026854948</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>40.05009236817521</v>
+        <v>23.85697646546294</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>40.33736510853024</v>
+        <v>24.10818850082475</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>36.70310413885181</v>
+        <v>21.57285065374312</v>
       </c>
     </row>
     <row r="14">
@@ -1278,79 +1278,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.56501599550791</v>
+        <v>13.88558985927636</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>11.41798775823852</v>
+        <v>21.3827497786164</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>13.53853099404945</v>
+        <v>24.01101396502555</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.83316067412352</v>
+        <v>26.00930674175247</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>10.1381961641647</v>
+        <v>20.58155840009127</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>9.14454825652507</v>
+        <v>20.74505497117736</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9.563744476418854</v>
+        <v>19.96101778655533</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>9.290740021579325</v>
+        <v>19.66481577079097</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.33433819211956</v>
+        <v>18.50527553432061</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>12.12349821359452</v>
+        <v>21.59766663470151</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>11.2162252071843</v>
+        <v>20.58384388667025</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.571009862969007</v>
+        <v>17.72816675869865</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.825840648160032</v>
+        <v>17.91580612941527</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>13.16907659160519</v>
+        <v>20.2637461817583</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>10.14380039613059</v>
+        <v>17.00098687747982</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>11.9272149870356</v>
+        <v>18.86161265114711</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>8.234200699940288</v>
+        <v>14.87684026661835</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>9.320076271607164</v>
+        <v>14.74879304011949</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>11.91571056501069</v>
+        <v>16.26432186203661</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>12.10625216186807</v>
+        <v>16.48397340277572</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>12.75767682277496</v>
+        <v>17.22007052281673</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>15.06569191689193</v>
+        <v>21.04437556316874</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>17.72532744770054</v>
+        <v>23.89150574580555</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>22.41738985313751</v>
+        <v>28.93215801305073</v>
       </c>
     </row>
     <row r="15">
@@ -1360,79 +1360,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.043853457449778</v>
+        <v>-2.461310362675349</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.46791684746966</v>
+        <v>-0.5950043145117832</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.745242006529885</v>
+        <v>3.438043150617901</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>15.0297944735641</v>
+        <v>11.30231143599747</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>19.2705432612599</v>
+        <v>14.204539032798</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>19.46377378018069</v>
+        <v>15.42362090175724</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>20.98849201354007</v>
+        <v>19.92701305193204</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>21.86285120310343</v>
+        <v>20.68937901467807</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>24.19798505752578</v>
+        <v>23.99824803902448</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>23.43719844489863</v>
+        <v>24.27319409942763</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>21.43081943498981</v>
+        <v>22.43569701123599</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>18.87168365910222</v>
+        <v>20.04954134436258</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>16.61266592238312</v>
+        <v>17.88445802024759</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>18.68954493464385</v>
+        <v>20.82439056641156</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>19.18652062548234</v>
+        <v>21.21286092069354</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>17.49309897082189</v>
+        <v>19.65788136662641</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>18.51230293325878</v>
+        <v>20.62242142834247</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>19.56072496720786</v>
+        <v>21.55826834073649</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>16.34047569429475</v>
+        <v>19.65569748571583</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>18.82845776105626</v>
+        <v>22.00156490393957</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>19.44136830871209</v>
+        <v>23.56793045657525</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>20.52114445414383</v>
+        <v>23.50112998895155</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>24.24984554377991</v>
+        <v>26.94333388381654</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>21.8837281125795</v>
+        <v>24.66302289285232</v>
       </c>
     </row>
     <row r="16">
@@ -1442,79 +1442,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4634295554463961</v>
+        <v>-0.8583236539144039</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.009921602971424193</v>
+        <v>1.554090920040494</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6528889535154789</v>
+        <v>1.191934387315179</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.728074291295556</v>
+        <v>-3.832358180916543</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-8.003886925785402</v>
+        <v>-7.654249702082673</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.454074295184</v>
+        <v>-5.725642570495161</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.012222576840074</v>
+        <v>-10.06866510713885</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-6.501308339610077</v>
+        <v>-9.486599987065716</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.30553141710886</v>
+        <v>-6.699315101436632</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.821934803160886</v>
+        <v>0.5029207366891626</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.88822180252776</v>
+        <v>1.665066664970638</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.613667545817037</v>
+        <v>1.391589271490915</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.86720011876357</v>
+        <v>2.948838589493342</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11.18533023700734</v>
+        <v>8.04129905302343</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>8.952096141140764</v>
+        <v>5.585249133097271</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>11.13097250836549</v>
+        <v>7.927931266434641</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>8.626604536911557</v>
+        <v>5.1555028017249</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.148958381226151</v>
+        <v>3.242736529484048</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>6.366996234956865</v>
+        <v>3.458384412152483</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.178462132328455</v>
+        <v>0.9993523795842094</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>6.016824316782582</v>
+        <v>2.217168556677549</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.564425905375373</v>
+        <v>-0.5332425470917386</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.047120748350608</v>
+        <v>-1.181916960448369</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.385643821391305</v>
+        <v>-3.129530298637285</v>
       </c>
     </row>
     <row r="17">
@@ -1527,76 +1527,76 @@
         <v>133</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.234839780100017</v>
+        <v>1.332163176229017</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.375730391058774</v>
+        <v>5.561436662494486</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.931501915849225</v>
+        <v>7.299048905114894</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.970492084897096</v>
+        <v>7.457694170638185</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.148466181958256</v>
+        <v>5.695427882678331</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.842707452292913</v>
+        <v>4.360019973764025</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.824493762866524</v>
+        <v>4.319061784975496</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>8.781906395379011</v>
+        <v>9.250426690438957</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>10.31989674012338</v>
+        <v>10.87457042402929</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>8.80585030998553</v>
+        <v>9.337692763355392</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>10.58052667159263</v>
+        <v>11.11080412681613</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>10.30849806610132</v>
+        <v>10.84109430620616</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8.443754365200526</v>
+        <v>8.984734859433992</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>9.724577795644322</v>
+        <v>10.23878781166642</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>12.07137425134312</v>
+        <v>12.56191110164358</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>9.670038255319241</v>
+        <v>10.12772250520821</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>7.29112607297192</v>
+        <v>7.778853217457844</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.938801675651234</v>
+        <v>5.398704407827694</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>5.156595143783228</v>
+        <v>5.615257713693524</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.844029844344533</v>
+        <v>4.330545707558663</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.050871181413513</v>
+        <v>1.512691508491962</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.230165387829103</v>
+        <v>3.692875221276736</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.009467167674515</v>
+        <v>5.44154522957809</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>6.439946244114957</v>
+        <v>6.785883235197296</v>
       </c>
     </row>
     <row r="18">
@@ -1609,76 +1609,76 @@
         <v>133</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.746876657013232</v>
+        <v>-1.649894837274921</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.319635867639896</v>
+        <v>-4.134836367335346</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-6.497637723934268</v>
+        <v>-6.131398410885133</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.463888659029166</v>
+        <v>-5.978036358134858</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.065279343238572</v>
+        <v>-2.519305067989585</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.866276119795323</v>
+        <v>-5.349994415192597</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.406821631090871</v>
+        <v>-0.912919199920303</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1901792893008292</v>
+        <v>0.2775628285876479</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.141240464806437</v>
+        <v>-2.587590457572183</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.650465956190033</v>
+        <v>-7.119735812731172</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-9.622813517329483</v>
+        <v>-9.093742052740417</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-12.89543241427311</v>
+        <v>-12.36409424682056</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-19.26001924595148</v>
+        <v>-18.72039652519901</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-23.98169805603619</v>
+        <v>-23.46892833471019</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-23.89607113356021</v>
+        <v>-23.40688646799259</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-24.06174245443388</v>
+        <v>-23.60519294413676</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-22.70372913828248</v>
+        <v>-22.21691801256044</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-23.56677275167375</v>
+        <v>-23.10762288634429</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-22.60958347490974</v>
+        <v>-22.15153301040456</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-23.93261260986554</v>
+        <v>-23.44659555343317</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-22.98121060566869</v>
+        <v>-22.51972375970092</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-22.31400215679999</v>
+        <v>-21.85152345088017</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-19.04147795760228</v>
+        <v>-18.60950679610837</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-19.12396353032113</v>
+        <v>-18.77802653923879</v>
       </c>
     </row>
     <row r="19">
@@ -1691,76 +1691,76 @@
         <v>206</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.125474337151815</v>
+        <v>-3.028833336649846</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-8.751632255447618</v>
+        <v>-8.567646794942476</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.297993491772182</v>
+        <v>-6.932491868643559</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-11.3799947326372</v>
+        <v>-10.89537368480558</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-15.08671588567965</v>
+        <v>-14.54253735640116</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-16.35067458093145</v>
+        <v>-15.83599177113745</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-20.49882286695087</v>
+        <v>-20.0069767236801</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-21.74937091429177</v>
+        <v>-21.28368597808643</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-23.16615426814538</v>
+        <v>-22.61446020829761</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-22.49597982076317</v>
+        <v>-21.9667928996221</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-21.74743463457371</v>
+        <v>-21.2196705026042</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-21.54816947267035</v>
+        <v>-21.01790271778794</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-21.70852818741511</v>
+        <v>-21.1696607254065</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-20.0042229858562</v>
+        <v>-19.49188009018214</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-18.73277620400499</v>
+        <v>-18.24391477422582</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-18.14811599689624</v>
+        <v>-17.69180934725367</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-17.32058068032841</v>
+        <v>-16.83400573255656</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-16.94809663645184</v>
+        <v>-16.4891093310593</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-17.22428125422609</v>
+        <v>-16.76638782437552</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-15.5908894973518</v>
+        <v>-15.1049584882788</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-15.16954160942933</v>
+        <v>-14.70811797293988</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-15.73652575762928</v>
+        <v>-15.27409907836766</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-15.95401794446922</v>
+        <v>-15.52208217341911</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-16.03614690137011</v>
+        <v>-15.69020991028777</v>
       </c>
     </row>
     <row r="20">
@@ -1773,76 +1773,76 @@
         <v>206</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.162944534531</v>
+        <v>2.25987701424831</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.314139180027915</v>
+        <v>2.498677866876655</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5573103506783781</v>
+        <v>-0.1921026064084899</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3023708954475879</v>
+        <v>0.1820526559214599</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8126679244453783</v>
+        <v>1.356896303124714</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5198825981371087</v>
+        <v>1.034713758188524</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2450818147413827</v>
+        <v>0.2471405407054803</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.886227797133003</v>
+        <v>2.352580034619045</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.962139312476495</v>
+        <v>1.514334999862562</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.605564562342757</v>
+        <v>3.135345489868861</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.81119498407282</v>
+        <v>5.339620922668729</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.53873333844853</v>
+        <v>5.069567630700035</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.906081645236569</v>
+        <v>4.445427990822537</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.753895819754149</v>
+        <v>2.266525735363011</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.1328349239199511</v>
+        <v>0.6218517899989493</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.7263993003149238</v>
+        <v>-0.2699801144180682</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.8602081337619865</v>
+        <v>-0.3735867545751148</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.933788153146267</v>
+        <v>-1.474786087462789</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.719914952504055</v>
+        <v>-1.261996272671624</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-5.410918171633504</v>
+        <v>-4.925083853672938</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.409906920739921</v>
+        <v>-6.948584716222804</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.45933051004566</v>
+        <v>-7.996978968033417</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-8.189458456015494</v>
+        <v>-7.757553390911596</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-7.298282823700099</v>
+        <v>-6.952345832617759</v>
       </c>
     </row>
     <row r="21">
@@ -1855,76 +1855,76 @@
         <v>189</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1994798388045425</v>
+        <v>-0.1031014101256744</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.132760623977568</v>
+        <v>3.316962281123082</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.277327873724168</v>
+        <v>3.642017375434484</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.525275687604946</v>
+        <v>2.008636203842769</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.769861200269432</v>
+        <v>3.3129590250525</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.057120311234954</v>
+        <v>5.571222079195216</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.771388225397921</v>
+        <v>4.262880247380338</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.969104747603865</v>
+        <v>3.434607060874711</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.535096067218163</v>
+        <v>4.086446983624107</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.66664578515595</v>
+        <v>1.195324580750629</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.940412778784335</v>
+        <v>1.467704855442605</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.193084316509804</v>
+        <v>1.722882573218598</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4490671964427548</v>
+        <v>0.08922723465069282</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1431670265119607</v>
+        <v>0.3686599908113024</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.7972022266436198</v>
+        <v>-0.3088601538269273</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2060446596948751</v>
+        <v>0.2498717067998655</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.8667602750759613</v>
+        <v>-0.3806366323592627</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.4445651981140628</v>
+        <v>0.01407727098668232</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.285813772587481</v>
+        <v>-0.8282245894099063</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.5719381375252865</v>
+        <v>-0.08630026222012788</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.642683635410137</v>
+        <v>-1.181493512954411</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.719812068037527</v>
+        <v>-1.257541227228387</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.447401866326622</v>
+        <v>-1.015530660789487</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.52440908866155</v>
+        <v>-1.17847209757921</v>
       </c>
     </row>
     <row r="22">
@@ -1937,76 +1937,76 @@
         <v>196</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.089778679679021</v>
+        <v>-2.994336237717377</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.41701407328852</v>
+        <v>-2.234307050566429</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.332638539507052</v>
+        <v>-1.970006434964283</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.524272212106276</v>
+        <v>-1.042978213354445</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3390102310551555</v>
+        <v>0.2019500818466611</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.373131921998947</v>
+        <v>2.885454892470982</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.623759840520378</v>
+        <v>3.113769319281928</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.346209846395773</v>
+        <v>2.810445331656638</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.374559363112027</v>
+        <v>1.924348113657871</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.115119019413982</v>
+        <v>1.642582009731669</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.401926938373954</v>
+        <v>2.928200715352176</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.117033328269464</v>
+        <v>1.645718178243875</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.5098420822110583</v>
+        <v>1.047132550780809</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.811618706108597</v>
+        <v>2.322669487132885</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.174766500642001</v>
+        <v>2.662491355628617</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7354249968697388</v>
+        <v>1.190721031255769</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.4135868675337235</v>
+        <v>0.07191066920877631</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.55268293313717</v>
+        <v>-2.094666463557488</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-3.865963494091297</v>
+        <v>-3.408924349306737</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.190945821607158</v>
+        <v>-3.70579763138209</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-6.263356336637109</v>
+        <v>-5.802556003009521</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-6.343417351902232</v>
+        <v>-5.881408613570713</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-7.093938568630143</v>
+        <v>-6.662197990926408</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-6.664242799923592</v>
+        <v>-6.318305808841366</v>
       </c>
     </row>
     <row r="23">
@@ -2016,79 +2016,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.389742780975958</v>
+        <v>-3.48581638891946</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.063364578070171</v>
+        <v>-1.780400725157982</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.72839702351974</v>
+        <v>-2.637478899127338</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.813649061966558</v>
+        <v>-3.616473450834562</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.762175475381731</v>
+        <v>-3.49592386017526</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.579910505072014</v>
+        <v>-3.343043338849149</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.6686983203038466</v>
+        <v>-1.380051878550219</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.094181680596151</v>
+        <v>-2.863878829975619</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.056397590304499</v>
+        <v>-2.741411868153378</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.057589066781368</v>
+        <v>-2.74418226543883</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.6385369264247842</v>
+        <v>-1.294872896610421</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.057909249068381</v>
+        <v>-2.744596258024501</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.022144077159858</v>
+        <v>-2.668898917332484</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.244787589977271</v>
+        <v>-2.918383922747793</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.5957140208267617</v>
+        <v>-1.229030597943726</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.309056939036843</v>
+        <v>-3.039428129057868</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.058588729560931</v>
+        <v>-2.748689914379661</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.2414690716734782</v>
+        <v>-0.9059575448568822</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.951301952530514</v>
+        <v>-2.670898618682358</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.766661973932862</v>
+        <v>-2.458795811080869</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.309689893709944</v>
+        <v>-3.026762203337796</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.002799602897632</v>
+        <v>-2.708572552663327</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.732081944715368</v>
+        <v>-2.072157018224274</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.19650976076219</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="24">
@@ -2101,76 +2101,76 @@
         <v>224</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.334090481112163</v>
+        <v>4.429822016188645</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.310831139167234</v>
+        <v>5.495337165358436</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>7.843482383507101</v>
+        <v>8.207164490489497</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.15098938244482</v>
+        <v>7.630929023145214</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>10.34867179363594</v>
+        <v>10.88836295871978</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>12.29996921951185</v>
+        <v>12.81191740011644</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>11.98923159441095</v>
+        <v>12.47904027176482</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>8.195009129053034</v>
+        <v>8.658225361036628</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.03360384761217</v>
+        <v>6.581018347696066</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.716397144175403</v>
+        <v>6.241759495365187</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.315642255730189</v>
+        <v>7.840393835775515</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.614397671515391</v>
+        <v>7.1412093077344</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>8.164332114332929</v>
+        <v>8.700063847624385</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.177477782847419</v>
+        <v>6.686871210058719</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7.302498561932516</v>
+        <v>7.789037772732833</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>8.344356517233578</v>
+        <v>8.798940683080957</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>9.5505003803367</v>
+        <v>10.03536781604279</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>9.896501581551533</v>
+        <v>10.354248531319</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>11.00870561367277</v>
+        <v>11.46561547230445</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>11.20276332070605</v>
+        <v>11.68772160242432</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>11.56056256576822</v>
+        <v>12.02128277491633</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>12.38311672061921</v>
+        <v>12.84509638103385</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>9.987365990329437</v>
+        <v>10.41904384879974</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>9.917389853137514</v>
+        <v>10.26332684421981</v>
       </c>
     </row>
     <row r="25">
@@ -2183,76 +2183,76 @@
         <v>189</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.742609955928984</v>
+        <v>-1.650840268896403</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.131121896319527</v>
+        <v>-2.951534021695281</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-7.159171931006632</v>
+        <v>-6.804863427284715</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.377068436528496</v>
+        <v>-7.90819689007629</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-11.31650279205105</v>
+        <v>-10.79034511303708</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-12.19010039425131</v>
+        <v>-11.69139693239666</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-13.99884961644272</v>
+        <v>-13.52211994916779</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-12.19189509905831</v>
+        <v>-11.7392462706603</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-11.63788661857612</v>
+        <v>-11.10056554559501</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-9.797186887993654</v>
+        <v>-9.280345538383592</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-8.495354119175218</v>
+        <v>-7.978212968808279</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-8.237366141898022</v>
+        <v>-7.71774345816543</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.212278079343477</v>
+        <v>-5.682900238272715</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.338833635699501</v>
+        <v>-3.834293038514978</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-4.995354870951758</v>
+        <v>-4.513362980793858</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-5.983143099785337</v>
+        <v>-5.532808442944059</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-4.543601207394211</v>
+        <v>-4.062473502143227</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-4.652943840971403</v>
+        <v>-4.198338505451737</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-4.441650937534234</v>
+        <v>-3.987431827925789</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-4.786335697168411</v>
+        <v>-4.303676692777877</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-4.275673874304978</v>
+        <v>-3.816646796554323</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.772607996384203</v>
+        <v>-2.311703671323926</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.974614410962189</v>
+        <v>-1.543407192615838</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.9953085595608897</v>
+        <v>-0.6493715684784931</v>
       </c>
     </row>
     <row r="26">
@@ -2262,79 +2262,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.301984206567163</v>
+        <v>2.119348755152039</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.689680341434624</v>
+        <v>1.88056402912504</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.63684862031532</v>
+        <v>-2.882924541785123</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-10.858502748137</v>
+        <v>-6.119168951359519</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-13.84372305499741</v>
+        <v>-8.161457573640092</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-15.45053370981262</v>
+        <v>-8.006291407449012</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-12.67544031589226</v>
+        <v>-4.422413869938381</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-14.73064476726305</v>
+        <v>-7.382900287616387</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-12.04422153764713</v>
+        <v>-5.493231724939029</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-9.269455710215006</v>
+        <v>-3.65563526486828</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-8.131667693594665</v>
+        <v>-3.368017583419771</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.834438531599254</v>
+        <v>-1.025997964657719</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.389857246916705</v>
+        <v>0.4973548031038248</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.06100829497406579</v>
+        <v>2.01997417242071</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.3020598124007705</v>
+        <v>2.209625181476149</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.8955100198266308</v>
+        <v>2.77188278685675</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.656446971722723</v>
+        <v>2.668847510651098</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.447429139405699</v>
+        <v>2.534561950310746</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.560884691907283</v>
+        <v>3.640612404243228</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.750655727586206</v>
+        <v>2.962234144262823</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.908007933287571</v>
+        <v>5.932494844804836</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>8.532131487676729</v>
+        <v>8.193930214514644</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>7.01168226820333</v>
+        <v>7.208589786184582</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>6.04029847604604</v>
+        <v>6.691898272791285</v>
       </c>
     </row>
     <row r="27">
@@ -2344,243 +2344,243 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.162604922199307</v>
+        <v>0.735295503804636</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.449543193637844</v>
+        <v>0.4706670326671727</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.948201006357984</v>
+        <v>-0.2052924916364418</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.720154497752368</v>
+        <v>2.029587242112925</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.22004982124211</v>
+        <v>5.131960018029275</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>12.31290217510728</v>
+        <v>5.846331313101281</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14.11814498698156</v>
+        <v>7.321885576954543</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>15.78035854372142</v>
+        <v>10.41573097383926</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12.0072250997964</v>
+        <v>7.169001107118355</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.974758502010033</v>
+        <v>6.387633065862097</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.320353916305216</v>
+        <v>5.52388154883829</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>11.91696388853347</v>
+        <v>9.797310556028336</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.45599959410966</v>
+        <v>10.39892396604937</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.961545737661808</v>
+        <v>10.16301685958283</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>11.8919489631533</v>
+        <v>12.3361861241567</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>11.85638857657743</v>
+        <v>12.91306224569159</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>11.7357162281581</v>
+        <v>12.82464667430722</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>11.64323152314229</v>
+        <v>13.8461543829946</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>13.16229311186886</v>
+        <v>15.21694825446096</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>13.36489059159382</v>
+        <v>15.44971431943661</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>14.13443333869224</v>
+        <v>16.04270816090057</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>12.77636595100596</v>
+        <v>15.39611706751666</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>12.41446517780545</v>
+        <v>14.49689440993783</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>12.35245478820253</v>
+        <v>15.47761255850558</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 4.425</t>
+          <t>X ≈ 4.424</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-5.788299730368166</v>
+        <v>-5.083727427145377</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-8.199063045365591</v>
+        <v>-7.652447635245373</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.467185687478924</v>
+        <v>-1.330572390830206</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4716708129808111</v>
+        <v>2.739858326898613</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6628323316174018</v>
+        <v>3.055005097396105</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.8250536442727565</v>
+        <v>3.240683915163046</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.618223030215006</v>
+        <v>5.377029753933805</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.3263735861980237</v>
+        <v>2.710249576926778</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.926096805538883</v>
+        <v>2.84263522017698</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.203470371009622</v>
+        <v>2.033765325385765</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.418851871219971</v>
+        <v>1.173431998388686</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.2854278991868</v>
+        <v>2.633820590785952</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.18136157482305</v>
+        <v>-0.8738464035732747</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.00681848698008</v>
+        <v>-0.5224849302264332</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>7.013204305648209</v>
+        <v>3.877038938581336</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>7.621516677482191</v>
+        <v>5.369378379204662</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.501338856473041</v>
+        <v>5.006877216698591</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>9.504846810496048</v>
+        <v>8.189806982275812</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>9.209848053301819</v>
+        <v>8.746181126588667</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>10.46615880644596</v>
+        <v>11.08120775098337</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>12.05217477540383</v>
+        <v>13.23318435137671</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>11.99438301502874</v>
+        <v>13.15802182942142</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>10.70199718578992</v>
+        <v>11.61594202898552</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.586702022449693</v>
+        <v>10.26332684421985</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 4.456</t>
+          <t>X ≈ 4.454</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.427641505726577</v>
+        <v>6.868773344943591</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.336683349221857</v>
+        <v>4.624043340999052</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.829991453553326</v>
+        <v>4.024541508000034</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.000555153799496</v>
+        <v>-1.224459003475815</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.569550886641835</v>
+        <v>-2.836706618786948</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9395745328437499</v>
+        <v>-2.027199833326002</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.120600354699633</v>
+        <v>-1.477626746941795</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.3465396296589276</v>
+        <v>-1.764593680547755</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.108971381247251</v>
+        <v>2.407419097340643</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.375691104205998</v>
+        <v>4.326302685387674</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.002656018928803</v>
+        <v>1.899859788150678</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.463959300100377</v>
+        <v>1.63908200718285</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.09200763117716804</v>
+        <v>1.893565858291304</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1852176178422127</v>
+        <v>2.334637237375468</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.408148932290352</v>
+        <v>-1.068605579883773</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-3.799486421437614</v>
+        <v>-3.228389996438267</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.478648362634985</v>
+        <v>-2.651998299319736</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-5.527083414788102</v>
+        <v>-5.505970839855479</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-6.472912460114721</v>
+        <v>-7.332324939240316</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-5.83600872896595</v>
+        <v>-7.798010603024871</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-5.129795762824386</v>
+        <v>-7.685182995562116</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-6.365554745952615</v>
+        <v>-9.120889735204429</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-6.440427093525486</v>
+        <v>-9.557527358769626</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-8.505955094597631</v>
+        <v>-11.7604826795897</v>
       </c>
     </row>
     <row r="30">
@@ -2593,240 +2593,240 @@
         <v>147</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.182282138268675</v>
+        <v>2.243664396526356</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.929137992980124</v>
+        <v>4.427878000811376</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.089758399731444</v>
+        <v>-1.129998969139344</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.458437033349931</v>
+        <v>1.253792571126652</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.081830234272019</v>
+        <v>-2.756409393758702</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.547707984995249</v>
+        <v>-4.192842432254238</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.456031409948501</v>
+        <v>-4.616531730790797</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>-5.9871115771737</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.903141832481793</v>
+        <v>-10.89888805772692</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.995785399674745</v>
+        <v>-10.6591897194595</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.442814192886892</v>
+        <v>-12.73086554067172</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.041291487491385</v>
+        <v>-11.99456929371713</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.123637227816936</v>
+        <v>-10.71434379481376</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.024988213107015</v>
+        <v>-11.27080493949532</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-9.723947837218191</v>
+        <v>-13.99377564791101</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-9.129560915275199</v>
+        <v>-13.43247162909132</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-9.263478052252673</v>
+        <v>-13.53635204081633</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-12.76967930029152</v>
+        <v>-17.07059669019561</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-11.87351581052368</v>
+        <v>-16.17586235420631</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-12.36694210939917</v>
+        <v>-16.64154801799086</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-12.22921616852172</v>
+        <v>-16.52872041052802</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-12.30506212993079</v>
+        <v>-16.60388293248332</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-12.03058741744874</v>
+        <v>-15.67997633836139</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-10.74587545298495</v>
+        <v>-14.48157111496378</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 4.518</t>
+          <t>X ≈ 4.517</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.089311616726768</v>
+        <v>2.171658986175153</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>7.929137992980124</v>
+        <v>3.354323579042671</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>12.84032529315544</v>
+        <v>7.813915191436763</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>16.8892760356175</v>
+        <v>10.07865584977144</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>24.48999349957812</v>
+        <v>16.9459548525293</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>19.91505492377082</v>
+        <v>12.81717417281309</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>17.55580465257881</v>
+        <v>10.59352073200887</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>20.45219638242899</v>
+        <v>13.14574314574318</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>18.90638197704206</v>
+        <v>11.84510062685582</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>19.72076788830717</v>
+        <v>12.47762056020791</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>21.58212911777071</v>
+        <v>14.17842700338372</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>18.12877653971945</v>
+        <v>11.04470219176947</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>23.35482082206972</v>
+        <v>15.6440957886045</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>21.54644035832155</v>
+        <v>13.96729029859991</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>24.06290023534417</v>
+        <v>16.14227877385776</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>23.0699855699856</v>
+        <v>15.27501136410599</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>21.34876684570651</v>
+        <v>13.74255952380951</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>24.41852931648846</v>
+        <v>16.46681827579077</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>23.04711911011123</v>
+        <v>15.25270907436513</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>20.05936174547604</v>
+        <v>12.61015266228125</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>19.51681557751001</v>
+        <v>12.04270816090047</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>19.44096961610091</v>
+        <v>11.96754563894516</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>13.36623797937666</v>
+        <v>6.496894409937887</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>22.81421524996291</v>
+        <v>14.90618398707704</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 4.549</t>
+          <t>X ≈ 4.547</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>84</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-9.593228065812923</v>
+        <v>-9.495007680491554</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-8.737528673686541</v>
+        <v>-8.550438325719227</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-11.36602391319369</v>
+        <v>-10.99560861808697</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-12.07897793263647</v>
+        <v>-11.58801081689523</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-15.98619697661231</v>
+        <v>-15.43499752842313</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-12.22780221908636</v>
+        <v>-11.70663535099648</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-11.80927471250049</v>
+        <v>-11.31124117275297</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-10.89700996677744</v>
+        <v>-10.42568542568547</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-9.665046594386517</v>
+        <v>-9.107280325525139</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-10.43796227042301</v>
+        <v>-9.903331820744476</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-11.35437881873728</v>
+        <v>-10.82157299661634</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-6.871223460280483</v>
+        <v>-6.336250189182842</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-6.803909336660425</v>
+        <v>-6.260666116157438</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-8.215464403583212</v>
+        <v>-7.699376368066744</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-6.492655320211369</v>
+        <v>-6.000578368999399</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-4.707792207792245</v>
+        <v>-4.248798159703604</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-6.032185535245873</v>
+        <v>-5.543154761904766</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-6.137026239067055</v>
+        <v>-5.676038867066367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-5.921134858142729</v>
+        <v>-5.461576639920594</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-6.924765238650885</v>
+        <v>-6.437466385337792</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-5.0863590256645</v>
+        <v>-4.623958505766112</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-5.162204987073622</v>
+        <v>-4.699121027721418</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-3.697254084115393</v>
+        <v>-3.265010351966865</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-4.963562527814901</v>
+        <v>-4.617625536732561</v>
       </c>
     </row>
     <row r="33">
@@ -2836,161 +2836,161 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.41975894717411</v>
+        <v>4.08449191595718</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.5698306336727796</v>
+        <v>2.143669826016065</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.383339930509742</v>
+        <v>0.8889757241244567</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.096293949952482</v>
+        <v>1.991488779553528</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4017813921967317</v>
+        <v>5.105761147928796</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.760269751553871</v>
+        <v>1.872864245452277</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.532218435444243</v>
+        <v>1.07778223321958</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.264975334742779</v>
+        <v>5.857607552522779</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.3219663926265</v>
+        <v>11.07028222491876</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.033899201438473</v>
+        <v>8.579315475462124</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.307958843600375</v>
+        <v>8.851550490066487</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.574663985606961</v>
+        <v>13.65971429830705</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.936350403599313</v>
+        <v>10.84990692661902</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.745574557455754</v>
+        <v>13.99150337366046</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>3.572279744723666</v>
+        <v>11.61443373753809</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.166666666666664</v>
+        <v>12.17573775635779</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>5.547901044840714</v>
+        <v>13.76677259887003</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>15.32880374794573</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>15.5432659750915</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>8.876100562214901</v>
+        <v>15.75785242015053</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.333554394248871</v>
+        <v>15.19040791876979</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>5.227405402536753</v>
+        <v>13.42033014257724</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>3.986728599867284</v>
+        <v>11.96904937361828</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.3957448314925</v>
+        <v>10.11199512509153</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 4.611</t>
+          <t>X ≈ 4.61</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>70</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.502010029425151</v>
+        <v>5.028801843318</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.404195340353233</v>
+        <v>-2.359962135243059</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-12.5565001036699</v>
+        <v>-9.328941951420326</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-16.12659698025551</v>
+        <v>-14.20705843594284</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.74810173851707</v>
+        <v>-8.768330861756482</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-9.132564123848283</v>
+        <v>-8.611397255758384</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-9.904512807738627</v>
+        <v>-9.406479267991109</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>-6.854256854256839</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.855522784862721</v>
+        <v>-5.297756516001328</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-8.057009889470621</v>
+        <v>-7.522379439792068</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-10.64009310445157</v>
+        <v>-10.10728728233062</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-10.91884250789956</v>
+        <v>-10.38386923680189</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-16.32771886046994</v>
+        <v>-15.78447563996698</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-17.97736916548797</v>
+        <v>-17.4612811299715</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-21.49265532021138</v>
+        <v>-21.00057836899941</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-19.46969696969697</v>
+        <v>-19.01070292160835</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-19.60361410667444</v>
+        <v>-19.11458333333331</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-19.70845481049562</v>
+        <v>-19.24746743849492</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-20.92113485814271</v>
+        <v>-20.46157663992057</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-17.87714619103184</v>
+        <v>-15.96127590914734</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-19.84826378756929</v>
+        <v>-17.9572918390995</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-19.92410974897838</v>
+        <v>-19.46102578962622</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-21.07820646506777</v>
+        <v>-20.64596273291924</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-19.72546728971962</v>
+        <v>-19.37953029863728</v>
       </c>
     </row>
   </sheetData>
@@ -3180,575 +3180,575 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 3.728</t>
+          <t>X &gt; 3.729</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3354</v>
+        <v>3379</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0725912650458298</v>
+        <v>-0.07407881511824144</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2730172767106893</v>
+        <v>-0.2748611145348434</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3025318497016585</v>
+        <v>-0.3079335480589904</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.4360219950747179</v>
+        <v>-0.4429261281212149</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4884769873417696</v>
+        <v>-0.4962380340426833</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4628471267291303</v>
+        <v>-0.4701802155127837</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3579602798749022</v>
+        <v>-0.3655908278093705</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.411634807811744</v>
+        <v>-0.4183216554350651</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.5313485915878857</v>
+        <v>-0.5389384336711629</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.5451334049100538</v>
+        <v>-0.5521466074903003</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.521292985651435</v>
+        <v>-0.5284463119802041</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.4859420749991159</v>
+        <v>-0.4934028762677229</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6113104546113206</v>
+        <v>-0.6180196770508246</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5771653265207561</v>
+        <v>-0.5835675187081719</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.5933732166473931</v>
+        <v>-0.5991616039462855</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.5761812052710269</v>
+        <v>-0.5814144657476845</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.6330696258651614</v>
+        <v>-0.6385053652293777</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.631073858114668</v>
+        <v>-0.6359460204742504</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.6655315748526291</v>
+        <v>-0.6701210505926625</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.7291839686205392</v>
+        <v>-0.7338784174873396</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.7180880354096359</v>
+        <v>-0.7223505533007213</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.7167199992763784</v>
+        <v>-0.7210080433972763</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.7524666311312203</v>
+        <v>-0.7558528428093538</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.8107386075490766</v>
+        <v>-0.8119067413718284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 3.759</t>
+          <t>X &gt; 3.76</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3312</v>
+        <v>3337</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1222713273476472</v>
+        <v>0.1180875576036868</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2263737618117716</v>
+        <v>-0.2309271333292102</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2681284093576295</v>
+        <v>-0.278486748493421</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3943040630886401</v>
+        <v>-0.4077478269807528</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3531109592573074</v>
+        <v>-0.3688757280939399</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2994452907294303</v>
+        <v>-0.3146120737272966</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2435249520977152</v>
+        <v>-0.2583405849686997</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2342352415026809</v>
+        <v>-0.2482323985455608</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.385987811270013</v>
+        <v>-0.4017456056705981</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4202089273539684</v>
+        <v>-0.4349428536983879</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3694164127222379</v>
+        <v>-0.3844727833967099</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2999667987711376</v>
+        <v>-0.3156185862878971</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4126679168303866</v>
+        <v>-0.4277594767991957</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.4053385470997384</v>
+        <v>-0.4195806732725487</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3832648612274383</v>
+        <v>-0.3968724514859758</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4034319094560033</v>
+        <v>-0.4157851338654339</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.4894230852824606</v>
+        <v>-0.5021431419457727</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.5764475772225666</v>
+        <v>-0.5875811088509053</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.6442064805209498</v>
+        <v>-0.6547885746047015</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.7110252191207636</v>
+        <v>-0.7220404364488076</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.692909338097202</v>
+        <v>-0.7032285371319915</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.6905551322010979</v>
+        <v>-0.7009179729146027</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.7905948916125567</v>
+        <v>-0.7991768046474022</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.848655695516733</v>
+        <v>-0.8539084826348926</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 3.79</t>
+          <t>X &gt; 3.791</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3277</v>
+        <v>3295</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.147031674446815</v>
+        <v>0.104148437651908</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.08050417852927438</v>
+        <v>-0.0954373925753913</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1680395648151958</v>
+        <v>-0.1879803798194359</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3486169984538705</v>
+        <v>-0.3415122174554455</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2427272586280296</v>
+        <v>-0.2382851681621858</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2814910694368109</v>
+        <v>-0.275836046668644</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.247127084779116</v>
+        <v>-0.2389499374182904</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2044152854186763</v>
+        <v>-0.1342326923722297</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3582132899833397</v>
+        <v>-0.29128262735221</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3541840006830199</v>
+        <v>-0.2845432355007631</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3361417366703918</v>
+        <v>-0.2368433369168912</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2933810128728425</v>
+        <v>-0.2240351186974578</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5169785059339844</v>
+        <v>-0.4746493501043787</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4159801438008088</v>
+        <v>-0.3724546765459564</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3258002641293132</v>
+        <v>-0.2499730421229103</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.3524975785249751</v>
+        <v>-0.245943611889885</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.4075117924235343</v>
+        <v>-0.332027306682825</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.5552412862799727</v>
+        <v>-0.4773977626391428</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.5650801876456413</v>
+        <v>-0.4875506658946165</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.6041022584328957</v>
+        <v>-0.497715522883091</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.6104589095205171</v>
+        <v>-0.5016910420796421</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.5462506455932257</v>
+        <v>-0.437671224870364</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.6197387582779186</v>
+        <v>-0.5098670325031662</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.6165261850507235</v>
+        <v>-0.5024438039483599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 3.821</t>
+          <t>X &gt; 3.822</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3228</v>
+        <v>3253</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.03494495054834346</v>
+        <v>0.02880184331797153</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.09870083485870396</v>
+        <v>-0.1091442508373675</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1043170143677088</v>
+        <v>-0.1256955948447214</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2460551083343248</v>
+        <v>-0.2735767022777935</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1334684506469443</v>
+        <v>-0.1654667332199651</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1139918150726231</v>
+        <v>-0.1443491708564295</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.06740076723674093</v>
+        <v>-0.09673702246902849</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.07269234077940467</v>
+        <v>0.04387713167156448</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.08397087085010213</v>
+        <v>-0.1167808209497352</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.03726898879202167</v>
+        <v>-0.06905835010736183</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1004190831448639</v>
+        <v>0.06767553807005555</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1481768924531863</v>
+        <v>0.114927525394549</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.06167554904225625</v>
+        <v>-0.09382437946276667</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.10610387783683</v>
+        <v>0.0742908677518912</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.2077727657588682</v>
+        <v>0.1766135378062259</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.2027381353710211</v>
+        <v>0.1735963730865464</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.08726688250639825</v>
+        <v>0.05719580777095956</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.03003798922166112</v>
+        <v>-0.05753187543878369</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.07406667732880123</v>
+        <v>-0.1011451745167449</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1163611839597039</v>
+        <v>-0.1447927300605159</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1144352515123614</v>
+        <v>-0.1413915231991609</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.01698900594434605</v>
+        <v>-0.04474314753710473</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.095593537580271</v>
+        <v>-0.1208946848026429</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.0290608461012809</v>
+        <v>-0.0496809288248059</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 3.852</t>
+          <t>X &gt; 3.853</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3200</v>
+        <v>3218</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0979056014299573</v>
+        <v>0.08279752366355098</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.0281004830040672</v>
+        <v>0.00776273248182946</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.003929221739227273</v>
+        <v>-0.05712084261249828</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2259758622430965</v>
+        <v>-0.261942403118347</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.07841727572915858</v>
+        <v>-0.1187876338999843</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.02930566695400927</v>
+        <v>-0.06822226017300181</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.05552094153976839</v>
+        <v>-0.01146933202289802</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1371051718153424</v>
+        <v>0.04122861265717859</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.02126373131903847</v>
+        <v>-0.1225543596670917</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.06371195247088224</v>
+        <v>-0.06569627147525381</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2313665905375473</v>
+        <v>0.100521003472096</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2820114326804202</v>
+        <v>0.1512921961923439</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.08016475389138833</v>
+        <v>-0.04762654913831454</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1890749822645859</v>
+        <v>0.06305946128358642</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3285617923737547</v>
+        <v>0.2048756130272338</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.3495050253155014</v>
+        <v>0.2267428316464759</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3277859556891372</v>
+        <v>0.2032461240310113</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.2416387640520981</v>
+        <v>0.1197782190732966</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1954240899294888</v>
+        <v>0.07341737630208911</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1512112193480348</v>
+        <v>0.0270188500971642</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.1892010891088134</v>
+        <v>0.06772257523501679</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.2882575214775684</v>
+        <v>0.1663034029203843</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.2066598713449537</v>
+        <v>0.08674041357700446</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>0.1605567119282867</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 3.883</t>
+          <t>X &gt; 3.884</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3172</v>
+        <v>3197</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1306708834381425</v>
+        <v>0.1219695451813223</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.03189017713494025</v>
+        <v>0.01699610378415883</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.04251862633109482</v>
+        <v>-0.07119534749597278</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2055443486765611</v>
+        <v>-0.2424063643588497</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.08507626508733779</v>
+        <v>-0.1276059150613662</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.09987267736371308</v>
+        <v>-0.1399464670447585</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.03890334664468043</v>
+        <v>-0.07765003872627574</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.04581132736133497</v>
+        <v>0.008488243782352356</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.082964624478997</v>
+        <v>-0.1260788785702545</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.02185609160495972</v>
+        <v>-0.06364384340466955</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1448362519063764</v>
+        <v>0.101880496930626</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2297576356754618</v>
+        <v>0.1859566991817161</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.004582203216600078</v>
+        <v>-0.03812722528937229</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1792259678513517</v>
+        <v>0.1372755986132859</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.325730632094718</v>
+        <v>0.2845120863967168</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.373070325900521</v>
+        <v>0.3340708693433072</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.352346887348844</v>
+        <v>0.3111345193508086</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.2663721246837341</v>
+        <v>0.2280242880114685</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.2493314398023259</v>
+        <v>0.2112171496751927</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.2345846473992523</v>
+        <v>0.1943897310544003</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.2462244014070762</v>
+        <v>0.2078867323290865</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.3468417318029537</v>
+        <v>0.3076519221587333</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.3251522310737656</v>
+        <v>0.2885499089104613</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.4258567960306863</v>
+        <v>0.3952585659232426</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 3.914</t>
+          <t>X &gt; 3.915</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3144</v>
+        <v>3169</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1324399089867256</v>
+        <v>0.1227868057239832</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.004161306158842137</v>
+        <v>-0.01228787280851407</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1213838770844902</v>
+        <v>-0.152945534044612</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2479623405589209</v>
+        <v>-0.2891262583681495</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.18669981448474</v>
+        <v>-0.2336472266964194</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1400638979514497</v>
+        <v>-0.18475330040404</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.07172933053881536</v>
+        <v>-0.1149359086511268</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.01619075654989643</v>
+        <v>-0.02537145394289553</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1457592973214332</v>
+        <v>-0.1936646279898397</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.04561026945795277</v>
+        <v>-0.09228204739498125</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1517979313419247</v>
+        <v>0.1037210682126215</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2082623264296188</v>
+        <v>0.1595358020448074</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1040376288647948</v>
+        <v>-0.1510524593739788</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.04237900010674167</v>
+        <v>-0.003410281097195877</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.1959858831776771</v>
+        <v>0.151089346544957</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.2384248577141932</v>
+        <v>0.1960959452472011</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2186645350266048</v>
+        <v>0.173829764903445</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1328150307742177</v>
+        <v>0.09111523867041882</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.1136607685868469</v>
+        <v>0.07222478234964314</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.09707780606381533</v>
+        <v>0.05331145747281596</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1136046585698764</v>
+        <v>0.07189209172378952</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.2157503908817304</v>
+        <v>0.1731590101215161</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1913824515799618</v>
+        <v>0.1516938691537604</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.2936166797460231</v>
+        <v>0.2607347692074597</v>
       </c>
     </row>
     <row r="13">
@@ -3758,79 +3758,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3130</v>
+        <v>3155</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.05404663855027536</v>
+        <v>0.04453500883087003</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.07333964782239377</v>
+        <v>-0.09007589935114169</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.256549974459233</v>
+        <v>-0.2888196052526482</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4123112659697981</v>
+        <v>-0.4545275023095456</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.3810918033902766</v>
+        <v>-0.4291464167119088</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3033755233763031</v>
+        <v>-0.3492748839606179</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2631309928582297</v>
+        <v>-0.3072178736477369</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1736424252280457</v>
+        <v>-0.2159724014028654</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3047619399842105</v>
+        <v>-0.3540881969386831</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2325824085545918</v>
+        <v>-0.2803472529823665</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.03557512799593354</v>
+        <v>-0.08474038478371426</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.02232326458385359</v>
+        <v>-0.02751577024951501</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2864217303476053</v>
+        <v>-0.3346064945829781</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1384246704925189</v>
+        <v>-0.1852711999331333</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.01874503476972222</v>
+        <v>-0.02712704156579093</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.05866504432470521</v>
+        <v>0.01553798891965386</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.03935688471860743</v>
+        <v>-0.006423940543960782</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.04646501457725805</v>
+        <v>-0.0889732910732306</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.0667261089971376</v>
+        <v>-0.1089545784377677</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.08427537327270329</v>
+        <v>-0.1289600768314969</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.06530815399126055</v>
+        <v>-0.1078392018064349</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.03757607477638203</v>
+        <v>-0.005846822252109973</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.01181497947299448</v>
+        <v>-0.02854466302969172</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.1147883013346913</v>
+        <v>0.08164244304258261</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3102</v>
+        <v>3113</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.08715288656802755</v>
+        <v>0.1244651086240935</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.08967698450503292</v>
+        <v>0.2146562288490088</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1782923364131577</v>
+        <v>-0.06556333896705269</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4251235657776178</v>
+        <v>-0.2893164269145245</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3585745723157601</v>
+        <v>-0.291775488649364</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2818315231156632</v>
+        <v>-0.18095513320511</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2984119512369858</v>
+        <v>-0.2234578165990371</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2056327102943101</v>
+        <v>-0.1268679121028171</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3703951438159123</v>
+        <v>-0.3324660519896341</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2906427521150405</v>
+        <v>-0.2470356598112744</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.03014125854465277</v>
+        <v>0.01153183840789751</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.03078589837625145</v>
+        <v>0.07327362034094165</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3027544256115249</v>
+        <v>-0.2869450015912633</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1193082033139063</v>
+        <v>-0.1322476914279775</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.01306172070333389</v>
+        <v>0.005187165914101399</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.01632076390919224</v>
+        <v>-0.02319891648177475</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.09895022761364913</v>
+        <v>-0.1081730769230802</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2811703832111903</v>
+        <v>-0.2862619239069275</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.3358205908200915</v>
+        <v>-0.3415363210348588</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.419690575173135</v>
+        <v>-0.4289417050133082</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4279739324968403</v>
+        <v>-0.4320763613807941</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.323594285060878</v>
+        <v>-0.3277994653886367</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3521809597963852</v>
+        <v>-0.354192845773639</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.2154737371728785</v>
+        <v>-0.2083128235328857</v>
       </c>
     </row>
     <row r="15">
@@ -3922,79 +3922,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3018</v>
+        <v>3036</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.20447749817383</v>
+        <v>-0.2245489249069408</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2256239117817813</v>
+        <v>-0.322215709007402</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5600727074399572</v>
+        <v>-0.6762011691407892</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7941414173852053</v>
+        <v>-0.9563104927865211</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6507312130925484</v>
+        <v>-0.8211716380014877</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5441959702627202</v>
+        <v>-0.7116872735336557</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5729053706946061</v>
+        <v>-0.7353829224761483</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4699452714200234</v>
+        <v>-0.6288309040602655</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6405070060487077</v>
+        <v>-0.8102348603380776</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.63616556229384</v>
+        <v>-0.8010679643822485</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3431613987438666</v>
+        <v>-0.5102296990480397</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2069141722088403</v>
+        <v>-0.3744954085304499</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.5846636324361896</v>
+        <v>-0.7486089795515696</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.489163843729159</v>
+        <v>-0.6495373911102362</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.268907148990472</v>
+        <v>-0.425865725321259</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.3487452182098494</v>
+        <v>-0.5021615287042493</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.3308868339471616</v>
+        <v>-0.4882277631723113</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.5484019004427196</v>
+        <v>-0.6675857816902067</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.6768174818372543</v>
+        <v>-0.7626993908953708</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.768325164275673</v>
+        <v>-0.8578924505007066</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.7949701761823391</v>
+        <v>-0.8797757388785499</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.7519243185148241</v>
+        <v>-0.8698473827795894</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.8553322872416231</v>
+        <v>-0.9691199839658609</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.84541427447774</v>
+        <v>-0.9473827360549336</v>
       </c>
     </row>
     <row r="16">
@@ -4004,79 +4004,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2931</v>
+        <v>2942</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1201971472843724</v>
+        <v>-0.1530820400836177</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.3352581820154441</v>
+        <v>-0.3134998256228343</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8065968903520684</v>
+        <v>-0.8076556103567327</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.263838593268048</v>
+        <v>-1.347986380381933</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.242048469751943</v>
+        <v>-1.301258926599424</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.138086576980079</v>
+        <v>-1.227227371588491</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.212905907176498</v>
+        <v>-1.395568245927663</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.132843017337294</v>
+        <v>-1.309970174067544</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.377780567812941</v>
+        <v>-1.602892029794255</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.350728055854319</v>
+        <v>-1.602217058195343</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.9894719864391277</v>
+        <v>-1.243376235678454</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7732185090645416</v>
+        <v>-1.02706490369426</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.095126843377599</v>
+        <v>-1.343955103950321</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.058439744008396</v>
+        <v>-1.335652016537516</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.8463968168100351</v>
+        <v>-1.117245842495088</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.878339365069543</v>
+        <v>-1.14629614194731</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.8902036233524484</v>
+        <v>-1.162735249237031</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.145295123740432</v>
+        <v>-1.377725240394533</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.18193672657403</v>
+        <v>-1.415088686069218</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.350010634935472</v>
+        <v>-1.588276200098733</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.395639384024648</v>
+        <v>-1.660905712492642</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.383366482698143</v>
+        <v>-1.648525789626198</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.600521803208487</v>
+        <v>-1.860952296532666</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.520076638064907</v>
+        <v>-1.765662181710027</v>
       </c>
     </row>
     <row r="17">
@@ -4086,79 +4086,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2805</v>
+        <v>2830</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1047792209284282</v>
+        <v>-0.1251714179108063</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3498722315553948</v>
+        <v>-0.3874115441791304</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.8135014179960649</v>
+        <v>-0.8867913275790826</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.153145652821884</v>
+        <v>-1.249664952233566</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9383081326894711</v>
+        <v>-1.049833143258745</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.944213331884292</v>
+        <v>-1.049198218840239</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9524018428707421</v>
+        <v>-1.05232200972425</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.891692703395627</v>
+        <v>-0.9863721037298063</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.291186412015698</v>
+        <v>-1.401196134379433</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.583082965029334</v>
+        <v>-1.685529932056504</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.253496734178817</v>
+        <v>-1.358480689697075</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.015196278374731</v>
+        <v>-1.122785492959544</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.407873081249178</v>
+        <v>-1.513846585810981</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.60842727256739</v>
+        <v>-1.706753966993638</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.286543024546859</v>
+        <v>-1.382503594179305</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.417795085587478</v>
+        <v>-1.505417509346174</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.317696610230627</v>
+        <v>-1.41278565973446</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.472951430915401</v>
+        <v>-1.560584504785488</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.521033180460975</v>
+        <v>-1.607961119638411</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.598348449079957</v>
+        <v>-1.690684115619753</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.728605667911175</v>
+        <v>-1.814384270141787</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.605620258419094</v>
+        <v>-1.692664207705299</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.809292912476387</v>
+        <v>-1.887825779798192</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.650600979559201</v>
+        <v>-1.711685775669089</v>
       </c>
     </row>
     <row r="18">
@@ -4168,79 +4168,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2672</v>
+        <v>2697</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1714593583299262</v>
+        <v>-0.1970384928164819</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6348666734744342</v>
+        <v>-0.6807733578563884</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.199012437233115</v>
+        <v>-1.290468283807598</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.557503369557153</v>
+        <v>-1.679060118470844</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.241280057782348</v>
+        <v>-1.382469300637176</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.182484463731427</v>
+        <v>-1.315948689591586</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.190173966958717</v>
+        <v>-1.31720671298531</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.373200442967878</v>
+        <v>-1.491190138444104</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.869133290471723</v>
+        <v>-2.006563932773339</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.100196784481788</v>
+        <v>-2.229129716442777</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.84254056388226</v>
+        <v>-1.973391657660088</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.5788382498625</v>
+        <v>-1.71277289128696</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.898242261779792</v>
+        <v>-2.031574183963592</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.172532689510561</v>
+        <v>-2.295837043212316</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.951439356018923</v>
+        <v>-2.0701591946778</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.969696969696976</v>
+        <v>-2.079094788521452</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.746204625524761</v>
+        <v>-1.866062623274168</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.792099321324599</v>
+        <v>-1.903775244636265</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.853415129235103</v>
+        <v>-1.964167313495722</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.869245272817025</v>
+        <v>-1.987615360144311</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.866955376354355</v>
+        <v>-1.978455860263509</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.846323660721112</v>
+        <v>-1.958246982660661</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.148699757783291</v>
+        <v>-2.249266767653978</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.053311601096873</v>
+        <v>-2.130735341277258</v>
       </c>
     </row>
     <row r="19">
@@ -4250,79 +4250,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2539</v>
+        <v>2564</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.08893454512595156</v>
+        <v>-0.1216758197224976</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4418480429805314</v>
+        <v>-0.501603942778118</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9214554608127727</v>
+        <v>-1.039359193752475</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.300493033401267</v>
+        <v>-1.456063301046775</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.145733817149932</v>
+        <v>-1.323499270583412</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9371342115626646</v>
+        <v>-1.106694367631789</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.178825349656798</v>
+        <v>-1.338177945137275</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.435170436444722</v>
+        <v>-1.582939024799494</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.802496719307278</v>
+        <v>-1.976424881369965</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.809457989744807</v>
+        <v>-1.975443830792862</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.434987864863558</v>
+        <v>-1.604044308773325</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9860430455038482</v>
+        <v>-1.160266752329861</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9887832862402703</v>
+        <v>-1.165890341770023</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.030106933800475</v>
+        <v>-1.197544866235248</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.8019174866164107</v>
+        <v>-0.9633788797983698</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.8124531534425543</v>
+        <v>-0.9624914130546642</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6483902260774244</v>
+        <v>-0.8104215285881011</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.6514803507706688</v>
+        <v>-0.8038876719579662</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.7661483352316765</v>
+        <v>-0.917006768375245</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.7135036990370125</v>
+        <v>-0.8744935326453245</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7609309787573508</v>
+        <v>-0.9129376735922179</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7741687808556179</v>
+        <v>-0.9263414560330503</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.263808264842801</v>
+        <v>-1.400627171794213</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.159102579203676</v>
+        <v>-1.267205805657568</v>
       </c>
     </row>
     <row r="20">
@@ -4332,79 +4332,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2333</v>
+        <v>2358</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1791868424254162</v>
+        <v>0.1322997733593709</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2918920117850945</v>
+        <v>0.2030630748409905</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3584178121296802</v>
+        <v>-0.524522327328576</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.41048988293295</v>
+        <v>-0.6314246500483307</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.08523159481625697</v>
+        <v>-0.1686554004907634</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4238556367399298</v>
+        <v>0.1800890357279172</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5270981345106165</v>
+        <v>0.2927688523096492</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3585395071628668</v>
+        <v>0.1381610058947871</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.08387852932566631</v>
+        <v>-0.1734413031905362</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.01712730695034281</v>
+        <v>-0.2289561682912478</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3585672292471429</v>
+        <v>0.1096193875494862</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.8295583449789206</v>
+        <v>0.574539443125758</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8407355520117648</v>
+        <v>0.581682473763955</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6452757951851567</v>
+        <v>0.4006879819976064</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.781347363697364</v>
+        <v>0.5462862577131133</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.7182568961723135</v>
+        <v>0.4990181265742564</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.8237363206759838</v>
+        <v>0.5894335799859007</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.7874836247331132</v>
+        <v>0.566407349999146</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.6870772889915813</v>
+        <v>0.4676295749394583</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.6001445969136299</v>
+        <v>0.3687107849375906</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.5113252535265929</v>
+        <v>0.2922392312702087</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.5469823281093937</v>
+        <v>0.3271098035941407</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.03331269272387516</v>
+        <v>-0.1669462004902584</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.1545155649738987</v>
+        <v>-0.007180849951957669</v>
       </c>
     </row>
     <row r="21">
@@ -4414,79 +4414,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2127</v>
+        <v>2152</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.01294013668778149</v>
+        <v>-0.0713623602945006</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.09603732600323411</v>
+        <v>-0.01668443777951722</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3391550650958237</v>
+        <v>-0.5563431742196272</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4209612094124822</v>
+        <v>-0.7092946895603163</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.01477936919162204</v>
+        <v>-0.3146886955394521</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4145554232712882</v>
+        <v>0.09828016359646341</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6018837807475279</v>
+        <v>0.2971366181973991</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2105828603674453</v>
+        <v>-0.0738140498288189</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.001181048168028553</v>
+        <v>-0.3350035329437659</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.2335629020815517</v>
+        <v>-0.5510036318511879</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.07266987347691867</v>
+        <v>-0.3910220233401844</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4703246596687407</v>
+        <v>0.144253287623755</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5438567108249757</v>
+        <v>0.2118257932276748</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.5379059197450005</v>
+        <v>0.2220808364616929</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.8441558087345769</v>
+        <v>0.5390527541578578</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.8581718827620506</v>
+        <v>0.5726304117250081</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.9868263806732642</v>
+        <v>0.6816186120117251</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.051038860390456</v>
+        <v>0.7618004020982028</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.9201945441622925</v>
+        <v>0.6331978484561276</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.182316167351203</v>
+        <v>0.8754587847302346</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.278496775810979</v>
+        <v>0.985366430704957</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.419243938198683</v>
+        <v>1.123932427643993</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.829688271774323</v>
+        <v>0.5596639673660633</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.8763192641120554</v>
+        <v>0.6576444225523019</v>
       </c>
     </row>
     <row r="22">
@@ -4496,79 +4496,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1938</v>
+        <v>1963</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.005251815685838324</v>
+        <v>-0.0683064864187557</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2001137077001474</v>
+        <v>-0.3376519517237853</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6918461256928126</v>
+        <v>-0.9605663753834719</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6107644981308979</v>
+        <v>-0.9709803435863833</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2539050818268009</v>
+        <v>-0.6639629793865609</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.03820245279947443</v>
+        <v>-0.4286612638351102</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.2927835020896694</v>
+        <v>-0.08468994620177739</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.05843707600390502</v>
+        <v>-0.4116090523366935</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3460501786159043</v>
+        <v>-0.760706104330076</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3213541517657035</v>
+        <v>-0.7191422116686752</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1714689556633928</v>
+        <v>-0.5699824818679176</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3998388107817732</v>
+        <v>-0.00773903788689978</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6406898472922649</v>
+        <v>0.2236297298405248</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6043263463923481</v>
+        <v>0.2079680192573719</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.004226329212635</v>
+        <v>0.6206908283346948</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.9619577065620248</v>
+        <v>0.6037060078690999</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.167594119546642</v>
+        <v>0.783893824027075</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.196894983743057</v>
+        <v>0.8337920841053688</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.135331578148723</v>
+        <v>0.7739053577565258</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.353396695535757</v>
+        <v>0.9680581020372188</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.563379695171548</v>
+        <v>1.193994311169362</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.725374787104073</v>
+        <v>1.35322357424149</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.05175743384919</v>
+        <v>0.7113255999291681</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.110446022973875</v>
+        <v>0.8344279285659724</v>
       </c>
     </row>
     <row r="23">
@@ -4578,79 +4578,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1742</v>
+        <v>1767</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3534871641884294</v>
+        <v>0.2562559534536462</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.04931939887580938</v>
+        <v>-0.1272702882415189</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5072334316012004</v>
+        <v>-0.848596793222832</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5079817702668592</v>
+        <v>-0.9629941622199212</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2443295311673523</v>
+        <v>-0.7600121927435026</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3095121757963142</v>
+        <v>-0.7962712053382077</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.03051521142811708</v>
+        <v>-0.4394709399962267</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3289943646321092</v>
+        <v>-0.7690072748962322</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5396434450789798</v>
+        <v>-1.058538943450415</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4829779988100285</v>
+        <v>-0.9811104897640135</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4610129253713779</v>
+        <v>-0.9580095937270841</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3191441348761472</v>
+        <v>-0.1911445921379666</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.6554120987020795</v>
+        <v>0.1322847649824155</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4684886296848916</v>
+        <v>-0.02659988549848435</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.8725237611298908</v>
+        <v>0.3942092757882278</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.9874458874458867</v>
+        <v>0.5385928530395674</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.345499672628016</v>
+        <v>0.8628687523487315</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.61877631078584</v>
+        <v>1.158623932063442</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.698049048963334</v>
+        <v>1.237875149824653</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.977214797349767</v>
+        <v>1.486493712535342</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.443999822745887</v>
+        <v>1.970068935718913</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.633229700562879</v>
+        <v>2.155706827671708</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.968265135620683</v>
+        <v>1.529215030493802</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.985210092599544</v>
+        <v>1.627826803796218</v>
       </c>
     </row>
     <row r="24">
@@ -4660,79 +4660,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1483</v>
+        <v>1515</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.007227255757932</v>
+        <v>0.8786996698087819</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.2436451912082518</v>
+        <v>0.1477058636416118</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2939621097489393</v>
+        <v>-0.5510401657060484</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1053062284258388</v>
+        <v>-0.5216233498562985</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1954021610454078</v>
+        <v>-0.3049298559825786</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.08700378326128089</v>
+        <v>-0.3726497019423292</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1526300494042374</v>
+        <v>-0.2830178729892339</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.02071148207332385</v>
+        <v>-0.420553392467184</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2747484190416145</v>
+        <v>-0.7786155262720982</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2079784933450384</v>
+        <v>-0.687847065691372</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4300090708381106</v>
+        <v>-0.901976885920746</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7342869713168909</v>
+        <v>0.2335879621877126</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.12303654209267</v>
+        <v>0.5982242289714321</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.9423514354114602</v>
+        <v>0.4544097365390272</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.128945598976664</v>
+        <v>0.6642135320129583</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.563166880068295</v>
+        <v>1.133748818378542</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.940010054399387</v>
+        <v>1.4636032632501</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.943660703272002</v>
+        <v>1.502039464858122</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.335393559676014</v>
+        <v>1.888047420229782</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.631067854505673</v>
+        <v>2.142739890721018</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.274212659267846</v>
+        <v>2.801225006373883</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.442893618024968</v>
+        <v>2.964814684994764</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.614515906899875</v>
+        <v>2.12825513364691</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.715530687353876</v>
+        <v>2.270634717864361</v>
       </c>
     </row>
     <row r="25">
@@ -4742,79 +4742,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1259</v>
+        <v>1291</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.415315133057895</v>
+        <v>0.2625483099411596</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6579033809464931</v>
+        <v>-0.7801558029614597</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.741767960812773</v>
+        <v>-2.070666690096289</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.396338966182014</v>
+        <v>-1.936163808068805</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.611057249359902</v>
+        <v>-2.247065867209024</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.085914610479882</v>
+        <v>-2.660289539944785</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.953326063448422</v>
+        <v>-2.497348643264147</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.482444140446873</v>
+        <v>-1.995802378357851</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.397124040749674</v>
+        <v>-2.055577561724363</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.262037383579028</v>
+        <v>-1.890195531746116</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.808107480013099</v>
+        <v>-2.418856081629471</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3118963462720359</v>
+        <v>-0.9649458731356475</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1297436073765965</v>
+        <v>-0.8075171146213478</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.01092307812341886</v>
+        <v>-0.6269778467827507</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.0305533323348044</v>
+        <v>-0.5720069404279897</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.3566645141230751</v>
+        <v>-0.1962302503227278</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.5859593530411971</v>
+        <v>-0.02367424242424221</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.5286993397020012</v>
+        <v>-0.0338976620878455</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.7922466970109809</v>
+        <v>0.2262540479100892</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.106000511829826</v>
+        <v>0.486600538729121</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.799913708468736</v>
+        <v>1.201462852885506</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.852258212956571</v>
+        <v>1.250497798927555</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.302745915884607</v>
+        <v>0.6897294386862356</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.434183226563135</v>
+        <v>0.8838314364517998</v>
       </c>
     </row>
     <row r="26">
@@ -4824,79 +4824,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1070</v>
+        <v>1102</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.7964813403649202</v>
+        <v>0.590706605222735</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2210451572030294</v>
+        <v>-0.4077506456650042</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.784862025890682</v>
+        <v>-1.258721877638379</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1632942279619414</v>
+        <v>-0.9119221996301334</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1032691128537735</v>
+        <v>-0.7818392088954909</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3011565608230597</v>
+        <v>-1.111397255758384</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.174341180958983</v>
+        <v>-0.6065303339939092</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4092252344854188</v>
+        <v>-0.324739859623584</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.411758321128076</v>
+        <v>-0.5043046679389178</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2455731363596385</v>
+        <v>-0.6227378627311566</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6269022325349241</v>
+        <v>-1.465391061959053</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.088023084917985</v>
+        <v>0.1932018070554875</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.9446479956156821</v>
+        <v>0.0286420599431878</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.7792445911257815</v>
+        <v>-0.07690291825516482</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.9183072112330777</v>
+        <v>0.1039606563316795</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.47649969078541</v>
+        <v>0.7190268081214057</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.492021919323705</v>
+        <v>0.6690054854223035</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.443961546381701</v>
+        <v>0.6803303954400803</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.716738896010092</v>
+        <v>0.948927941315695</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.146796346877174</v>
+        <v>1.308163512190831</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.873078244117551</v>
+        <v>2.062100533234066</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.669173833111152</v>
+        <v>1.861437978489747</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.881644141841655</v>
+        <v>1.072726556032954</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.863317757009341</v>
+        <v>1.1467854908364</v>
       </c>
     </row>
     <row r="27">
@@ -4906,79 +4906,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>959</v>
+        <v>990</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7379716238389094</v>
+        <v>0.417769311493366</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.051057143178312</v>
+        <v>-0.6666306896816607</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1075205118331866</v>
+        <v>-1.07497369745208</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.074628760296072</v>
+        <v>-0.3228195368082183</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.717571647401719</v>
+        <v>0.0530267071160111</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.452316706682517</v>
+        <v>-0.331368826476222</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.661646442846866</v>
+        <v>-0.17483441881636</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.161598091830655</v>
+        <v>0.4737590978867132</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.85348278861926</v>
+        <v>0.06009920113583433</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.346895557600291</v>
+        <v>-0.2796221970348398</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2417411107159992</v>
+        <v>-1.250144425187749</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.773521770458551</v>
+        <v>0.3311314781987988</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.33060219991296</v>
+        <v>-0.0243840281719514</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.8623772593977748</v>
+        <v>-0.3141253769982981</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.9896351166245054</v>
+        <v>-0.1342559364119325</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.543746670427133</v>
+        <v>0.4867845155775967</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.472990448190977</v>
+        <v>0.4427607310529851</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.327814619556193</v>
+        <v>0.4705587447880433</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.503287192835344</v>
+        <v>0.6444141434895485</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.961156731383227</v>
+        <v>1.12103632957259</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.521798582493069</v>
+        <v>1.624237742430104</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.990562467462802</v>
+        <v>1.145034816434411</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.287864963503651</v>
+        <v>0.3785682916117707</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.379850749904989</v>
+        <v>0.5194596003526115</v>
       </c>
     </row>
     <row r="28">
@@ -4988,653 +4988,653 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4654330798047468</v>
+        <v>0.3495888407516787</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5294328597866169</v>
+        <v>-0.910835722087846</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6920933240088942</v>
+        <v>-1.261715060664031</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.005384859043395807</v>
+        <v>-0.8279375568219578</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.09101060544963957</v>
+        <v>-1.03754179522732</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6253605133639724</v>
+        <v>-1.657868856446846</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7213358873354139</v>
+        <v>-1.7845595712825</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4437299946180104</v>
+        <v>-1.661020139281014</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.08897226221462518</v>
+        <v>-1.466352128369607</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3036521361128734</v>
+        <v>-1.711241425264241</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.303732643396721</v>
+        <v>-2.704689879733216</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1669628086514265</v>
+        <v>-1.70148366121245</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6064303450637922</v>
+        <v>-2.26251764656304</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8783332320962174</v>
+        <v>-2.56381849528259</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.096024923580991</v>
+        <v>-2.811958219356121</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.4291065637929137</v>
+        <v>-2.181434628925409</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4903136140636022</v>
+        <v>-2.21592643467644</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.6455694837385408</v>
+        <v>-2.401501668323789</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7271313308058609</v>
+        <v>-2.48465759813007</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.2204271375266345</v>
+        <v>-1.955673668250967</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.3002510639158444</v>
+        <v>-1.471752838223061</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.07280863373676283</v>
+        <v>-1.915013519687548</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.84070203401496</v>
+        <v>-2.652974126433712</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.7192561095953991</v>
+        <v>-2.692413734220111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 4.44</t>
+          <t>X &gt; 4.439</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.384192010198703</v>
+        <v>1.7604035749197</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.823749128970576</v>
+        <v>0.8396910188865903</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.15935546932851</v>
+        <v>-1.243835568441604</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.151754212959915</v>
+        <v>-1.754351325701492</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.08443469689727578</v>
+        <v>-2.100212394857508</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.070373948093419</v>
+        <v>-2.929826917699494</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.439155100674746</v>
+        <v>-3.64413763408983</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6800117750956645</v>
+        <v>-2.796063898667271</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.7072320898208133</v>
+        <v>-2.585223650094228</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.07288290534364</v>
+        <v>-2.683669762372737</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.139071074017764</v>
+        <v>-3.711682886726223</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.533037230374525</v>
+        <v>-2.827188629273849</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.768593775029082</v>
+        <v>-2.623099978591299</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.377186600449178</v>
+        <v>-3.093871105683576</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-3.584083891639963</v>
+        <v>-4.548823014616552</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-2.899184149184151</v>
+        <v>-4.14207850120647</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-2.942297894796432</v>
+        <v>-4.091399407521898</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.759901755833248</v>
+        <v>-5.151640545140999</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-3.775977278202532</v>
+        <v>-5.400856834223973</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.49926600670004</v>
+        <v>-5.340829894574568</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.305452802108881</v>
+        <v>-5.290036374316976</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-3.775242435062538</v>
+        <v>-5.828877412501008</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-4.382212021909638</v>
+        <v>-6.358040454270544</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-3.881311445563782</v>
+        <v>-6.056500932331254</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 4.471</t>
+          <t>X &gt; 4.47</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.125887166486891</v>
+        <v>0.2585428625326713</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.196789881321664</v>
+        <v>-0.2729085638144682</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.255427950670786</v>
+        <v>-2.792738428915442</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.06001559580939642</v>
+        <v>-1.910139668435839</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.5355841496312834</v>
+        <v>-1.883683093022256</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.103007473601963</v>
+        <v>-3.195199280505292</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.077795914084597</v>
+        <v>-4.281091834911358</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9361290626916343</v>
+        <v>-3.099316142794407</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.908840663738395</v>
+        <v>-4.053060617840075</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.681756339774886</v>
+        <v>-4.744601662014311</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.421895480574413</v>
+        <v>-5.361476433140048</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.280766587876371</v>
+        <v>-4.140272196392125</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.186890115178741</v>
+        <v>-3.95099973463477</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.016488261402202</v>
+        <v>-4.689852558542931</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-3.87747131557505</v>
+        <v>-5.57200694042799</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.674565123855182</v>
+        <v>-4.410702921608326</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-2.808482260832655</v>
+        <v>-4.514583333333334</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.319002477838424</v>
+        <v>-5.047467438494934</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-3.103111096914098</v>
+        <v>-4.83300521134916</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-2.916265286946071</v>
+        <v>-4.618418766290176</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-2.850292185135231</v>
+        <v>-4.585863267670909</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-3.128977903136615</v>
+        <v>-4.861025789626197</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.868701973616027</v>
+        <v>-5.417391304347817</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-2.727495687285554</v>
+        <v>-4.379530298637277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 4.502</t>
+          <t>X &gt; 4.501</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1726390209464199</v>
+        <v>-0.5681224788188075</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.663485183458086</v>
+        <v>-2.23045990942353</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.101504232489077</v>
+        <v>-3.48515401131511</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.658388887769966</v>
+        <v>-3.227697853182825</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9710579730340072</v>
+        <v>-1.520253160420964</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.229178492138928</v>
+        <v>-2.779750149323732</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.579161858110211</v>
+        <v>-4.141404399516794</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.256217233499122</v>
+        <v>-1.896749772103881</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.6366953695034923</v>
+        <v>-1.202248624459436</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.698628386580445</v>
+        <v>-2.281586238658946</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.713586085458985</v>
+        <v>-2.292637343034777</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2582314426642043</v>
+        <v>-0.8695025836250565</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5143414863989406</v>
+        <v>-1.134536344135313</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.313455044926457</v>
+        <v>-1.949342643528773</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.393563660426089</v>
+        <v>-2.064924787453478</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.06787528463829062</v>
+        <v>-0.6537624116933145</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.06604185233918258</v>
+        <v>-0.7576428234183226</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.6961694669610168</v>
+        <v>-0.04066857163940796</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.623043506844887</v>
+        <v>-0.1094924634738135</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.098906657853369</v>
+        <v>0.3883801005653496</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.134395171968272</v>
+        <v>0.3875078371449518</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.7695318695187083</v>
+        <v>0.02905919620948794</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.4010801232015524</v>
+        <v>-1.143736913412972</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.6791569877370165</v>
+        <v>-0.1727314317817559</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 4.533</t>
+          <t>X &gt; 4.532</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>283</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.344027325446099</v>
+        <v>-1.24580694012473</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.798945466552098</v>
+        <v>-3.611855118584785</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-6.650392077420541</v>
+        <v>-6.279976782313817</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-7.009989206403922</v>
+        <v>-6.519022090662681</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.63906589803247</v>
+        <v>-6.08786644984329</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.158813492853817</v>
+        <v>-6.637646624763931</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.284119067203527</v>
+        <v>-7.786085527456009</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-6.088832278741066</v>
+        <v>-5.617507737649092</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.987274425448263</v>
+        <v>-4.429508156586884</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.466903882403486</v>
+        <v>-5.932273432724955</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.899558021160296</v>
+        <v>-6.366752199039354</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.351452300933367</v>
+        <v>-3.816479029835726</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.827971258248851</v>
+        <v>-5.284728037745865</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-6.402407025154808</v>
+        <v>-5.88631898963834</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-7.060550322735367</v>
+        <v>-6.568473371523396</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.052735838954924</v>
+        <v>-4.593741790866282</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-4.83329608547303</v>
+        <v>-4.344265312131924</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-4.584779898834846</v>
+        <v>-4.123792526834158</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-4.36888851791052</v>
+        <v>-3.909330299688385</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-3.121972036564401</v>
+        <v>-2.634673183251309</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-2.957804423611698</v>
+        <v>-2.49540390371331</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-3.387007275480165</v>
+        <v>-2.923923316127961</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-3.465889453457478</v>
+        <v>-3.03364572130895</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-4.248435487599487</v>
+        <v>-3.902498496517147</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 4.564</t>
+          <t>X &gt; 4.563</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>199</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.138047358929839</v>
+        <v>2.236267744251208</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.714317379118462</v>
+        <v>-1.527227031151149</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.659874116591666</v>
+        <v>-4.289458821484942</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-4.870315573220338</v>
+        <v>-4.379348457479097</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.693543231697262</v>
+        <v>-2.142343783508082</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.019139859670233</v>
+        <v>-4.497972991580347</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-6.796113669188728</v>
+        <v>-6.29808012944121</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.059249737057378</v>
+        <v>-3.587925195965404</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.01273742951453</v>
+        <v>-2.454971160653152</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.790678231179164</v>
+        <v>-4.256047781500634</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.019131151831317</v>
+        <v>-4.486325329710375</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.287830304023018</v>
+        <v>-2.752857032925377</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-5.416017496507287</v>
+        <v>-4.8727742760043</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.637096372953877</v>
+        <v>-5.121008337437409</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-7.30026479616258</v>
+        <v>-6.808187844950609</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-5.198340185777369</v>
+        <v>-4.739346137688727</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-4.327232197126705</v>
+        <v>-3.838201423785598</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-3.929560338133818</v>
+        <v>-3.468572966133131</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-3.713668957209492</v>
+        <v>-3.254110738987357</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-1.516772895985184</v>
+        <v>-1.029474042672092</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-2.059319063951214</v>
+        <v>-1.596918544052826</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-2.637677588174377</v>
+        <v>-2.174593628822173</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-3.368228001320468</v>
+        <v>-2.935984269171939</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-3.946572817357819</v>
+        <v>-3.600635826275479</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 4.595</t>
+          <t>X &gt; 4.594</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.998250630928929</v>
+        <v>1.457373271889409</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.847804362909606</v>
+        <v>-3.07424784952876</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-5.789582810436833</v>
+        <v>-6.471799094277479</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-5.750657130631453</v>
+        <v>-7.064201293085702</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-3.830808505434369</v>
+        <v>-5.196902290327898</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-5.147601717833233</v>
+        <v>-7.182825827186953</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.423309800219819</v>
+        <v>-9.406479267991102</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-5.445882147228531</v>
+        <v>-7.568542568542568</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-6.156274664561955</v>
+        <v>-8.154899373144183</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-7.68107003984656</v>
+        <v>-9.665236582649229</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-8.158890096932758</v>
+        <v>-10.10728728233062</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-7.685759801132633</v>
+        <v>-9.669583522516191</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-9.560801567236872</v>
+        <v>-11.49876135425269</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.28563984217971</v>
+        <v>-13.17556684425722</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-12.69566283900838</v>
+        <v>-14.57200694042799</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-9.84563681932103</v>
+        <v>-11.86784577875119</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-9.227674257050381</v>
+        <v>-11.25744047619047</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-9.332514960871563</v>
+        <v>-11.39032458135208</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-9.116623579947237</v>
+        <v>-11.1758623542063</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-6.674138672234854</v>
+        <v>-8.104133052004471</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-7.216684840200884</v>
+        <v>-8.671577553385205</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-6.540651102361856</v>
+        <v>-8.74674007534049</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-7.018056089127931</v>
+        <v>-9.217391304347821</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-7.093888342351207</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 4.626</t>
+          <t>X &gt; 4.625</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.3274068548220015</v>
+        <v>-2.114055299539174</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.00736994352781295</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.729214182044366</v>
+        <v>-3.614656237134625</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.778164924506392</v>
+        <v>0.0786558497714438</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>3.855072864657529</v>
+        <v>-1.625473718899322</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.7198657111498505</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-4.666417569643372</v>
+        <v>-9.406479267991102</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.357327427094866</v>
+        <v>-8.282828282828291</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-6.49044341978334</v>
+        <v>-11.01204223028704</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-7.26335909581983</v>
+        <v>-11.80809372550637</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.401997866356311</v>
+        <v>-10.10728728233062</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-4.093445682502725</v>
+        <v>-8.955297808230483</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-7.213047068538401</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-3.850385038503845</v>
+        <v>-8.889852558542934</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-2.921226748782821</v>
+        <v>-8.143435511856566</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.8477633477633475</v>
+        <v>-4.724988635894043</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.301147798087463</v>
+        <v>-3.40029761904762</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.196307094266281</v>
+        <v>-3.533181724209221</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>3.999500062492189</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>5.773647459761804</v>
+        <v>-0.2469901948616027</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>8.329858504989851</v>
+        <v>1.967545638945232</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>8.604333217471904</v>
+        <v>2.21118012422361</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
   </sheetData>
@@ -5824,575 +5824,575 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 3.728</t>
+          <t>X &lt; 3.729</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.089311616726768</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.10374116758329</v>
+        <v>13.35432357904267</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.84032529315548</v>
+        <v>14.95677233429395</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>23.23848238482385</v>
+        <v>21.50722727834288</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>22.90269191227658</v>
+        <v>24.08881199538639</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>21.50235651107238</v>
+        <v>22.81717417281305</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19.14310623988043</v>
+        <v>17.73637787486605</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>22.03949796973053</v>
+        <v>20.28860028860029</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>25.2555883262484</v>
+        <v>26.13081491257011</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>26.06997423751351</v>
+        <v>26.7633348459222</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>24.75673229237383</v>
+        <v>25.60699843195511</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>22.89068130162426</v>
+        <v>23.90184504891238</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>28.11672558397449</v>
+        <v>29.92981007431874</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>27.8956467075279</v>
+        <v>28.2530045843142</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>27.23750340994734</v>
+        <v>28.99942163100058</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>26.24458874458874</v>
+        <v>28.13215422124881</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>29.28527478221444</v>
+        <v>30.88541666666666</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>29.18043407839326</v>
+        <v>30.75253256150506</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>30.98362704661918</v>
+        <v>32.39556621722227</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>34.34507603119037</v>
+        <v>35.4672955194241</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>33.80252986322434</v>
+        <v>34.89985101804336</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>33.72668390181524</v>
+        <v>34.82468849608808</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>35.58846020159888</v>
+        <v>36.4968944099379</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>38.68723112297878</v>
+        <v>39.1918982727913</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 3.759</t>
+          <t>X &lt; 3.76</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>112</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>6.738661802503927</v>
+        <v>6.92575215047124</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.979214182044366</v>
+        <v>8.34962947715109</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.73054587688735</v>
+        <v>12.22151299262859</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.50189826148292</v>
+        <v>11.0530977096721</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.903150161866023</v>
+        <v>9.424317029955908</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.238344335118533</v>
+        <v>7.736377874866051</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.960132890365458</v>
+        <v>7.431457431457432</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.46590578656587</v>
+        <v>12.02367205542725</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.47870439624367</v>
+        <v>13.0133348459222</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>10.9670497526913</v>
+        <v>11.49985557481224</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.902586063529014</v>
+        <v>9.437559334626656</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.24370971095862</v>
+        <v>12.78695293146161</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.02263083451203</v>
+        <v>12.5387188700285</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>11.36448753693147</v>
+        <v>11.85656448814344</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>11.95887445887446</v>
+        <v>12.4178685069631</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>14.50352875046842</v>
+        <v>14.99255952380953</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>17.07725947521867</v>
+        <v>17.53824684721936</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>19.07886514185727</v>
+        <v>19.53842336007941</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>21.05142523753959</v>
+        <v>21.53872409085268</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>20.50887906957356</v>
+        <v>20.97127958947195</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>20.43303310816446</v>
+        <v>20.89611706751666</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>23.38607924921794</v>
+        <v>23.81832298136647</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>25.09596128170895</v>
+        <v>25.44189827279128</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 3.79</t>
+          <t>X &lt; 3.791</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.300711059010197</v>
+        <v>-2.243925429409302</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.806689013388279</v>
+        <v>2.055622280341375</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.770030508574983</v>
+        <v>4.047681425203045</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.818981251037009</v>
+        <v>7.351383122498717</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.442374451959118</v>
+        <v>5.127773034347427</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.309612746900036</v>
+        <v>5.93405728969617</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.537664063009686</v>
+        <v>5.138975277463452</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.579180509413071</v>
+        <v>2.886002886002878</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.022028235545463</v>
+        <v>6.260685042440237</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.929384668352498</v>
+        <v>6.113984196571543</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>7.523172201670896</v>
+        <v>5.087517912474581</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.56415068937936</v>
+        <v>4.810935958003284</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>11.56343760211508</v>
+        <v>10.18955033405901</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.301542399137873</v>
+        <v>7.99326432457395</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.282854883870236</v>
+        <v>5.363057994636939</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.877241805813227</v>
+        <v>5.275011364105964</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>9.103868886522832</v>
+        <v>7.119182900432897</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>12.40038872691935</v>
+        <v>10.23305204202454</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>12.61628010784367</v>
+        <v>10.44751426917031</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>13.48339802665524</v>
+        <v>10.6621007142293</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>13.62112396753275</v>
+        <v>10.74400686219921</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>12.18473378843657</v>
+        <v>9.37014304154264</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>13.8197527186057</v>
+        <v>10.91247882552231</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>13.74392046538242</v>
+        <v>10.75033983123284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 3.821</t>
+          <t>X &lt; 3.822</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>196</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5796226236360482</v>
+        <v>-0.4814022383146792</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.636620986177405</v>
+        <v>1.823711334144718</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.729214182044366</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.077484652397551</v>
+        <v>4.568451768138793</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.211081934952318</v>
+        <v>2.762281383141499</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.88784403941704</v>
+        <v>2.409010907506925</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.115895355526689</v>
+        <v>1.613928895274206</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.203132415757004</v>
+        <v>-0.7318078746650301</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.389375174320975</v>
+        <v>1.947141443182353</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.6164594982844847</v>
+        <v>1.151089947963015</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.660501267716867</v>
+        <v>-1.127695445595926</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.449454752797507</v>
+        <v>-1.914481481699866</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.019219915040253</v>
+        <v>1.56246313554324</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.752879369569605</v>
+        <v>-1.236791334053137</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-3.431430830415472</v>
+        <v>-2.939353879203502</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-3.347247990105139</v>
+        <v>-2.888253942016497</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.440348800551995</v>
+        <v>-0.9513180272108883</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.4956268221574405</v>
+        <v>0.9566141941581279</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.22172228471441</v>
+        <v>1.681280502936545</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.918772176315095</v>
+        <v>2.406071029628187</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.886430089981715</v>
+        <v>2.348830609880103</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.2799718836746621</v>
+        <v>0.7430558430268661</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.574854759422017</v>
+        <v>2.007098491570545</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.4786143429334402</v>
+        <v>0.82455133401578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 3.852</t>
+          <t>X &lt; 3.853</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.408704256289106</v>
+        <v>-1.161674347158211</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.1088798841607854</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.05650010366991154</v>
+        <v>0.8009281784497944</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.248403019744487</v>
+        <v>3.671729442845034</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.126898261482921</v>
+        <v>1.664569571143971</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.4210073047231617</v>
+        <v>0.9557023113411915</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7973699505957583</v>
+        <v>0.1606202991084729</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.968438538205973</v>
+        <v>-0.5772005772005784</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3051915008515778</v>
+        <v>1.71523049698569</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>0.9191790017663521</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.318664533022989</v>
+        <v>-1.405988581031913</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.043842507899555</v>
+        <v>-2.115470968403642</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.14914743189852</v>
+        <v>0.6657408102494813</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.709512022630832</v>
+        <v>-0.8811945498849241</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-4.706941034497099</v>
+        <v>-2.862050230471276</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-5.005411255411261</v>
+        <v>-3.166547077452485</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-4.69289982096015</v>
+        <v>-2.837527056277054</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.458454810495624</v>
+        <v>-1.671709862737359</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.796134858142729</v>
+        <v>-1.024347202691153</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-2.162860476746133</v>
+        <v>-0.3768603247317373</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.705406644712163</v>
+        <v>-0.9443048261124716</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-4.120538320406972</v>
+        <v>-2.31816864676906</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-2.95320646506778</v>
+        <v>-1.208733295689811</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.921895861148194</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 3.883</t>
+          <t>X &lt; 3.884</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>252</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.656720129304979</v>
+        <v>-1.55849974398361</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.2171049923858988</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5387379915681834</v>
+        <v>0.9091532866749077</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.603561749903221</v>
+        <v>3.094528865644463</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.077295086879751</v>
+        <v>1.628494535068931</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.26426127297713</v>
+        <v>1.785428141067015</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.4923125890867794</v>
+        <v>0.9903461288342967</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5795496493170873</v>
+        <v>-0.1082251082251133</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.049239119899205</v>
+        <v>1.607005388760584</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2763234438627151</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.830569294927741</v>
+        <v>-1.2977634728068</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.902969492026529</v>
+        <v>-2.367996220928887</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.05787759062868503</v>
+        <v>0.4853656298743019</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.263083451202263</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.111702939259004</v>
+        <v>-3.619625988047034</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-4.707792207792203</v>
+        <v>-4.248798159703561</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-4.444883947944277</v>
+        <v>-3.95585317460317</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.359248461289276</v>
+        <v>-2.898261089288589</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.14335708036495</v>
+        <v>-2.683798862142815</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.956511270396923</v>
+        <v>-2.469212417083831</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-3.102232041537555</v>
+        <v>-2.639831521639167</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-4.368554193422845</v>
+        <v>-3.905470234070641</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-4.094079480940792</v>
+        <v>-3.661835748792264</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-5.360387924640264</v>
+        <v>-5.014450933557924</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 3.914</t>
+          <t>X &lt; 3.915</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>280</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.497989970574821</v>
+        <v>-1.399769585253452</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.04705248321035782</v>
+        <v>0.1400378647569553</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.372071324901512</v>
+        <v>1.742486620008236</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.801974448315917</v>
+        <v>3.292941564057159</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.10904111862579</v>
+        <v>2.66024056681497</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.581721590437454</v>
+        <v>2.102888458527339</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.8097729065471029</v>
+        <v>1.30780644629462</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.6444772151373</v>
+        <v>2.202243483998679</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5144186819579559</v>
+        <v>1.049049131636487</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.711521675880128</v>
+        <v>-1.178715853759186</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.347413936470979</v>
+        <v>-1.812440665373337</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.172281139530043</v>
+        <v>1.715524360033029</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4773691654879713</v>
+        <v>0.03871887002849661</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.206941034497099</v>
+        <v>-1.714864083285129</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.683982683982684</v>
+        <v>-2.224988635894043</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.494169096209909</v>
+        <v>-1.033181724209221</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.278277715285583</v>
+        <v>-0.8187194970634479</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.091431905317556</v>
+        <v>-0.6041330520044639</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.276835216140725</v>
+        <v>-0.814434696242337</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.42410974897841</v>
+        <v>-1.961025789626206</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.149635036496356</v>
+        <v>-1.717391304347828</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.296895861148194</v>
+        <v>-2.950958870065854</v>
       </c>
     </row>
     <row r="13">
@@ -6405,76 +6405,76 @@
         <v>294</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5796226236360482</v>
+        <v>-0.4814022383146792</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.786280850122985</v>
+        <v>0.9733711980902982</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.749622345309675</v>
+        <v>3.120037640416399</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.417620706819321</v>
+        <v>4.908587822560563</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.081830234272047</v>
+        <v>4.633029682461228</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.248388257104118</v>
+        <v>3.769555125194003</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.816575627635537</v>
+        <v>3.314609167383054</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.858092074038922</v>
+        <v>2.329416615130896</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.260123473640704</v>
+        <v>3.817889742502082</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.487207797604214</v>
+        <v>3.021838247282744</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3803150588137498</v>
+        <v>0.9131208809346916</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.238570399056016</v>
+        <v>0.2964028720416252</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.060036241570863</v>
+        <v>3.60327946207385</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.478413147437195</v>
+        <v>1.994501182953663</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2001383134086652</v>
+        <v>0.2919386378033053</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.6261595547309824</v>
+        <v>-0.1671655066423412</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.4199406372866861</v>
+        <v>0.06909013605442027</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.4956268221574405</v>
+        <v>0.9566141941581279</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.7115182030817664</v>
+        <v>1.171076421303901</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.8983640130497932</v>
+        <v>1.385662866362885</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.6959538995055325</v>
+        <v>1.158354419403921</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.400300225168877</v>
+        <v>0.06278373418332706</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.1258255126868235</v>
+        <v>0.3064182194617047</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.222065929175407</v>
+        <v>-0.8761289380930677</v>
       </c>
     </row>
     <row r="14">
@@ -6484,79 +6484,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8458160575313443</v>
+        <v>-1.161674347158211</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.8700338496699871</v>
+        <v>-2.002819278100176</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.729214182044366</v>
+        <v>0.6115342390558567</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.121850224713434</v>
+        <v>2.697703468819064</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.475500745954974</v>
+        <v>2.71976437633878</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.730789913418818</v>
+        <v>1.686221791860667</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.890518248162003</v>
+        <v>2.081615970104146</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.991188790986563</v>
+        <v>1.181457431457432</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.585471003957181</v>
+        <v>3.095100626855817</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.812555327920691</v>
+        <v>2.29904913163648</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2915839141819916</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2977244954771905</v>
+        <v>-0.6814882844209578</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.926939524623208</v>
+        <v>2.667905312413986</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.153065617120717</v>
+        <v>1.229195060504679</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.1261956928821988</v>
+        <v>-0.04819741661846422</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1576322228496139</v>
+        <v>0.2154875545821469</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.9553921045056768</v>
+        <v>1.004464285714278</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.713905437951581</v>
+        <v>2.657294466266968</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.240355825087086</v>
+        <v>3.169375741031793</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>4.04831964747747</v>
+        <v>3.979200281328865</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.126891491933804</v>
+        <v>4.006993875186225</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.119368511891167</v>
+        <v>3.038974210373802</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>3.393843224373221</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.075774946305224</v>
+        <v>1.929993510886526</v>
       </c>
     </row>
     <row r="15">
@@ -6566,79 +6566,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.531566679671478</v>
+        <v>1.663184409903927</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.689400718760091</v>
+        <v>2.385800576621364</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.192268369236494</v>
+        <v>5.005198484415025</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.942368536985867</v>
+        <v>7.076234542265389</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.867661808280957</v>
+        <v>6.074284150350074</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.069406319501489</v>
+        <v>5.262694753926851</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.282679310487985</v>
+        <v>5.43613574411544</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.511857028296482</v>
+        <v>4.646953799496167</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.78487130380725</v>
+        <v>5.985536462206909</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.75087188392839</v>
+        <v>5.915877218803544</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.561877338898199</v>
+        <v>3.766804727354618</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.544211679292573</v>
+        <v>2.763830521067334</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.361936311943836</v>
+        <v>5.523030413301804</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.648246598058826</v>
+        <v>4.790534850658034</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.004881625601421</v>
+        <v>3.139857466351671</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.599268547544412</v>
+        <v>3.701161485171333</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.465351410566939</v>
+        <v>3.597281073446325</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.084648637780241</v>
+        <v>4.917181471916692</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>5.039456274862196</v>
+        <v>5.615905200273104</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>5.718912922268643</v>
+        <v>6.314753146542756</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>5.915283010460264</v>
+        <v>6.473700896978002</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>5.593131630331946</v>
+        <v>6.398538375022717</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>6.36021718025242</v>
+        <v>7.126434361511748</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>6.284384927029144</v>
+        <v>6.964295367222284</v>
       </c>
     </row>
     <row r="16">
@@ -6648,79 +6648,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7202076533023174</v>
+        <v>0.8952430943746066</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.008148907690838</v>
+        <v>1.832768211333459</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.829764747097975</v>
+        <v>4.720085943761411</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7.565086589724203</v>
+        <v>7.875218261718473</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.432135873769219</v>
+        <v>7.599660121619138</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.807743033497438</v>
+        <v>7.164877751285857</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7.252832889160835</v>
+        <v>8.144943668047219</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>6.771781687815476</v>
+        <v>7.642784565861476</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>8.233147165876218</v>
+        <v>9.348622745762562</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.068750759616591</v>
+        <v>9.341525885651691</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.908733322671019</v>
+        <v>7.24689699493058</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.615785136261565</v>
+        <v>5.984121746573692</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.535219418289834</v>
+        <v>7.827809510779723</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.314140541843244</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5.047477974485794</v>
+        <v>6.502943749907324</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>5.236185383244205</v>
+        <v>6.669770451172738</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.305108002859029</v>
+        <v>6.763128698224854</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.822985351776182</v>
+        <v>8.010915204503092</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>7.038876732700508</v>
+        <v>8.225377431648866</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>8.03708156903771</v>
+        <v>9.228918511816332</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>8.30589442744084</v>
+        <v>9.647667304321189</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>8.230048466031739</v>
+        <v>9.572504782365904</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>9.518721961475251</v>
+        <v>10.80233256152989</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>9.037210195067395</v>
+        <v>10.24571624968619</v>
       </c>
     </row>
     <row r="17">
@@ -6733,76 +6733,76 @@
         <v>619</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4787005440801479</v>
+        <v>0.576920929401517</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.597881742499318</v>
+        <v>1.784972090466631</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.713982241125841</v>
+        <v>4.084397536232565</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.26274066110151</v>
+        <v>5.753707776842752</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.280746634434692</v>
+        <v>4.831946082623872</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.306161932002183</v>
+        <v>4.827328800092069</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.341967690761265</v>
+        <v>4.840001230508783</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.06375624600819</v>
+        <v>4.535080787100163</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.882303201751654</v>
+        <v>6.440069470613032</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>7.209549076603693</v>
+        <v>7.744179526282224</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.706548944936863</v>
+        <v>6.239354767057804</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.620045098839434</v>
+        <v>5.155018369937075</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.404799025521278</v>
+        <v>6.948042246024265</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7.314576368783889</v>
+        <v>7.830664404300357</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.848678628553891</v>
+        <v>6.340755579765862</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>6.443065550496883</v>
+        <v>6.902059598585524</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.986046636459648</v>
+        <v>6.475077409800754</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.688960375287905</v>
+        <v>7.149947747288593</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.904851756212231</v>
+        <v>7.364409974434366</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>7.253248454710132</v>
+        <v>7.740547308023224</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>7.841558506453318</v>
+        <v>8.303959026351706</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>7.281059879454553</v>
+        <v>7.744143838806757</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>8.201738146056144</v>
+        <v>8.633981878204672</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>7.479702338713331</v>
+        <v>7.825639329795671</v>
       </c>
     </row>
     <row r="18">
@@ -6815,76 +6815,76 @@
         <v>752</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.6144720355041997</v>
+        <v>0.7126924208255687</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.274376088218219</v>
+        <v>2.461466436185532</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.293803847697859</v>
+        <v>4.664219142804583</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.575530679318952</v>
+        <v>6.066497795060194</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.441867866346151</v>
+        <v>4.993067314535331</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.229897882230759</v>
+        <v>4.751064750320644</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.255821538765936</v>
+        <v>4.753855078513453</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4.908461157842659</v>
+        <v>5.379785698934633</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>6.678671744012682</v>
+        <v>7.236438012874061</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>7.501500748827254</v>
+        <v>8.036131198505785</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>6.578751880350872</v>
+        <v>7.111557702471814</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>5.635108859881612</v>
+        <v>6.170082130979253</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.772585090897827</v>
+        <v>7.315828311400814</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7.748314725089529</v>
+        <v>8.264402760605996</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6.95719270410472</v>
+        <v>7.449269655316691</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>7.019664732430684</v>
+        <v>7.478658780519325</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>6.220853978431933</v>
+        <v>6.709884751773039</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>6.381970721419279</v>
+        <v>6.842958093419966</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>6.597862102343605</v>
+        <v>7.05742032056574</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>6.651729188907368</v>
+        <v>7.13902804222046</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>6.641097914558351</v>
+        <v>7.103498434456739</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>6.56525195314925</v>
+        <v>7.028335912501454</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>7.637599006056845</v>
+        <v>8.069842738205374</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>7.295809306025056</v>
+        <v>7.641746297107396</v>
       </c>
     </row>
     <row r="19">
@@ -6897,76 +6897,76 @@
         <v>885</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2574579713137979</v>
+        <v>0.3556783566351669</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.278613376353803</v>
+        <v>1.465703724321116</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.665453084384971</v>
+        <v>3.035868379491696</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.760408669462002</v>
+        <v>4.251375785203244</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.311623846632237</v>
+        <v>3.862823294821418</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.707629580752226</v>
+        <v>3.228796448842111</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.404607450534186</v>
+        <v>3.902640990281704</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.143345158323484</v>
+        <v>4.614669699415458</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.201781492780555</v>
+        <v>5.759547761641933</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.219826268721476</v>
+        <v>5.754456718400007</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.137953707493566</v>
+        <v>4.670759529614507</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.842255151503188</v>
+        <v>3.37722842260083</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.849036587471936</v>
+        <v>3.392279807974923</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.966940761872806</v>
+        <v>3.483028797389274</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.308797464292248</v>
+        <v>2.800874415504218</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.338212634822803</v>
+        <v>2.797206682911444</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.865312446997876</v>
+        <v>2.354343220338983</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.873466093459179</v>
+        <v>2.334453465459866</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.202351824665996</v>
+        <v>2.661910042888131</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.050214583786556</v>
+        <v>2.537513437099648</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.185634517515446</v>
+        <v>2.648035037413834</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.222782906388836</v>
+        <v>2.68586686574104</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.627201121695748</v>
+        <v>4.059444853844276</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>3.325380167907497</v>
+        <v>3.671317158989837</v>
       </c>
     </row>
     <row r="20">
@@ -6979,76 +6979,76 @@
         <v>1091</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3869516047243593</v>
+        <v>-0.2887312194029903</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.6300693746598753</v>
+        <v>-0.4429790266925622</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.773341457152398</v>
+        <v>1.143756752259122</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.885318693438343</v>
+        <v>1.376285809179585</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1837440064233107</v>
+        <v>0.3674554417658698</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9133681044689297</v>
+        <v>-0.3922012363790444</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.13536261787349</v>
+        <v>-0.6373290781259726</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7719608637264699</v>
+        <v>-0.3006363226344959</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1805195113259686</v>
+        <v>0.3772467575354099</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.03684490321947465</v>
+        <v>0.4977855464590561</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7710345736148412</v>
+        <v>-0.2382287514938994</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.783056204377218</v>
+        <v>-1.248082933279576</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.806309930261762</v>
+        <v>-1.263066709758775</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.385775607808256</v>
+        <v>-0.8696875722917881</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.677282791731621</v>
+        <v>-1.18520584051965</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.541191011860121</v>
+        <v>-1.08219696377148</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.766767177251893</v>
+        <v>-1.277736403910787</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.688289824244478</v>
+        <v>-1.227302452243791</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.472398443320152</v>
+        <v>-1.012840225098017</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.285552633352125</v>
+        <v>-0.7982537800390332</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.094826574003761</v>
+        <v>-0.6324260541053732</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.170672535412862</v>
+        <v>-0.7075885760606582</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.07126656720211599</v>
+        <v>0.3609771649464122</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3304168772539882</v>
+        <v>0.01552011382835161</v>
       </c>
     </row>
     <row r="21">
@@ -7061,76 +7061,76 @@
         <v>1297</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.02145049643695529</v>
+        <v>0.1196708817583243</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1591242972867946</v>
+        <v>0.02796605068051861</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.5616847184470615</v>
+        <v>0.9321000135537858</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6968417244476512</v>
+        <v>1.187808840188893</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.02445375966478025</v>
+        <v>0.5267456885244002</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6855985990107314</v>
+        <v>-0.1644317309208461</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9949412690228954</v>
+        <v>-0.4969077292753781</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3479406860196121</v>
+        <v>0.1233838550723618</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.001950505147213732</v>
+        <v>0.5597167740085922</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.385549863806169</v>
+        <v>0.9201803134846998</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1199024897768908</v>
+        <v>0.6527083118978325</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7756549321753496</v>
+        <v>-0.2406816610777085</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.8965039689620795</v>
+        <v>-0.3532607484590926</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8862798384695836</v>
+        <v>-0.3701918029531157</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.390221131424084</v>
+        <v>-0.898144180212114</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.412642227985323</v>
+        <v>-0.9536481798966818</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.623660367275825</v>
+        <v>-1.134629593934719</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.728501071097007</v>
+        <v>-1.26751369909632</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.512609690172681</v>
+        <v>-1.053051471950546</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.942571898708898</v>
+        <v>-1.455273045395806</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.099613055109785</v>
+        <v>-1.637212535211397</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.329661021144943</v>
+        <v>-1.866577061792739</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.361277287845617</v>
+        <v>-0.9290335556970888</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.437109541068892</v>
+        <v>-1.091172549986553</v>
       </c>
     </row>
     <row r="22">
@@ -7143,76 +7143,76 @@
         <v>1486</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.006930558923215813</v>
+        <v>0.0912898263981532</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2639454018117604</v>
+        <v>0.4510357497790736</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9120636340728225</v>
+        <v>1.282478929179547</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.8047623737148797</v>
+        <v>1.295729489456122</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3343823991487582</v>
+        <v>0.8855818473379387</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.05028532818018761</v>
+        <v>0.5714521962700729</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3851896006630611</v>
+        <v>0.1128439390844562</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.07684121568750868</v>
+        <v>0.5481657567794826</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4548021526493145</v>
+        <v>1.012568421510693</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4221287377164558</v>
+        <v>0.9567591873949866</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.2251251228124289</v>
+        <v>0.7579309449333707</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5246875377015101</v>
+        <v>0.01028573339613104</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.840312592444576</v>
+        <v>-0.2970693719415891</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7922124648534776</v>
+        <v>-0.2761244293370098</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.315766260415195</v>
+        <v>-0.8236893092032247</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.259737346547567</v>
+        <v>-0.8007432984589258</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.528243985543888</v>
+        <v>-1.039213212202782</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.56578993835565</v>
+        <v>-1.104802566354962</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.484488059450172</v>
+        <v>-1.024929841228037</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.768705506548088</v>
+        <v>-1.281406653234995</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.042072670476436</v>
+        <v>-1.579672150578048</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.252508133904385</v>
+        <v>-1.789424174552181</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.372380662337534</v>
+        <v>-0.9401369301890057</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.448212915560809</v>
+        <v>-1.102275924478469</v>
       </c>
     </row>
     <row r="23">
@@ -7225,76 +7225,76 @@
         <v>1682</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3709303476769108</v>
+        <v>-0.2727099623555418</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.05172379287571971</v>
+        <v>0.1353665550915935</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5316602496509617</v>
+        <v>0.902075544757686</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5321426154638615</v>
+        <v>1.023109731205103</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.25580517502123</v>
+        <v>0.8070046232104104</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3238652969093394</v>
+        <v>0.8450321649992247</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.03191216224855964</v>
+        <v>0.4661213774989577</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3438597461493771</v>
+        <v>0.8151842872413511</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5637060243779999</v>
+        <v>1.121472293239378</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5042267335971573</v>
+        <v>1.038857183275688</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4810212152358986</v>
+        <v>1.01382703735684</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.3328054771538405</v>
+        <v>0.2021677939438007</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.6830781266496686</v>
+        <v>-0.1398349061466817</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.4879857783637931</v>
+        <v>0.02810225715267478</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.9083169475258117</v>
+        <v>-0.4162399963138412</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.027366410838468</v>
+        <v>-0.5683723627498267</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.399095676234488</v>
+        <v>-0.9100649028933816</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.682295476369589</v>
+        <v>-1.221308104368902</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.763669255968445</v>
+        <v>-1.30411103774631</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.052447702837512</v>
+        <v>-1.565148849524419</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.535540838698914</v>
+        <v>-2.073140318800526</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.730292864317285</v>
+        <v>-2.267208904965081</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.039646927102766</v>
+        <v>-1.607403194954237</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.056026148221413</v>
+        <v>-1.710089157139073</v>
       </c>
     </row>
     <row r="24">
@@ -7304,79 +7304,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1941</v>
+        <v>1934</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7814962633546898</v>
+        <v>-0.6987797787827787</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1889160292470038</v>
+        <v>-0.1173856837731009</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2277789866369915</v>
+        <v>0.4376410002711992</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.08154315369605314</v>
+        <v>0.4140081913285414</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1512076485781577</v>
+        <v>0.2418626675683981</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.06728113275384118</v>
+        <v>0.2953836572272905</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1179521247327955</v>
+        <v>0.2241899593689212</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.01599511160635103</v>
+        <v>0.332919981317076</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.2120417989306347</v>
+        <v>0.6159678155099755</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1604038148055267</v>
+        <v>0.5438046346649941</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.3314237866943941</v>
+        <v>0.7126270329301363</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5655636383919287</v>
+        <v>-0.1844306195763252</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8644083430636158</v>
+        <v>-0.4720218063135491</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.7248483735545079</v>
+        <v>-0.3583117105594766</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.8677933197697882</v>
+        <v>-0.5234030107485665</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.200763430284297</v>
+        <v>-0.8928125389816444</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.48924007267135</v>
+        <v>-1.151811875215444</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.491041106219477</v>
+        <v>-1.181283364037853</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.790348076660429</v>
+        <v>-1.483884218588045</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.015660947784625</v>
+        <v>-1.682948238885835</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.506687280614116</v>
+        <v>-2.198686432096977</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.634053077159756</v>
+        <v>-2.325555262221854</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.998939518722004</v>
+        <v>-1.668270311586703</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.074771771945279</v>
+        <v>-1.778702997706574</v>
       </c>
     </row>
     <row r="25">
@@ -7386,79 +7386,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2165</v>
+        <v>2158</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2459279448407372</v>
+        <v>-0.1598649116138375</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.3892721621212232</v>
+        <v>0.4746731090307605</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.029775053044041</v>
+        <v>1.258903937630379</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8249041744788954</v>
+        <v>1.176232971444954</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9510074663658088</v>
+        <v>1.364066861002705</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.230352405350018</v>
+        <v>1.613678872932212</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.151244368110937</v>
+        <v>1.51368490518513</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.8730329233578615</v>
+        <v>1.208764461776511</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.822141352385735</v>
+        <v>1.244014965529196</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.7420663230005147</v>
+        <v>1.143051514795495</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.062315341605853</v>
+        <v>1.461625732365533</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1831040443934242</v>
+        <v>0.5826341393400227</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.07610825929249643</v>
+        <v>0.4872044871348393</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.006402487823841341</v>
+        <v>0.3779880345988644</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.01789451519654506</v>
+        <v>0.3445824942337339</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.2087269927916608</v>
+        <v>0.1181200626363363</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.3426441297691341</v>
+        <v>0.01423965091132828</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.3089167042600636</v>
+        <v>0.02037315464686174</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.462540334883073</v>
+        <v>-0.1358782419330353</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.6452095364624029</v>
+        <v>-0.2920054205997289</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.049187575098166</v>
+        <v>-0.7204323130833288</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.078844160063852</v>
+        <v>-0.7492556320729093</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7581800711383764</v>
+        <v>-0.4129427408631088</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.8340123243616517</v>
+        <v>-0.5287425321868682</v>
       </c>
     </row>
     <row r="26">
@@ -7468,79 +7468,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2354</v>
+        <v>2347</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3698190760487918</v>
+        <v>-0.283146540637226</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1025409140465996</v>
+        <v>0.1952755542085356</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3637572091107586</v>
+        <v>0.6022772341661309</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.07561202569181091</v>
+        <v>0.4359508768576887</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.04777402884356974</v>
+        <v>0.3734306575082513</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1391921572538095</v>
+        <v>0.5303642635063355</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.08050503980560819</v>
+        <v>0.289180845223342</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1887929501491712</v>
+        <v>0.1546907384146365</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1897866518368545</v>
+        <v>0.2400120639487682</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1130846558257659</v>
+        <v>0.2961122517289994</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2884176371432972</v>
+        <v>0.6961700187832705</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5001023695332378</v>
+        <v>-0.09170294548776781</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.433799695522751</v>
+        <v>-0.01358270673914319</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.3575123867526884</v>
+        <v>0.03643632087760551</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.4209233138999409</v>
+        <v>-0.04921188290774836</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.6761540640045283</v>
+        <v>-0.3400595470876553</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.6826285501748686</v>
+        <v>-0.3161172063627333</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.6600266031889106</v>
+        <v>-0.3211785590743972</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.7839822910836176</v>
+        <v>-0.4475770051284584</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.9794644335370037</v>
+        <v>-0.6164588174192858</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.309606183491134</v>
+        <v>-0.9708653980501225</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.215528610490722</v>
+        <v>-0.8755975834054937</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.8560921308039084</v>
+        <v>-0.5041403456771718</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.8469626168224309</v>
+        <v>-0.5384565875166984</v>
       </c>
     </row>
     <row r="27">
@@ -7550,79 +7550,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2465</v>
+        <v>2459</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2939911296591404</v>
+        <v>-0.1713838361528346</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.02031929308637359</v>
+        <v>0.2732048602310257</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.04274649151988541</v>
+        <v>0.4401192067553623</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.426799820012107</v>
+        <v>0.1320386976303283</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6814543899224645</v>
+        <v>-0.02166728974764709</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5756241064620014</v>
+        <v>0.1352663162504371</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.6579176179385584</v>
+        <v>0.07129722034591168</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.8549931600547183</v>
+        <v>-0.193005838822252</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.7323700755030913</v>
+        <v>-0.0244595448976952</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5316549198965816</v>
+        <v>0.1136887974134382</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.09532347246083361</v>
+        <v>0.5077759647391318</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.6986164864564941</v>
+        <v>-0.1343624478962653</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5236041111219407</v>
+        <v>0.009884346107071451</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3390034743839436</v>
+        <v>0.1272067428380552</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.3886275021876315</v>
+        <v>0.05431312455982606</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.6055996066138007</v>
+        <v>-0.1967305414296163</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.5772449383174489</v>
+        <v>-0.1787588004332505</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.5198138368647918</v>
+        <v>-0.189790752873499</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.5878981151696721</v>
+        <v>-0.2596502154109004</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.7661638670677746</v>
+        <v>-0.4512376127564721</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.9841664244861335</v>
+        <v>-0.6531256559731062</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.7760367266660282</v>
+        <v>-0.4606194507395642</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.5015620141839747</v>
+        <v>-0.152350653941312</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.5368263160887921</v>
+        <v>-0.2091358293408234</v>
       </c>
     </row>
     <row r="28">
@@ -7632,653 +7632,653 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2619</v>
+        <v>2634</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1471472279795023</v>
+        <v>-0.1106965043714965</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1671786846290644</v>
+        <v>0.2880686356546249</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2182776195614125</v>
+        <v>0.3985622470736203</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.001696261439789737</v>
+        <v>0.2612226193689224</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.02863411183295028</v>
+        <v>0.3269614075972385</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.196514586673743</v>
+        <v>0.5218168945206187</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2263986633790367</v>
+        <v>0.5610162626443653</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1390997806725451</v>
+        <v>0.5215489857128048</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.02785691294998571</v>
+        <v>0.4598684907704396</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.09495650991845395</v>
+        <v>0.5360202568328631</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4071986644897052</v>
+        <v>0.8461771523624932</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.05208423622306668</v>
+        <v>0.5316733169659003</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.18894507887439</v>
+        <v>0.7061251509751258</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2733263017023404</v>
+        <v>0.7991880178696533</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.3406507398987983</v>
+        <v>0.8754712544904777</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.1332049012461312</v>
+        <v>0.6783376548042597</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.1520178139059354</v>
+        <v>0.68822288585514</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.1999071597220166</v>
+        <v>0.7449481853200055</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.224885978599751</v>
+        <v>0.7698010078393125</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.06808917688393024</v>
+        <v>0.6051686436453494</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.09263186698892412</v>
+        <v>0.4548648324428441</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.0224347336485593</v>
+        <v>0.5920849842736544</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.2587269337212916</v>
+        <v>0.8205593597887955</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.2210771929073374</v>
+        <v>0.8330741053110842</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 4.44</t>
+          <t>X &lt; 4.439</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2808</v>
+        <v>2802</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5425565151413707</v>
+        <v>-0.413181493402206</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4143703505282161</v>
+        <v>-0.1967839194332441</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.0361500833199031</v>
+        <v>0.2910539843650781</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.03437168071314289</v>
+        <v>0.4098893388996672</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.01909402867868693</v>
+        <v>0.4899499754717382</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2416727503886094</v>
+        <v>0.6824454591369715</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3244249211991104</v>
+        <v>0.847534143917045</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1530510832836427</v>
+        <v>0.6492993335098518</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1589257295858175</v>
+        <v>0.5994188548582571</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.240710908250179</v>
+        <v>0.6212905459831575</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4791580147995589</v>
+        <v>0.8579636829203494</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3428587538017069</v>
+        <v>0.6525054837833437</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3949103621592656</v>
+        <v>0.6044696963467899</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.5299568418380289</v>
+        <v>0.7118544115850867</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.7977394701834015</v>
+        <v>1.046989857864432</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.6442631442631495</v>
+        <v>0.9537098897795744</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.6527961497358135</v>
+        <v>0.9423764388275728</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.83285573081492</v>
+        <v>1.187005495977999</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.8350718980640366</v>
+        <v>1.244871525380447</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.7726299587443108</v>
+        <v>1.231474319953584</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.7286592893537716</v>
+        <v>1.220197338389696</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.8308760060073581</v>
+        <v>1.344965651172657</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.9629005760392602</v>
+        <v>1.467589073818431</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.8514557872034487</v>
+        <v>1.398485404431945</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 4.471</t>
+          <t>X &lt; 4.47</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2931</v>
+        <v>2949</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1879019543256675</v>
+        <v>-0.04482341618089691</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1998027130008779</v>
+        <v>0.04722175892970171</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2096632722495571</v>
+        <v>0.4822877111104447</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.01002632623993094</v>
+        <v>0.3292231263610219</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0895060968705863</v>
+        <v>0.3240265949132635</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1843956203749499</v>
+        <v>0.54855060307424</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.3474740114123875</v>
+        <v>0.7335294222034676</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.156603877810312</v>
+        <v>0.5299945820391798</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3194359970207259</v>
+        <v>0.6917186928047414</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4489323855718226</v>
+        <v>0.8081376267844576</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.5730280135608723</v>
+        <v>0.9113966359815535</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3820652150265147</v>
+        <v>0.7024050836731561</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3664639112111132</v>
+        <v>0.6689594008286619</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5056541016223335</v>
+        <v>0.7924725512914677</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.650201822645748</v>
+        <v>0.941853776272481</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.4486426015857816</v>
+        <v>0.7458070547190232</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.4712667646666091</v>
+        <v>0.7636304691023881</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.5571223090140833</v>
+        <v>0.8540554041446597</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.5210605486303379</v>
+        <v>0.818044213159979</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.4898530788635114</v>
+        <v>0.7819876001168637</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.4789345764388813</v>
+        <v>0.7767383583453551</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.5259413931968382</v>
+        <v>0.8236234818072106</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.6505013891516711</v>
+        <v>0.9182019159911547</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.4587701718975694</v>
+        <v>0.7425449811185629</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 4.502</t>
+          <t>X &lt; 4.501</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3078</v>
+        <v>3096</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.01926252861898092</v>
+        <v>0.06429856845882398</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1856664107988664</v>
+        <v>0.252518392567822</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3462795948503512</v>
+        <v>0.3946934122535239</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.296902051377792</v>
+        <v>0.3656538325332264</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1084875875588551</v>
+        <v>0.1722790900894466</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2491265369121649</v>
+        <v>0.3151097632341902</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4001260106320288</v>
+        <v>0.4696163678218568</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1404819530674501</v>
+        <v>0.2151518861030368</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.0712242476069278</v>
+        <v>0.1364171534664607</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1900793731425736</v>
+        <v>0.2589710425230152</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1918152007663636</v>
+        <v>0.2603090968450559</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.02891523597470069</v>
+        <v>0.0987562458235729</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.05761157471480516</v>
+        <v>0.128899687634302</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1471682142307529</v>
+        <v>0.2215447370140566</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.1561946959855689</v>
+        <v>0.234756344596164</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.007610125886209573</v>
+        <v>0.07434862478342552</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.007406963017615453</v>
+        <v>0.08619011171984425</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.07810461594309714</v>
+        <v>0.004627983813257686</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.06992314413503209</v>
+        <v>0.01246399213358274</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1233684956577861</v>
+        <v>-0.04422521790308309</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1273939401171731</v>
+        <v>-0.0441401311752756</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.08644741131606537</v>
+        <v>-0.003311135010321209</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.04507103690409764</v>
+        <v>0.1303645884516627</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.07634448270208338</v>
+        <v>0.01969450756426028</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 4.533</t>
+          <t>X &lt; 4.532</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3141</v>
+        <v>3166</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1202148334706905</v>
+        <v>0.1105560878191554</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3398993256510323</v>
+        <v>0.3206257837388549</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.5952121941524382</v>
+        <v>0.5576509034812815</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.6275947312281929</v>
+        <v>0.5790594010224481</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5945745725136717</v>
+        <v>0.5409313046485522</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.6413245389292896</v>
+        <v>0.5899667069121151</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.7423703913928463</v>
+        <v>0.6922595677882626</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5458155004383087</v>
+        <v>0.4996086391435171</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.4472112365025041</v>
+        <v>0.3940744446130324</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.5800741041902313</v>
+        <v>0.5279350256167135</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.6190789220001136</v>
+        <v>0.5667791356804415</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3905680308164037</v>
+        <v>0.3398563767915519</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.5232601097983505</v>
+        <v>0.4707516634189801</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5750178318371368</v>
+        <v>0.5245051240767111</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.6343288067727357</v>
+        <v>0.5854733745326399</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.454088358978801</v>
+        <v>0.4095869334641336</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.4345053342404199</v>
+        <v>0.387465201176596</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.4122951100636314</v>
+        <v>0.3679171768896765</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.3930055469067639</v>
+        <v>0.3488932433969794</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.280927849395141</v>
+        <v>0.2352089939621891</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.2662400292245977</v>
+        <v>0.2228461043707455</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.304970747362681</v>
+        <v>0.261196432596023</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.312172729257945</v>
+        <v>0.2710835930314062</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.3827784918785895</v>
+        <v>0.3488335674397902</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 4.564</t>
+          <t>X &lt; 4.563</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3225</v>
+        <v>3250</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1309948966831982</v>
+        <v>-0.1359661720458192</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1050659557882838</v>
+        <v>0.09288452909507328</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2856792819475444</v>
+        <v>0.2609606559081428</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2986726653531235</v>
+        <v>0.2665108082686061</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1652327691454261</v>
+        <v>0.1304149320642765</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3079891557429448</v>
+        <v>0.2738973761702823</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4171581184973974</v>
+        <v>0.3836296130268764</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2492411902728833</v>
+        <v>0.2186151604400166</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1850415890350092</v>
+        <v>0.1496291764073376</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2943331176303303</v>
+        <v>0.2594833053059418</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.3084642060575788</v>
+        <v>0.273606724061402</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2021248781280747</v>
+        <v>0.1679394695132359</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.3330616445627186</v>
+        <v>0.297357277192539</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.3467641972852675</v>
+        <v>0.3126014291871329</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.4492123359419793</v>
+        <v>0.415719355981949</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.3199720683481857</v>
+        <v>0.2894812404542932</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.2664353982760517</v>
+        <v>0.2345109251867754</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.242024917142885</v>
+        <v>0.211992020964523</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.2287987995308711</v>
+        <v>0.1989456335049127</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.09347717754754825</v>
+        <v>0.06295800076574665</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.1269530649709694</v>
+        <v>0.09769037512035084</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.1626581469001209</v>
+        <v>0.1330701513332144</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.2077735189903223</v>
+        <v>0.1797172776269562</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.2435249583423911</v>
+        <v>0.2204697013627097</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 4.595</t>
+          <t>X &lt; 4.594</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3291</v>
+        <v>3309</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.08019533310608296</v>
+        <v>-0.06123417108778995</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.114324775208857</v>
+        <v>0.1292088558793125</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2324923048877068</v>
+        <v>0.2720876496092686</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2309989122241021</v>
+        <v>0.2970826617698989</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1539267465929797</v>
+        <v>0.2186196876940798</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2068996761776418</v>
+        <v>0.3022529653760557</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2984583444465656</v>
+        <v>0.395943204305091</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.2190209632843647</v>
+        <v>0.3186754765702062</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2476662221375605</v>
+        <v>0.3434674826233959</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.309102062117887</v>
+        <v>0.4072022634880739</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.3284298979697482</v>
+        <v>0.4259543105136316</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3094780664700707</v>
+        <v>0.4076307416899354</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3850958838408474</v>
+        <v>0.4848875269865545</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.4547076943380546</v>
+        <v>0.555763590899673</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.5116736841176106</v>
+        <v>0.6148526135201706</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.3969292806819382</v>
+        <v>0.5009039520727043</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.3721287677949334</v>
+        <v>0.4752839766787318</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.3764708795256055</v>
+        <v>0.481039348835381</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.3678734636325842</v>
+        <v>0.4721245412157131</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.2693961891979484</v>
+        <v>0.3424626101058337</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.2913840569965771</v>
+        <v>0.3665521912662868</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.2641684168278502</v>
+        <v>0.3698410179847968</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.2835362879264949</v>
+        <v>0.3898594509391913</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.286687070657166</v>
+        <v>0.3968371839858662</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 4.626</t>
+          <t>X &lt; 4.625</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3354</v>
+        <v>3379</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.04585706187155836</v>
+        <v>0.04349908023743154</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.08243296025613489</v>
+        <v>0.07797628622964226</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.08265333548352771</v>
+        <v>0.07441939311748058</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.008554175642530026</v>
+        <v>-0.001619861572223158</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.04517258277385849</v>
+        <v>0.03348533264360753</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1302726834725263</v>
+        <v>0.1185745681198327</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2056706901636645</v>
+        <v>0.1938909154179598</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1818370022772768</v>
+        <v>0.1707799645943879</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2403937651945398</v>
+        <v>0.2271193152976068</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2565293029284348</v>
+        <v>0.2436093606794643</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2212077568493029</v>
+        <v>0.2085819899065839</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1973615494809806</v>
+        <v>0.1848631219628913</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1613492779295385</v>
+        <v>0.148941974866581</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1957240908395264</v>
+        <v>0.1836204423422814</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.1797460221275031</v>
+        <v>0.1682527998317482</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.1079353919924984</v>
+        <v>0.09765255521482175</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.08100356663707231</v>
+        <v>0.07029557983854318</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.08321185617104021</v>
+        <v>0.07306431925986345</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.0489667877552904</v>
+        <v>0.03909880756337003</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.01530679969392423</v>
+        <v>0.005110645474530884</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.003163996088808574</v>
+        <v>-0.01271128659462306</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.03138030916910139</v>
+        <v>-0.04073593455373725</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.03711640758427848</v>
+        <v>-0.04579367121172595</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.005729663005247687</v>
+        <v>-0.0128537671190827</v>
       </c>
     </row>
   </sheetData>
